--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -601,7 +601,7 @@
         <v>45979</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45664</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44643</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45238</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45245</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45960</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>44771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>46019</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45502</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>44840</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>45734</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>45091</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45950</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>45595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45981</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45219</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>46073</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45544</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44972</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45323</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45670</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45686</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>45502</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45297</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>45994</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46034</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>46043</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>46043</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>44690</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>46070</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>46114</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>46244</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45295</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>44884</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45106</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45670</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45728</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44594</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44685</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45631</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>45478</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>44951</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45029</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>45056</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44964</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44673</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>45931</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45296</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45971</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>45979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>45995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45741</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>45072</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>46085</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>46038</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>45673</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>46177</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>46182</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>45320</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>45734</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>45775</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45763</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45791</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45799</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>45834</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44959</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>44825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44711</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>44767</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44774</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>44876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>44547</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44686</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44781</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44765</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44605</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44462</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>44713</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>44855</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44475</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44879</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44823</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44722</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44831</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44816</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44741</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44812</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44546</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44460</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44473</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44502</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44651</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>44461</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>44509</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>44739</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44692</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44691</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44797</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44544</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>44853</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44545</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44634</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44732</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44490</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44525</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44830</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44620</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>44692</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>44840</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>44764</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44743</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44711</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44467</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44552</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44728</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44831</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>44728</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>44571</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44502</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44820</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44586</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>44461</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>44728</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44785</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>44530</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>44503</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>44711</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44566</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>44704</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>44684</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>44734</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>44728</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>44692</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>44659</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45644</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45775</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45726</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45573</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>44886</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45041</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>45188</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>45068</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44503</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45041</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44862</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>44599</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45625</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45631</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45139</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>44894</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45163</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>45352</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45170</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>44994</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45642</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>45070</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>45169</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>44601</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44692</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>45001</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>45289</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>45103</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44795</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45622</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>44900</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44830</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45345</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45345</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44895</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45762</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>44783</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45621</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45533</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>45691</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45610</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45343</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45253</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45336</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45309</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45149</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>44886</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45566</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45397</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44806</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45559</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45622</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45306</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45511</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45555</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45680</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>44945</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45646</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>45426</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45176</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45425</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>45037</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45499</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>44678</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45562</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45670</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45622</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45554</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45622</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45637</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>44560</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45243</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45623</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45196</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45183</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45419</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>45236</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>45642</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45189</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>44781</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44907</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>44998</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>44608</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>45148</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>45758</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>45120</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>44811</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>45541</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45131</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45271</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45216</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45089</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>44768</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>45463</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>45671</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45677</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>45176</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45646</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45184</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>44664</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>45596</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45103</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>45915</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45884</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45166</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>46043</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>44573</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>44945</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>46019</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45497</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>45223</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>46033</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45824</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>45884</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>45610</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45525</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45434</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>44748</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45044</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45701</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45888</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45888</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45890</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>46139</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>46048</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>46136</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>45636</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45232</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>45855</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45897</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>45897</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>46043</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>45896</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>46136</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45861</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>46135</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>45896</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>45896</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>45896</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>45897</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45898</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45169</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44886</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45546</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45546</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>45903</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>45509</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>45904</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45904</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26228,7 +26228,7 @@
         <v>45259</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>45908</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45909</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>44874</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>46048</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>46026</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>45908</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>45951</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>45884</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>46055</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>46021</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>46140</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>44833</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>45911</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>46031</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>44788</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45915</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>46084</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>46054</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45915</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>46070</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>46069</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>46048</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>45880</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>45170</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>46140</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>45917</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>46098</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>44607</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
         <v>44824</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>45917</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>44644</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28614,7 +28614,7 @@
         <v>45917</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>46038</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>45919</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>45918</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>45918</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>45324</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>45918</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>45566</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>45789</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>45923</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45489</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>45924</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45544</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45924</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45925</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45250</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45912</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45931</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45641</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45642</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>46146</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45931</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>44964</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>46119</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>45579</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>45936</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>46146</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>45936</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45936</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>46035</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>45936</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>45429</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45429</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45937</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>45938</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>45938</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>45938</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>45938</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46146</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45939</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>46146</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>45938</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>45938</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>46038</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>46055</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>45938</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>45938</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45938</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>44915</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>45042</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>45939</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45537</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>45938</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45937</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45939</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>45939</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45938</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>46030</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>45618</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>45313</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45712</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45089</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>45946</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45079</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45947</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>46149</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45946</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>45946</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>46149</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45947</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45947</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46078</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>45938</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45208</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>45043</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45950</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45950</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>44832</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>45950</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45951</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45222</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>44686</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>46128</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>44601</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>45741</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>44704</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45636</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>45141</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45946</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45222</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>44652</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>45297</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>45624</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>45729</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>45743</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45958</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>45959</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45960</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>46155</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45965</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45303</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>44783</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>46119</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>45568</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>46042</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45545</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>45537</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>45273</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36613,7 +36613,7 @@
         <v>45748</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45971</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45971</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>46155</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>46100</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>46026</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>45971</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>44616</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45968</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45971</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45020</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45020</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>45197</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45973</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45973</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>44987</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45973</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45973</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>45973</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>46155</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45428</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>46035</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45607</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45974</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>45974</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>45979</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>45631</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>45618</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>45546</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>45981</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>44512</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45980</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>45980</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>45246</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>46052</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45985</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>45628</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>44811</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>45603</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45603</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44790</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>45579</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>46157</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39842,7 +39842,7 @@
         <v>45985</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45985</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>45985</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>45986</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>45399</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>45635</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>45525</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>45985</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45537</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45987</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>46161</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>46160</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>45993</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45622</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>45622</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>45667</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41030,7 +41030,7 @@
         <v>45670</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>45287</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41181,7 +41181,7 @@
         <v>45455</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>44596</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>46043</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41405,7 +41405,7 @@
         <v>46163</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>44777</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>46051</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>45566</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>46136</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
         <v>45758</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41853,7 +41853,7 @@
         <v>45618</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>45686</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45995</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>46111</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>45994</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45999</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>44552</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45604</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>46000</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>46164</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>46167</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42676,7 +42676,7 @@
         <v>46000</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>44797</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>46003</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>45532</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44812</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>46164</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45601</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>46006</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>46006</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>46167</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>46167</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>45499</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>45140</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>46169</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>46008</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45231</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45671</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45950</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45090</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>44797</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>46168</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>45072</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>46021</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44400,7 +44400,7 @@
         <v>46024</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>46026</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>46170</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>44960</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>46030</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45170</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44853,7 +44853,7 @@
         <v>46031</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45121</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44999,7 +44999,7 @@
         <v>46030</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         <v>46170</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         <v>46030</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>46034</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>46042</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>46035</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>46035</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>46037</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>46035</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>45058</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45734,7 +45734,7 @@
         <v>46037</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45541</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>46037</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45958,7 +45958,7 @@
         <v>46041</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>45733</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>46038</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46182,7 +46182,7 @@
         <v>45757</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>46038</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46333,7 +46333,7 @@
         <v>46039</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45373</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>46043</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>45636</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>46043</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46708,7 +46708,7 @@
         <v>46043</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>46043</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>46043</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>46043</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>46043</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>46042</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>46042</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>46042</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47292,7 +47292,7 @@
         <v>46043</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47365,7 +47365,7 @@
         <v>46043</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47438,7 +47438,7 @@
         <v>46029</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47511,7 +47511,7 @@
         <v>46030</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47584,7 +47584,7 @@
         <v>45034</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44690</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>46171</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>46044</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>46044</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47954,7 +47954,7 @@
         <v>46044</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>46045</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
         <v>46045</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48173,7 +48173,7 @@
         <v>46045</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>46044</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>46171</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>46044</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
         <v>46171</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>46069</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48616,7 +48616,7 @@
         <v>46048</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>46043</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>46176</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>46048</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>46175</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>46048</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>46048</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>46175</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>46136</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>45579</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>46051</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         <v>46051</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>45140</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49575,7 +49575,7 @@
         <v>46050</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>46050</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>46050</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>46050</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49882,7 +49882,7 @@
         <v>46051</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>46051</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>46053</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>46055</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>46051</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>46043</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>46055</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>46055</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50476,7 +50476,7 @@
         <v>46052</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50549,7 +50549,7 @@
         <v>45204</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>46053</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>46042</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50768,7 +50768,7 @@
         <v>45631</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>46056</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50914,7 +50914,7 @@
         <v>46079</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>46057</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>46057</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>44930</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>44938</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>46057</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>46056</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>45297</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51513,7 +51513,7 @@
         <v>46079</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>46177</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>44960</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51737,7 +51737,7 @@
         <v>46178</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51815,7 +51815,7 @@
         <v>46062</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51888,7 +51888,7 @@
         <v>46062</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>46062</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>46062</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52107,7 +52107,7 @@
         <v>46062</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52185,7 +52185,7 @@
         <v>45364</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52263,7 +52263,7 @@
         <v>46062</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>45539</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>46179</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52482,7 +52482,7 @@
         <v>46177</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52555,7 +52555,7 @@
         <v>46063</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52628,7 +52628,7 @@
         <v>46062</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>46063</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52774,7 +52774,7 @@
         <v>46064</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52847,7 +52847,7 @@
         <v>46064</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52920,7 +52920,7 @@
         <v>45358</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52998,7 +52998,7 @@
         <v>46065</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53071,7 +53071,7 @@
         <v>46064</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53144,7 +53144,7 @@
         <v>46064</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53217,7 +53217,7 @@
         <v>45754</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>46065</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53373,7 +53373,7 @@
         <v>46064</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53446,7 +53446,7 @@
         <v>44952</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53524,7 +53524,7 @@
         <v>46069</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53597,7 +53597,7 @@
         <v>46066</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53670,7 +53670,7 @@
         <v>46069</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>46084</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53816,7 +53816,7 @@
         <v>46066</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>46069</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>46071</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54040,7 +54040,7 @@
         <v>46030</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>46071</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54191,7 +54191,7 @@
         <v>46071</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54264,7 +54264,7 @@
         <v>46071</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>46070</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54410,7 +54410,7 @@
         <v>46070</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>46181</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54561,7 +54561,7 @@
         <v>46071</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54634,7 +54634,7 @@
         <v>46071</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>46070</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54780,7 +54780,7 @@
         <v>45582</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54858,7 +54858,7 @@
         <v>46073</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>46182</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>46072</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>46072</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55155,7 +55155,7 @@
         <v>46073</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55228,7 +55228,7 @@
         <v>46072</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>46181</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55384,7 +55384,7 @@
         <v>44713</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55457,7 +55457,7 @@
         <v>46076</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55530,7 +55530,7 @@
         <v>44765</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55603,7 +55603,7 @@
         <v>46073</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55676,7 +55676,7 @@
         <v>46076</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>46183</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>46078</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45545</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55973,7 +55973,7 @@
         <v>46079</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56051,7 +56051,7 @@
         <v>46079</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56124,7 +56124,7 @@
         <v>46079</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56197,7 +56197,7 @@
         <v>46080</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56275,7 +56275,7 @@
         <v>46084</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>46184</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>46084</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56499,7 +56499,7 @@
         <v>46084</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56572,7 +56572,7 @@
         <v>46188</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56645,7 +56645,7 @@
         <v>46084</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>46084</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>46084</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56864,7 +56864,7 @@
         <v>45637</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56937,7 +56937,7 @@
         <v>46188</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57015,7 +57015,7 @@
         <v>45063</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>46086</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57166,7 +57166,7 @@
         <v>46185</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57239,7 +57239,7 @@
         <v>46188</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57312,7 +57312,7 @@
         <v>46188</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>46043</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57463,7 +57463,7 @@
         <v>46087</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57536,7 +57536,7 @@
         <v>46188</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>45037</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57682,7 +57682,7 @@
         <v>45149</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>46087</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57828,7 +57828,7 @@
         <v>45175</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57901,7 +57901,7 @@
         <v>44900</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57979,7 +57979,7 @@
         <v>44900</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>46185</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58135,7 +58135,7 @@
         <v>44704</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58208,7 +58208,7 @@
         <v>46188</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58281,7 +58281,7 @@
         <v>45607</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58359,7 +58359,7 @@
         <v>45607</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>45616</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58510,7 +58510,7 @@
         <v>46090</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58583,7 +58583,7 @@
         <v>46090</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>45590</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58729,7 +58729,7 @@
         <v>46092</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58807,7 +58807,7 @@
         <v>46031</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58880,7 +58880,7 @@
         <v>44763</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58958,7 +58958,7 @@
         <v>45545</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>45154</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59109,7 +59109,7 @@
         <v>45504</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59182,7 +59182,7 @@
         <v>46093</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>45902</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59328,7 +59328,7 @@
         <v>45219</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45695</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59479,7 +59479,7 @@
         <v>46098</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59552,7 +59552,7 @@
         <v>46098</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59625,7 +59625,7 @@
         <v>46098</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59703,7 +59703,7 @@
         <v>46097</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59776,7 +59776,7 @@
         <v>44679</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59854,7 +59854,7 @@
         <v>46098</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59932,7 +59932,7 @@
         <v>46099</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60010,7 +60010,7 @@
         <v>45617</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60088,7 +60088,7 @@
         <v>46099</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60166,7 +60166,7 @@
         <v>46195</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60239,7 +60239,7 @@
         <v>44628</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60312,7 +60312,7 @@
         <v>46196</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45607</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60458,7 +60458,7 @@
         <v>46195</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60531,7 +60531,7 @@
         <v>46195</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60604,7 +60604,7 @@
         <v>46196</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60682,7 +60682,7 @@
         <v>46196</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         <v>45617</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60838,7 +60838,7 @@
         <v>46104</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>46104</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60984,7 +60984,7 @@
         <v>46125</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61057,7 +61057,7 @@
         <v>45719</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61135,7 +61135,7 @@
         <v>46198</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61213,7 +61213,7 @@
         <v>45729</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61291,7 +61291,7 @@
         <v>44739</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>45574</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45173</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61510,7 +61510,7 @@
         <v>46107</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>46198</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61666,7 +61666,7 @@
         <v>46198</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61739,7 +61739,7 @@
         <v>46178</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61812,7 +61812,7 @@
         <v>45644</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>46197</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61963,7 +61963,7 @@
         <v>44938</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62036,7 +62036,7 @@
         <v>46111</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>46111</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62187,7 +62187,7 @@
         <v>46198</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62260,7 +62260,7 @@
         <v>46111</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62338,7 +62338,7 @@
         <v>45187</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62411,7 +62411,7 @@
         <v>46112</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62484,7 +62484,7 @@
         <v>46112</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62562,7 +62562,7 @@
         <v>46112</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>46111</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62713,7 +62713,7 @@
         <v>46111</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>46111</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62869,7 +62869,7 @@
         <v>45062</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>46113</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63020,7 +63020,7 @@
         <v>46113</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63093,7 +63093,7 @@
         <v>46118</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63166,7 +63166,7 @@
         <v>46120</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63239,7 +63239,7 @@
         <v>46119</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63312,7 +63312,7 @@
         <v>46119</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63385,7 +63385,7 @@
         <v>44952</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63463,7 +63463,7 @@
         <v>44952</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63541,7 +63541,7 @@
         <v>46120</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63614,7 +63614,7 @@
         <v>46119</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63687,7 +63687,7 @@
         <v>46120</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63760,7 +63760,7 @@
         <v>46120</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63833,7 +63833,7 @@
         <v>46120</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>46120</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63979,7 +63979,7 @@
         <v>45513</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64057,7 +64057,7 @@
         <v>46120</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64130,7 +64130,7 @@
         <v>44551</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64203,7 +64203,7 @@
         <v>45142</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64281,7 +64281,7 @@
         <v>45142</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64359,7 +64359,7 @@
         <v>46122</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64432,7 +64432,7 @@
         <v>46202</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64505,7 +64505,7 @@
         <v>46244</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64578,7 +64578,7 @@
         <v>46126</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64656,7 +64656,7 @@
         <v>45462</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64729,7 +64729,7 @@
         <v>46126</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64807,7 +64807,7 @@
         <v>46062</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64880,7 +64880,7 @@
         <v>46125</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64953,7 +64953,7 @@
         <v>46126</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65031,7 +65031,7 @@
         <v>44729</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65104,7 +65104,7 @@
         <v>46100</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65177,7 +65177,7 @@
         <v>45770</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65250,7 +65250,7 @@
         <v>44868</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65328,7 +65328,7 @@
         <v>46244</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65401,7 +65401,7 @@
         <v>46133</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65474,7 +65474,7 @@
         <v>46127</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65547,7 +65547,7 @@
         <v>45252</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65620,7 +65620,7 @@
         <v>45603</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65698,7 +65698,7 @@
         <v>45489</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65776,7 +65776,7 @@
         <v>45463</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65854,7 +65854,7 @@
         <v>45617</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65932,7 +65932,7 @@
         <v>44869</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66005,7 +66005,7 @@
         <v>46112</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66078,7 +66078,7 @@
         <v>45687</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66151,7 +66151,7 @@
         <v>45771</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66229,7 +66229,7 @@
         <v>44999</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66302,7 +66302,7 @@
         <v>46134</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66380,7 +66380,7 @@
         <v>44965</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66453,7 +66453,7 @@
         <v>46134</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66531,7 +66531,7 @@
         <v>44939</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66604,7 +66604,7 @@
         <v>45639</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66677,7 +66677,7 @@
         <v>45020</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66755,7 +66755,7 @@
         <v>45271</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66833,7 +66833,7 @@
         <v>45642</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66906,7 +66906,7 @@
         <v>46136</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66979,7 +66979,7 @@
         <v>46030</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67052,7 +67052,7 @@
         <v>46073</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67125,7 +67125,7 @@
         <v>45632</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67203,7 +67203,7 @@
         <v>46021</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67276,7 +67276,7 @@
         <v>44547</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67349,7 +67349,7 @@
         <v>45223</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67427,7 +67427,7 @@
         <v>44589</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67500,7 +67500,7 @@
         <v>46204</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67578,7 +67578,7 @@
         <v>45593</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67651,7 +67651,7 @@
         <v>44985</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67729,7 +67729,7 @@
         <v>45622</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67807,7 +67807,7 @@
         <v>46206</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67880,7 +67880,7 @@
         <v>45372</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67958,7 +67958,7 @@
         <v>45019</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68031,7 +68031,7 @@
         <v>45770</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68104,7 +68104,7 @@
         <v>46206</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68177,7 +68177,7 @@
         <v>46206</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68250,7 +68250,7 @@
         <v>46251</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68328,7 +68328,7 @@
         <v>44720</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68401,7 +68401,7 @@
         <v>45382</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68474,7 +68474,7 @@
         <v>44844</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68552,7 +68552,7 @@
         <v>44967</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68630,7 +68630,7 @@
         <v>44943</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68703,7 +68703,7 @@
         <v>46253</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68781,7 +68781,7 @@
         <v>46209</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68854,7 +68854,7 @@
         <v>45567</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68927,7 +68927,7 @@
         <v>45636</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69005,7 +69005,7 @@
         <v>45624</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69078,7 +69078,7 @@
         <v>46209</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69151,7 +69151,7 @@
         <v>45632</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69229,7 +69229,7 @@
         <v>46209</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69302,7 +69302,7 @@
         <v>46209</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69375,7 +69375,7 @@
         <v>46253</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69453,7 +69453,7 @@
         <v>46253</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69531,7 +69531,7 @@
         <v>46253</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69604,7 +69604,7 @@
         <v>45763</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69682,7 +69682,7 @@
         <v>45271</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69755,7 +69755,7 @@
         <v>46213</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69828,7 +69828,7 @@
         <v>46213</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69901,7 +69901,7 @@
         <v>44808</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69974,7 +69974,7 @@
         <v>46255</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70047,7 +70047,7 @@
         <v>45019</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70120,7 +70120,7 @@
         <v>44603</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70193,7 +70193,7 @@
         <v>45622</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70266,7 +70266,7 @@
         <v>46254</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70344,7 +70344,7 @@
         <v>44967</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70417,7 +70417,7 @@
         <v>44967</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70490,7 +70490,7 @@
         <v>45544</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70563,7 +70563,7 @@
         <v>45617</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70641,7 +70641,7 @@
         <v>46066</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70714,7 +70714,7 @@
         <v>44907</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70792,7 +70792,7 @@
         <v>46259</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70870,7 +70870,7 @@
         <v>45539</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70943,7 +70943,7 @@
         <v>46259</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71016,7 +71016,7 @@
         <v>45604</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71094,7 +71094,7 @@
         <v>45607</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71167,7 +71167,7 @@
         <v>45545</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71245,7 +71245,7 @@
         <v>46213</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71318,7 +71318,7 @@
         <v>46258</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71391,7 +71391,7 @@
         <v>46043</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71464,7 +71464,7 @@
         <v>46184</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71537,7 +71537,7 @@
         <v>45422</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71615,7 +71615,7 @@
         <v>45618</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71693,7 +71693,7 @@
         <v>45076</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71766,7 +71766,7 @@
         <v>45439</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71839,7 +71839,7 @@
         <v>46184</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71912,7 +71912,7 @@
         <v>46184</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71985,7 +71985,7 @@
         <v>44699</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72058,7 +72058,7 @@
         <v>45357</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72131,7 +72131,7 @@
         <v>45175</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72204,7 +72204,7 @@
         <v>45733</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72282,7 +72282,7 @@
         <v>46261</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72355,7 +72355,7 @@
         <v>45615</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72428,7 +72428,7 @@
         <v>44964</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72506,7 +72506,7 @@
         <v>46220</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72579,7 +72579,7 @@
         <v>46220</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72657,7 +72657,7 @@
         <v>44908</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72735,7 +72735,7 @@
         <v>46265</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72813,7 +72813,7 @@
         <v>45422</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72891,7 +72891,7 @@
         <v>46262</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72964,7 +72964,7 @@
         <v>46220</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73042,7 +73042,7 @@
         <v>46220</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73115,7 +73115,7 @@
         <v>45506</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73193,7 +73193,7 @@
         <v>44595</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73266,7 +73266,7 @@
         <v>45622</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73344,7 +73344,7 @@
         <v>45622</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73422,7 +73422,7 @@
         <v>45177</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73500,7 +73500,7 @@
         <v>45719</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73578,7 +73578,7 @@
         <v>45260</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73651,7 +73651,7 @@
         <v>45687</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73724,7 +73724,7 @@
         <v>45741</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73797,7 +73797,7 @@
         <v>46223</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73870,7 +73870,7 @@
         <v>44859</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73943,7 +73943,7 @@
         <v>46223</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74021,7 +74021,7 @@
         <v>45545</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74094,7 +74094,7 @@
         <v>44502</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74167,7 +74167,7 @@
         <v>45124</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74240,7 +74240,7 @@
         <v>44789</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74313,7 +74313,7 @@
         <v>44789</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74386,7 +74386,7 @@
         <v>45489</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74464,7 +74464,7 @@
         <v>45301</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74537,7 +74537,7 @@
         <v>45636</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74610,7 +74610,7 @@
         <v>46007</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74683,7 +74683,7 @@
         <v>45763</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74756,7 +74756,7 @@
         <v>46226</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74829,7 +74829,7 @@
         <v>46269</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74902,7 +74902,7 @@
         <v>46007</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -74975,7 +74975,7 @@
         <v>46226</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75048,7 +75048,7 @@
         <v>45777</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75126,7 +75126,7 @@
         <v>46227</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75199,7 +75199,7 @@
         <v>45763</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75277,7 +75277,7 @@
         <v>45763</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75355,7 +75355,7 @@
         <v>45783</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75428,7 +75428,7 @@
         <v>46273</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75506,7 +75506,7 @@
         <v>46272</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75579,7 +75579,7 @@
         <v>46273</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75652,7 +75652,7 @@
         <v>44999</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75725,7 +75725,7 @@
         <v>46272</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75798,7 +75798,7 @@
         <v>46273</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75871,7 +75871,7 @@
         <v>45498</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75949,7 +75949,7 @@
         <v>45784</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76022,7 +76022,7 @@
         <v>46275</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76095,7 +76095,7 @@
         <v>46274</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76168,7 +76168,7 @@
         <v>46274</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76241,7 +76241,7 @@
         <v>46231</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76314,7 +76314,7 @@
         <v>45120</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76387,7 +76387,7 @@
         <v>46234</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76465,7 +76465,7 @@
         <v>45786</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76543,7 +76543,7 @@
         <v>45786</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76621,7 +76621,7 @@
         <v>44525</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76699,7 +76699,7 @@
         <v>44788</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76772,7 +76772,7 @@
         <v>45758</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76850,7 +76850,7 @@
         <v>46280</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76923,7 +76923,7 @@
         <v>45790</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -76996,7 +76996,7 @@
         <v>45791</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77069,7 +77069,7 @@
         <v>46280</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77142,7 +77142,7 @@
         <v>45791</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77215,7 +77215,7 @@
         <v>45791</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77288,7 +77288,7 @@
         <v>45754</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77366,7 +77366,7 @@
         <v>45055</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77439,7 +77439,7 @@
         <v>46238</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77512,7 +77512,7 @@
         <v>45793</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77590,7 +77590,7 @@
         <v>45236</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77668,7 +77668,7 @@
         <v>45792</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77741,7 +77741,7 @@
         <v>45793</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77819,7 +77819,7 @@
         <v>45796</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77897,7 +77897,7 @@
         <v>45191</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77970,7 +77970,7 @@
         <v>46241</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78043,7 +78043,7 @@
         <v>45796</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78116,7 +78116,7 @@
         <v>45569</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78194,7 +78194,7 @@
         <v>46283</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78267,7 +78267,7 @@
         <v>46184</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78340,7 +78340,7 @@
         <v>45799</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78418,7 +78418,7 @@
         <v>45463</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78491,7 +78491,7 @@
         <v>45540</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78564,7 +78564,7 @@
         <v>45586</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78637,7 +78637,7 @@
         <v>45532</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78710,7 +78710,7 @@
         <v>45799</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78788,7 +78788,7 @@
         <v>46282</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78861,7 +78861,7 @@
         <v>45802</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78939,7 +78939,7 @@
         <v>45802</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79017,7 +79017,7 @@
         <v>46185</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79095,7 +79095,7 @@
         <v>45799</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79168,7 +79168,7 @@
         <v>45802</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79246,7 +79246,7 @@
         <v>44953</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79324,7 +79324,7 @@
         <v>44873</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79397,7 +79397,7 @@
         <v>45306</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79470,7 +79470,7 @@
         <v>44960</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79543,7 +79543,7 @@
         <v>45259</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79616,7 +79616,7 @@
         <v>45309</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79689,7 +79689,7 @@
         <v>45812</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79762,7 +79762,7 @@
         <v>45646</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79835,7 +79835,7 @@
         <v>45813</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79908,7 +79908,7 @@
         <v>45812</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -79986,7 +79986,7 @@
         <v>45663</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80059,7 +80059,7 @@
         <v>45817</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80137,7 +80137,7 @@
         <v>45817</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80215,7 +80215,7 @@
         <v>45817</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80293,7 +80293,7 @@
         <v>44540</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80371,7 +80371,7 @@
         <v>45824</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80449,7 +80449,7 @@
         <v>45825</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80522,7 +80522,7 @@
         <v>45826</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80600,7 +80600,7 @@
         <v>45827</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80678,7 +80678,7 @@
         <v>45826</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80756,7 +80756,7 @@
         <v>45832</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80829,7 +80829,7 @@
         <v>45832</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80907,7 +80907,7 @@
         <v>45832</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -80985,7 +80985,7 @@
         <v>45835</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81058,7 +81058,7 @@
         <v>45835</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81131,7 +81131,7 @@
         <v>45835</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81209,7 +81209,7 @@
         <v>45839</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81287,7 +81287,7 @@
         <v>45554</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81360,7 +81360,7 @@
         <v>45840</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81438,7 +81438,7 @@
         <v>45841</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81516,7 +81516,7 @@
         <v>45841</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81594,7 +81594,7 @@
         <v>45841</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81672,7 +81672,7 @@
         <v>45846</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81750,7 +81750,7 @@
         <v>45846</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81828,7 +81828,7 @@
         <v>45848</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81906,7 +81906,7 @@
         <v>45848</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81984,7 +81984,7 @@
         <v>45848</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82057,7 +82057,7 @@
         <v>45695</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82130,7 +82130,7 @@
         <v>45860</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82208,7 +82208,7 @@
         <v>45860</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82281,7 +82281,7 @@
         <v>45859</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82354,7 +82354,7 @@
         <v>45881</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82427,7 +82427,7 @@
         <v>45880</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82505,7 +82505,7 @@
         <v>45883</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82578,7 +82578,7 @@
         <v>45880</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82651,7 +82651,7 @@
         <v>45882</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82729,7 +82729,7 @@
         <v>45883</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82802,7 +82802,7 @@
         <v>45650</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82875,7 +82875,7 @@
         <v>45238</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82953,7 +82953,7 @@
         <v>45238</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83031,7 +83031,7 @@
         <v>44538</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83109,7 +83109,7 @@
         <v>45238</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83187,7 +83187,7 @@
         <v>45670</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83265,7 +83265,7 @@
         <v>45238</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83343,7 +83343,7 @@
         <v>45670</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83421,7 +83421,7 @@
         <v>45238</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83499,7 +83499,7 @@
         <v>44929</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83577,7 +83577,7 @@
         <v>45238</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83655,7 +83655,7 @@
         <v>45386</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83728,7 +83728,7 @@
         <v>45238</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83806,7 +83806,7 @@
         <v>45238</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83884,7 +83884,7 @@
         <v>45670</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83962,7 +83962,7 @@
         <v>45238</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84040,7 +84040,7 @@
         <v>45238</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84118,7 +84118,7 @@
         <v>45238</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84196,7 +84196,7 @@
         <v>45670</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84274,7 +84274,7 @@
         <v>45238</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84352,7 +84352,7 @@
         <v>45670</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84430,7 +84430,7 @@
         <v>45670</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84528,7 +84528,7 @@
         <v>46083</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -601,7 +601,7 @@
         <v>45979</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45664</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44643</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45238</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45245</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45960</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46019</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>44771</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45502</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>44840</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>46073</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45950</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>45981</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>46057</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>45595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45734</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>46210</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45091</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45219</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45544</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44972</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45323</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45670</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>46034</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>45295</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46043</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>46070</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>44884</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>46114</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>45994</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45502</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>45297</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45502</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>45686</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>46244</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45106</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45670</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45728</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44594</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44685</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45478</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45799</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>45029</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>44951</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44673</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>45931</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44711</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45971</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>45979</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>45995</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>45056</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45775</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45734</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>45834</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>46085</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>44964</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>46177</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>46182</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45631</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44586</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45673</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45320</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>46038</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>45072</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>45741</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45296</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45763</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>45791</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44959</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>44825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44767</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>44711</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44774</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>44876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>44547</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44686</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44781</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44765</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44605</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44713</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>44475</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44823</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44879</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44722</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44831</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44816</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44812</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44741</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44546</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44473</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44502</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44651</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44509</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44739</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>44692</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>44691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>44797</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44544</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>44853</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44634</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44545</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>44732</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44490</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44525</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44830</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44620</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44692</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44743</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>44840</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44764</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44711</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44467</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44552</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44728</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44831</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44728</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44502</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44571</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44820</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44586</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44728</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44785</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44530</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>44503</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44711</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44566</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44704</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44684</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>44692</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44734</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>44728</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45712</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>44790</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>44789</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>44765</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45043</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45324</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>45364</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>45183</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45541</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45741</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45419</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>44886</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45426</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44844</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45562</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45566</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45763</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>44945</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44832</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44833</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>44812</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44552</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45463</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45796</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>45489</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16566,7 +16566,7 @@
         <v>45139</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>45793</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>45950</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>45880</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>46021</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>44862</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>46024</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>45140</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>46026</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>45537</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45569</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>46030</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45191</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>45884</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>46030</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45793</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45796</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45513</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45504</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45463</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45883</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45532</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45540</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45603</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45603</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>46030</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44945</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45586</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45499</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45888</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45176</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>46034</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>46031</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>46035</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>45888</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44939</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>46035</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>45890</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>44930</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>46038</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>46037</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>46037</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>46037</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45622</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>45799</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44994</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45618</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>45855</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>45729</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>46038</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44560</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>46042</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>46042</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45896</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>46039</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>46042</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45861</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45896</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45896</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45896</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>46041</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45897</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45545</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>46043</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45897</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>46043</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45352</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>46043</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>46044</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>46043</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>46044</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>46043</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>46043</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45042</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>46043</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45897</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45898</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>46044</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>46044</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>46043</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>46043</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>46044</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>46048</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>46048</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>46048</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>46045</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45537</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>46045</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45799</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>46048</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>46069</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>46045</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45622</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>46050</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45904</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45566</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44599</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>46050</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>46050</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45903</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>46050</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45904</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45908</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>46052</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>46051</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>46051</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>46051</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>46051</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45908</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45358</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>45799</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>44900</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44900</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>45909</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>46056</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>46053</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>46053</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>46056</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>46055</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>46055</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>46055</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45301</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45802</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>46057</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>46057</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45184</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45911</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>46057</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>46062</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>45915</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>44664</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>46062</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45915</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45297</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>46079</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>46062</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>46062</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>46062</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>46062</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>45917</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>46062</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>46064</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45917</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45917</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>46063</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>46064</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>46064</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45918</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45260</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>46064</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>46064</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45918</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>45918</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>46063</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45802</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>46066</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>46066</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>46065</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45919</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45462</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>46065</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>46069</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45748</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>46069</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>46070</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45579</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>45802</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>45924</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>46070</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>45923</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>46070</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>45671</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44953</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45924</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>46069</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>46071</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>46071</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45687</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>46071</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>46071</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45925</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>46071</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30097,7 +30097,7 @@
         <v>46072</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>46030</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>46071</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>46072</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>46072</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>46076</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>46073</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44659</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>46076</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>45506</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>46073</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>45637</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44692</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>46078</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>46079</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>46079</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46073</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>46079</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45912</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>46080</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>46084</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45306</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>44873</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>46084</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45931</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>46084</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44960</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>46084</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>44967</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44967</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45931</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>46084</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>46084</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>46087</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45936</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>46087</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>46043</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>44943</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45936</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>45936</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>46086</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45259</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>45309</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>44915</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>45936</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>46031</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>46090</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>45372</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>45545</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33724,7 +33724,7 @@
         <v>45937</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>45253</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>46090</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45937</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>44589</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45938</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>45938</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>45938</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45938</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>45938</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34454,7 +34454,7 @@
         <v>45938</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>46092</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>44907</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34683,7 +34683,7 @@
         <v>45938</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34756,7 +34756,7 @@
         <v>45938</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45938</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>45938</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45938</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>45939</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>45757</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>46093</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>46097</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45939</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45939</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>45939</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45176</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>46099</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>46098</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>46098</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>46099</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>46098</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>46098</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>45946</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>45223</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45946</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45946</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>45607</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45607</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>45590</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36621,7 +36621,7 @@
         <v>46125</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>45947</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36772,7 +36772,7 @@
         <v>46104</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>46104</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36918,7 +36918,7 @@
         <v>45070</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44894</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45950</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>45947</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>45947</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>45950</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45950</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37439,7 +37439,7 @@
         <v>45951</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>46107</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>45622</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37663,7 +37663,7 @@
         <v>45812</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45938</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45624</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>46111</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>46111</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>46111</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>45958</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>46111</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>46111</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45223</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>46111</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>46112</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>46112</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>46113</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>46113</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45121</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45946</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>46112</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45271</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>45960</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>46119</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39251,7 +39251,7 @@
         <v>45582</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45579</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>46118</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>46119</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>46119</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>46120</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>46120</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45959</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>46120</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>46120</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>46120</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>46120</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>46120</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45763</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>46122</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45965</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>44960</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>45637</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>46125</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
         <v>45020</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>45020</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45567</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>44952</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>44952</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>45812</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>45090</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>46062</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>46126</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>46126</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45208</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45968</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>44704</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41642,7 +41642,7 @@
         <v>45646</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44540</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45140</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>45971</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45971</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45971</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45813</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45971</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>44704</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>45973</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45973</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>45973</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>45020</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45974</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>45973</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42772,7 +42772,7 @@
         <v>45973</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>46126</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>46100</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45642</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>45632</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>45974</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45062</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45663</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>44964</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45439</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45166</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45610</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>44729</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45429</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>45980</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45980</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>45979</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>46127</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>46134</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45646</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>46134</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45981</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>46133</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>45142</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45142</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>45616</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>45985</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>45985</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45617</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>45985</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45986</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45100,7 +45100,7 @@
         <v>44999</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45985</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45985</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45771</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45397,7 +45397,7 @@
         <v>44739</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45987</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>45636</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>46136</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>46135</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>44795</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         <v>46136</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45034</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>46112</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45817</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45993</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46215,7 +46215,7 @@
         <v>45994</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>46140</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>45995</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>46038</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>46048</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>45999</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45544</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45041</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45817</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46892,7 +46892,7 @@
         <v>46000</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>46000</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45636</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>46140</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45817</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>44987</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45250</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47418,7 +47418,7 @@
         <v>44797</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47496,7 +47496,7 @@
         <v>45625</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47569,7 +47569,7 @@
         <v>46006</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>46003</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>46139</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         <v>46006</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45610</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47939,7 +47939,7 @@
         <v>46008</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>46019</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>44985</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48168,7 +48168,7 @@
         <v>45509</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>46030</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>44895</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48392,7 +48392,7 @@
         <v>44830</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>46021</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48538,7 +48538,7 @@
         <v>46048</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48611,7 +48611,7 @@
         <v>45489</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>46054</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>46033</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>44789</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45824</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>46136</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>46026</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>45617</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>45273</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>45170</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45758</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45915</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45826</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>46043</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45826</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49746,7 +49746,7 @@
         <v>46043</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49819,7 +49819,7 @@
         <v>45525</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49897,7 +49897,7 @@
         <v>45824</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49975,7 +49975,7 @@
         <v>46021</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>46073</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50121,7 +50121,7 @@
         <v>46048</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45177</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>45624</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50350,7 +50350,7 @@
         <v>46098</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50423,7 +50423,7 @@
         <v>46070</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45825</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>44788</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>46055</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>45072</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50788,7 +50788,7 @@
         <v>45068</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50861,7 +50861,7 @@
         <v>46069</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45789</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>46031</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51090,7 +51090,7 @@
         <v>45951</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51163,7 +51163,7 @@
         <v>45827</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51241,7 +51241,7 @@
         <v>45880</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51319,7 +51319,7 @@
         <v>46084</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45231</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45884</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>46146</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51616,7 +51616,7 @@
         <v>44960</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51694,7 +51694,7 @@
         <v>46055</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>46119</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51840,7 +51840,7 @@
         <v>46030</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>46038</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51986,7 +51986,7 @@
         <v>46146</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>46035</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>46146</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52205,7 +52205,7 @@
         <v>46146</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52278,7 +52278,7 @@
         <v>44573</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>45044</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         <v>45832</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52497,7 +52497,7 @@
         <v>46078</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52570,7 +52570,7 @@
         <v>46149</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52643,7 +52643,7 @@
         <v>45832</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45148</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45832</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52872,7 +52872,7 @@
         <v>46149</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>46035</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>46128</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>46052</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>46026</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45037</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>45541</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>45646</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>46042</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>46119</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53607,7 +53607,7 @@
         <v>45222</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>46155</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53758,7 +53758,7 @@
         <v>44900</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53836,7 +53836,7 @@
         <v>46100</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53909,7 +53909,7 @@
         <v>44869</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53982,7 +53982,7 @@
         <v>46155</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45297</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>46155</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54206,7 +54206,7 @@
         <v>46157</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54284,7 +54284,7 @@
         <v>45555</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54357,7 +54357,7 @@
         <v>45573</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54430,7 +54430,7 @@
         <v>46160</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54503,7 +54503,7 @@
         <v>45835</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54581,7 +54581,7 @@
         <v>44964</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45835</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54732,7 +54732,7 @@
         <v>45835</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>44783</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45103</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54956,7 +54956,7 @@
         <v>46136</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55029,7 +55029,7 @@
         <v>45840</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45554</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55180,7 +55180,7 @@
         <v>45839</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55258,7 +55258,7 @@
         <v>46111</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>45841</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55409,7 +55409,7 @@
         <v>46051</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55482,7 +55482,7 @@
         <v>45841</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55560,7 +55560,7 @@
         <v>46043</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55633,7 +55633,7 @@
         <v>46161</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55706,7 +55706,7 @@
         <v>45841</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55784,7 +55784,7 @@
         <v>45644</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45846</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55940,7 +55940,7 @@
         <v>45846</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56018,7 +56018,7 @@
         <v>44512</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56096,7 +56096,7 @@
         <v>46164</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>46163</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>46164</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56325,7 +56325,7 @@
         <v>45848</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56403,7 +56403,7 @@
         <v>45397</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45848</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56549,7 +56549,7 @@
         <v>46168</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>46167</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56695,7 +56695,7 @@
         <v>45287</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56768,7 +56768,7 @@
         <v>45848</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>44952</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45622</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>46167</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57080,7 +57080,7 @@
         <v>46167</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57153,7 +57153,7 @@
         <v>45455</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57231,7 +57231,7 @@
         <v>46169</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>45695</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57377,7 +57377,7 @@
         <v>45079</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57455,7 +57455,7 @@
         <v>46030</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57528,7 +57528,7 @@
         <v>45860</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57606,7 +57606,7 @@
         <v>45859</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57679,7 +57679,7 @@
         <v>46171</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45271</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>46171</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>45860</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57976,7 +57976,7 @@
         <v>44938</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58049,7 +58049,7 @@
         <v>46043</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>46029</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58195,7 +58195,7 @@
         <v>46170</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>44998</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58346,7 +58346,7 @@
         <v>46171</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58419,7 +58419,7 @@
         <v>45289</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58492,7 +58492,7 @@
         <v>46170</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58565,7 +58565,7 @@
         <v>46175</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58638,7 +58638,7 @@
         <v>45604</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58716,7 +58716,7 @@
         <v>46035</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58789,7 +58789,7 @@
         <v>46175</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58867,7 +58867,7 @@
         <v>44502</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45058</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59013,7 +59013,7 @@
         <v>45041</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59091,7 +59091,7 @@
         <v>44628</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>45601</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59237,7 +59237,7 @@
         <v>46176</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59315,7 +59315,7 @@
         <v>45306</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>45141</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59461,7 +59461,7 @@
         <v>45343</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         <v>44601</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59612,7 +59612,7 @@
         <v>46177</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59690,7 +59690,7 @@
         <v>46042</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59763,7 +59763,7 @@
         <v>46136</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59836,7 +59836,7 @@
         <v>46079</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59909,7 +59909,7 @@
         <v>46177</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59982,7 +59982,7 @@
         <v>45754</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60060,7 +60060,7 @@
         <v>46084</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60133,7 +60133,7 @@
         <v>45120</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60206,7 +60206,7 @@
         <v>45463</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45525</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>46181</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>46181</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60518,7 +60518,7 @@
         <v>46051</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>46043</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60664,7 +60664,7 @@
         <v>45566</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60737,7 +60737,7 @@
         <v>46179</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60810,7 +60810,7 @@
         <v>45596</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60883,7 +60883,7 @@
         <v>46178</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>44601</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61034,7 +61034,7 @@
         <v>45618</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>45271</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>45642</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61258,7 +61258,7 @@
         <v>45076</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>44603</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61404,7 +61404,7 @@
         <v>46183</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61477,7 +61477,7 @@
         <v>46182</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>44616</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61628,7 +61628,7 @@
         <v>46185</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61706,7 +61706,7 @@
         <v>46184</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>45149</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>46185</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45170</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>44503</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>45063</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62159,7 +62159,7 @@
         <v>46188</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45618</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>46188</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62388,7 +62388,7 @@
         <v>45902</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62461,7 +62461,7 @@
         <v>46188</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62534,7 +62534,7 @@
         <v>45533</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62612,7 +62612,7 @@
         <v>45545</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62685,7 +62685,7 @@
         <v>45545</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62763,7 +62763,7 @@
         <v>46188</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62836,7 +62836,7 @@
         <v>45422</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62914,7 +62914,7 @@
         <v>45593</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>46188</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63060,7 +63060,7 @@
         <v>46188</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63133,7 +63133,7 @@
         <v>45539</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63206,7 +63206,7 @@
         <v>45574</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63279,7 +63279,7 @@
         <v>45618</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63357,7 +63357,7 @@
         <v>46195</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63430,7 +63430,7 @@
         <v>46195</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63503,7 +63503,7 @@
         <v>46195</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63576,7 +63576,7 @@
         <v>45188</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>44551</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63727,7 +63727,7 @@
         <v>45733</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63805,7 +63805,7 @@
         <v>46197</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63878,7 +63878,7 @@
         <v>44596</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63951,7 +63951,7 @@
         <v>46196</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64029,7 +64029,7 @@
         <v>45719</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64107,7 +64107,7 @@
         <v>45631</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64180,7 +64180,7 @@
         <v>45631</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64253,7 +64253,7 @@
         <v>45175</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64326,7 +64326,7 @@
         <v>46196</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64399,7 +64399,7 @@
         <v>46196</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>45173</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64550,7 +64550,7 @@
         <v>46198</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64628,7 +64628,7 @@
         <v>45170</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64706,7 +64706,7 @@
         <v>46178</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
         <v>45880</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64857,7 +64857,7 @@
         <v>45628</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64935,7 +64935,7 @@
         <v>44644</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65008,7 +65008,7 @@
         <v>45631</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65086,7 +65086,7 @@
         <v>46198</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>46198</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>45309</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65310,7 +65310,7 @@
         <v>45642</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65383,7 +65383,7 @@
         <v>46198</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65456,7 +65456,7 @@
         <v>45701</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65534,7 +65534,7 @@
         <v>45622</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65612,7 +65612,7 @@
         <v>45686</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65690,7 +65690,7 @@
         <v>45499</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65763,7 +65763,7 @@
         <v>45644</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65841,7 +65841,7 @@
         <v>45881</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65914,7 +65914,7 @@
         <v>45622</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65992,7 +65992,7 @@
         <v>44607</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66065,7 +66065,7 @@
         <v>46202</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66138,7 +66138,7 @@
         <v>45882</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66216,7 +66216,7 @@
         <v>45204</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66289,7 +66289,7 @@
         <v>45545</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66362,7 +66362,7 @@
         <v>45603</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66440,7 +66440,7 @@
         <v>45131</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66513,7 +66513,7 @@
         <v>45884</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45615</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66659,7 +66659,7 @@
         <v>44859</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66732,7 +66732,7 @@
         <v>46204</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66810,7 +66810,7 @@
         <v>45883</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66883,7 +66883,7 @@
         <v>45671</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66961,7 +66961,7 @@
         <v>45695</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67034,7 +67034,7 @@
         <v>46251</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67112,7 +67112,7 @@
         <v>46209</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67185,7 +67185,7 @@
         <v>46206</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67258,7 +67258,7 @@
         <v>46206</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67331,7 +67331,7 @@
         <v>45636</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67409,7 +67409,7 @@
         <v>45197</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67487,7 +67487,7 @@
         <v>44547</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67560,7 +67560,7 @@
         <v>46206</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67633,7 +67633,7 @@
         <v>45639</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67706,7 +67706,7 @@
         <v>46209</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67779,7 +67779,7 @@
         <v>46209</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67852,7 +67852,7 @@
         <v>45691</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67925,7 +67925,7 @@
         <v>46209</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67998,7 +67998,7 @@
         <v>45687</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68071,7 +68071,7 @@
         <v>46253</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68149,7 +68149,7 @@
         <v>45222</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68222,7 +68222,7 @@
         <v>45219</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68300,7 +68300,7 @@
         <v>46253</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68378,7 +68378,7 @@
         <v>46253</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68456,7 +68456,7 @@
         <v>45622</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68534,7 +68534,7 @@
         <v>45622</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68607,7 +68607,7 @@
         <v>46066</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68680,7 +68680,7 @@
         <v>46253</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68753,7 +68753,7 @@
         <v>44699</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68826,7 +68826,7 @@
         <v>44679</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68904,7 +68904,7 @@
         <v>44678</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68982,7 +68982,7 @@
         <v>45149</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69055,7 +69055,7 @@
         <v>46255</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69128,7 +69128,7 @@
         <v>46213</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69201,7 +69201,7 @@
         <v>45216</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69274,7 +69274,7 @@
         <v>46213</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69347,7 +69347,7 @@
         <v>44686</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69425,7 +69425,7 @@
         <v>46254</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69503,7 +69503,7 @@
         <v>46043</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69576,7 +69576,7 @@
         <v>46213</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69649,7 +69649,7 @@
         <v>46258</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69722,7 +69722,7 @@
         <v>45642</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69795,7 +69795,7 @@
         <v>46184</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69868,7 +69868,7 @@
         <v>45511</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69941,7 +69941,7 @@
         <v>44763</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70019,7 +70019,7 @@
         <v>46259</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70092,7 +70092,7 @@
         <v>44748</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70165,7 +70165,7 @@
         <v>46259</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70243,7 +70243,7 @@
         <v>45741</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70316,7 +70316,7 @@
         <v>46262</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70389,7 +70389,7 @@
         <v>45154</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70462,7 +70462,7 @@
         <v>44768</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70540,7 +70540,7 @@
         <v>45236</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70618,7 +70618,7 @@
         <v>45259</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70691,7 +70691,7 @@
         <v>46184</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70764,7 +70764,7 @@
         <v>46261</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70837,7 +70837,7 @@
         <v>46184</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70910,7 +70910,7 @@
         <v>44608</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70983,7 +70983,7 @@
         <v>44720</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71056,7 +71056,7 @@
         <v>45169</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71129,7 +71129,7 @@
         <v>45729</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71202,7 +71202,7 @@
         <v>45175</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71275,7 +71275,7 @@
         <v>45775</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71353,7 +71353,7 @@
         <v>45762</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71431,7 +71431,7 @@
         <v>46220</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71509,7 +71509,7 @@
         <v>46223</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71587,7 +71587,7 @@
         <v>46220</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71660,7 +71660,7 @@
         <v>46223</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71733,7 +71733,7 @@
         <v>45189</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71811,7 +71811,7 @@
         <v>46265</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71889,7 +71889,7 @@
         <v>46220</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71967,7 +71967,7 @@
         <v>46220</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72040,7 +72040,7 @@
         <v>44777</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72118,7 +72118,7 @@
         <v>44808</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72191,7 +72191,7 @@
         <v>46007</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72264,7 +72264,7 @@
         <v>46007</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72337,7 +72337,7 @@
         <v>45313</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72410,7 +72410,7 @@
         <v>44595</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72483,7 +72483,7 @@
         <v>46226</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72556,7 +72556,7 @@
         <v>46269</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72629,7 +72629,7 @@
         <v>44811</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72702,7 +72702,7 @@
         <v>44811</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72775,7 +72775,7 @@
         <v>46227</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72848,7 +72848,7 @@
         <v>46272</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72921,7 +72921,7 @@
         <v>46272</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72994,7 +72994,7 @@
         <v>44797</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73072,7 +73072,7 @@
         <v>45196</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73145,7 +73145,7 @@
         <v>46226</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73218,7 +73218,7 @@
         <v>46274</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73291,7 +73291,7 @@
         <v>46273</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73364,7 +73364,7 @@
         <v>44886</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73442,7 +73442,7 @@
         <v>44886</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73520,7 +73520,7 @@
         <v>46273</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73598,7 +73598,7 @@
         <v>44967</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73676,7 +73676,7 @@
         <v>46231</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73749,7 +73749,7 @@
         <v>46273</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73822,7 +73822,7 @@
         <v>44783</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73895,7 +73895,7 @@
         <v>46275</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73968,7 +73968,7 @@
         <v>46274</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74041,7 +74041,7 @@
         <v>45019</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74114,7 +74114,7 @@
         <v>45345</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74192,7 +74192,7 @@
         <v>45345</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74265,7 +74265,7 @@
         <v>45243</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74338,7 +74338,7 @@
         <v>46280</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74411,7 +74411,7 @@
         <v>44868</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74489,7 +74489,7 @@
         <v>45399</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74562,7 +74562,7 @@
         <v>46280</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74635,7 +74635,7 @@
         <v>46234</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74713,7 +74713,7 @@
         <v>45429</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74786,7 +74786,7 @@
         <v>45532</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74859,7 +74859,7 @@
         <v>46282</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74932,7 +74932,7 @@
         <v>46238</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75005,7 +75005,7 @@
         <v>46184</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75078,7 +75078,7 @@
         <v>45425</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75151,7 +75151,7 @@
         <v>45641</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75224,7 +75224,7 @@
         <v>44965</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75297,7 +75297,7 @@
         <v>45743</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75375,7 +75375,7 @@
         <v>46185</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75453,7 +75453,7 @@
         <v>46283</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75526,7 +75526,7 @@
         <v>46241</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75599,7 +75599,7 @@
         <v>45489</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75677,7 +75677,7 @@
         <v>46288</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75755,7 +75755,7 @@
         <v>44824</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75828,7 +75828,7 @@
         <v>44806</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75901,7 +75901,7 @@
         <v>44652</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75974,7 +75974,7 @@
         <v>46288</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76052,7 +76052,7 @@
         <v>45187</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76125,7 +76125,7 @@
         <v>45336</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76198,7 +76198,7 @@
         <v>46244</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76271,7 +76271,7 @@
         <v>45568</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76344,7 +76344,7 @@
         <v>46244</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76417,7 +76417,7 @@
         <v>45246</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76490,7 +76490,7 @@
         <v>45539</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76563,7 +76563,7 @@
         <v>45607</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76636,7 +76636,7 @@
         <v>46289</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76709,7 +76709,7 @@
         <v>45089</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76782,7 +76782,7 @@
         <v>45733</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76860,7 +76860,7 @@
         <v>46289</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76938,7 +76938,7 @@
         <v>45544</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77011,7 +77011,7 @@
         <v>45607</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77084,7 +77084,7 @@
         <v>44690</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77157,7 +77157,7 @@
         <v>45382</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77230,7 +77230,7 @@
         <v>45422</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77308,7 +77308,7 @@
         <v>45604</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77386,7 +77386,7 @@
         <v>45546</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77459,7 +77459,7 @@
         <v>45546</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77532,7 +77532,7 @@
         <v>45554</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77605,7 +77605,7 @@
         <v>45622</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77683,7 +77683,7 @@
         <v>45770</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77756,7 +77756,7 @@
         <v>45770</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77829,7 +77829,7 @@
         <v>45252</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77902,7 +77902,7 @@
         <v>45680</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77975,7 +77975,7 @@
         <v>45037</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78048,7 +78048,7 @@
         <v>45001</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78121,7 +78121,7 @@
         <v>45434</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78199,7 +78199,7 @@
         <v>45373</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78277,7 +78277,7 @@
         <v>45497</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78355,7 +78355,7 @@
         <v>45163</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78433,7 +78433,7 @@
         <v>45428</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78511,7 +78511,7 @@
         <v>44874</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78589,7 +78589,7 @@
         <v>45617</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78667,7 +78667,7 @@
         <v>45357</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78740,7 +78740,7 @@
         <v>45559</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78818,7 +78818,7 @@
         <v>45019</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78891,7 +78891,7 @@
         <v>45303</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78964,7 +78964,7 @@
         <v>45667</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79037,7 +79037,7 @@
         <v>45670</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79115,7 +79115,7 @@
         <v>45670</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79193,7 +79193,7 @@
         <v>45677</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79271,7 +79271,7 @@
         <v>45621</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79349,7 +79349,7 @@
         <v>45635</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79427,7 +79427,7 @@
         <v>45089</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79500,7 +79500,7 @@
         <v>45607</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79573,7 +79573,7 @@
         <v>45617</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79651,7 +79651,7 @@
         <v>45758</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79724,7 +79724,7 @@
         <v>45232</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79797,7 +79797,7 @@
         <v>45636</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79870,7 +79870,7 @@
         <v>45719</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79948,7 +79948,7 @@
         <v>45169</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80026,7 +80026,7 @@
         <v>45726</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80099,7 +80099,7 @@
         <v>45622</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80172,7 +80172,7 @@
         <v>44781</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80245,7 +80245,7 @@
         <v>45623</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80318,7 +80318,7 @@
         <v>45124</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80391,7 +80391,7 @@
         <v>45103</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80469,7 +80469,7 @@
         <v>44938</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80547,7 +80547,7 @@
         <v>44908</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80625,7 +80625,7 @@
         <v>45537</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80703,7 +80703,7 @@
         <v>44907</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80781,7 +80781,7 @@
         <v>44713</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80854,7 +80854,7 @@
         <v>45546</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80927,7 +80927,7 @@
         <v>45579</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81000,7 +81000,7 @@
         <v>45632</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81078,7 +81078,7 @@
         <v>45636</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81151,7 +81151,7 @@
         <v>45777</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81229,7 +81229,7 @@
         <v>45783</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81302,7 +81302,7 @@
         <v>45763</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81380,7 +81380,7 @@
         <v>45763</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81458,7 +81458,7 @@
         <v>44999</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81531,7 +81531,7 @@
         <v>45784</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81604,7 +81604,7 @@
         <v>45498</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81682,7 +81682,7 @@
         <v>45120</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81755,7 +81755,7 @@
         <v>45786</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81833,7 +81833,7 @@
         <v>44525</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81911,7 +81911,7 @@
         <v>45754</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81989,7 +81989,7 @@
         <v>45786</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82067,7 +82067,7 @@
         <v>45791</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82140,7 +82140,7 @@
         <v>45758</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82218,7 +82218,7 @@
         <v>45792</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82291,7 +82291,7 @@
         <v>45791</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82364,7 +82364,7 @@
         <v>45055</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82437,7 +82437,7 @@
         <v>45236</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82515,7 +82515,7 @@
         <v>44788</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82588,7 +82588,7 @@
         <v>45791</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82661,7 +82661,7 @@
         <v>45790</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82734,7 +82734,7 @@
         <v>45650</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82807,7 +82807,7 @@
         <v>45238</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82885,7 +82885,7 @@
         <v>45238</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82963,7 +82963,7 @@
         <v>44538</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83041,7 +83041,7 @@
         <v>45238</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83119,7 +83119,7 @@
         <v>45670</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83197,7 +83197,7 @@
         <v>45238</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83275,7 +83275,7 @@
         <v>45670</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83353,7 +83353,7 @@
         <v>45238</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83431,7 +83431,7 @@
         <v>44929</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83509,7 +83509,7 @@
         <v>45238</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83587,7 +83587,7 @@
         <v>45386</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83660,7 +83660,7 @@
         <v>45238</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83738,7 +83738,7 @@
         <v>45238</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83816,7 +83816,7 @@
         <v>45670</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83894,7 +83894,7 @@
         <v>45238</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83972,7 +83972,7 @@
         <v>45238</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84050,7 +84050,7 @@
         <v>45238</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84128,7 +84128,7 @@
         <v>45670</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84206,7 +84206,7 @@
         <v>45238</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84284,7 +84284,7 @@
         <v>45670</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84362,7 +84362,7 @@
         <v>45670</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84460,7 +84460,7 @@
         <v>46083</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -601,7 +601,7 @@
         <v>45979</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45664</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44643</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45238</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45245</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45960</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46019</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>44771</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45502</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>44840</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>46073</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45950</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>45981</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>46057</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>45595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45734</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>46210</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45091</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45219</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45544</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44972</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45323</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45670</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>46034</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>45295</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46043</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>46070</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>44884</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>46114</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>45994</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45502</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>45297</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45502</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>45686</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>46244</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45106</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45670</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45728</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44594</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44685</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45478</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45799</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>45029</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>44951</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44673</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>45931</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44711</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45971</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>45979</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>45995</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>45056</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45775</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45734</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>45834</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>46085</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>44964</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>46177</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>46182</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45631</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44586</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45673</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45320</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>46038</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>45072</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>45741</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45296</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45763</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>45791</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44959</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>44825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44767</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>44711</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44774</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>44876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>44547</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44686</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44781</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44765</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44605</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44713</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>44475</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44823</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44879</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44722</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44831</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44816</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44812</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44741</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44546</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44473</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44502</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44651</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44509</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44739</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>44692</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>44691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>44797</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44544</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>44853</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44634</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44545</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>44732</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44490</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44525</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44830</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44620</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44692</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44743</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>44840</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44764</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44711</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44467</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44552</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44728</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44831</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44728</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44502</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44571</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44820</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44586</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44728</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44785</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44530</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>44503</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44711</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44566</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44704</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44684</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>44692</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44734</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>44728</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45712</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>44790</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>44789</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>44765</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45043</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45324</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>45364</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>45183</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45541</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45741</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45419</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>44886</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45426</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44844</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45562</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45566</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45763</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>44945</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44832</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44833</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>44812</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>44552</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45463</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45796</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>45489</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16566,7 +16566,7 @@
         <v>45139</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>45793</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>45950</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>45880</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>46021</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>44862</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>46024</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>45140</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>46026</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>45537</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45569</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>46030</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45191</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>45884</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>46030</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45793</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45796</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45513</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45504</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45463</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45883</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45532</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45540</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45603</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45603</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>46030</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44945</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45586</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45499</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45888</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45176</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>46034</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>46031</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>46035</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>45888</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44939</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>46035</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>45890</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>44930</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>46038</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>46037</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>46037</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>46037</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45622</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>45799</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44994</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45618</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>45855</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>45729</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>46038</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44560</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>46042</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>46042</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45896</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>46039</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>46042</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45861</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45896</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45896</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45896</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>46041</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45897</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45545</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>46043</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45897</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>46043</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45352</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>46043</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>46044</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>46043</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>46044</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>46043</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>46043</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45042</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>46043</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45897</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45898</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>46044</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>46044</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>46043</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>46043</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>46044</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>46048</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>46048</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>46048</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>46045</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45537</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>46045</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45799</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>46048</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>46069</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>46045</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45622</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>46050</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45904</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45566</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44599</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>46050</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>46050</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45903</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>46050</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45904</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45908</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>46052</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>46051</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>46051</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>46051</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>46051</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45908</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45358</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>45799</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>44900</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44900</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>45909</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>46056</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>46053</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>46053</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>46056</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>46055</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>46055</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>46055</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45301</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45802</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>46057</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>46057</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45184</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45911</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>46057</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>46062</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>45915</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>44664</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>46062</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45915</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45297</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>46079</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>46062</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>46062</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>46062</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>46062</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>45917</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>46062</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>46064</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45917</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45917</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>46063</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>46064</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>46064</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45918</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45260</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>46064</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>46064</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45918</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>45918</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>46063</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45802</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>46066</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>46066</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>46065</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45919</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45462</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>46065</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>46069</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45748</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>46069</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>46070</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45579</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>45802</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>45924</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>46070</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>45923</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>46070</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>45671</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44953</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45924</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>46069</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>46071</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>46071</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45687</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>46071</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>46071</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45925</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>46071</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30097,7 +30097,7 @@
         <v>46072</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>46030</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>46071</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>46072</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>46072</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>46076</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>46073</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44659</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>46076</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>45506</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>46073</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>45637</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44692</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>46078</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>46079</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>46079</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>46073</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>46079</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45912</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>46080</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>46084</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45306</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>44873</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>46084</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45931</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>46084</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44960</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>46084</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>44967</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44967</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45931</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>46084</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>46084</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>46087</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45936</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>46087</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>46043</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>44943</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45936</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>45936</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>46086</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45259</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>45309</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>44915</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>45936</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>46031</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>46090</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>45372</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>45545</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33724,7 +33724,7 @@
         <v>45937</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>45253</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>46090</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45937</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>44589</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45938</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>45938</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>45938</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45938</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>45938</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34454,7 +34454,7 @@
         <v>45938</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>46092</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>44907</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34683,7 +34683,7 @@
         <v>45938</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34756,7 +34756,7 @@
         <v>45938</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45938</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>45938</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45938</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>45939</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>45757</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>46093</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>46097</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45939</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45939</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>45939</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45176</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>46099</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>46098</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>46098</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>46099</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>46098</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>46098</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>45946</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>45223</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45946</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45946</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>45607</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45607</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>45590</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36621,7 +36621,7 @@
         <v>46125</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>45947</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36772,7 +36772,7 @@
         <v>46104</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>46104</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36918,7 +36918,7 @@
         <v>45070</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44894</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45950</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>45947</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>45947</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>45950</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>45950</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37439,7 +37439,7 @@
         <v>45951</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>46107</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>45622</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37663,7 +37663,7 @@
         <v>45812</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45938</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45624</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>46111</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>46111</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>46111</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>45958</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>46111</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>46111</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45223</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>46111</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>46112</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>46112</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>46113</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>46113</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45121</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45946</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>46112</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45271</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>45960</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>46119</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39251,7 +39251,7 @@
         <v>45582</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45579</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>46118</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>46119</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>46119</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>46120</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>46120</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45959</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>46120</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>46120</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>46120</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>46120</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>46120</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45763</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>46122</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45965</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>44960</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>45637</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>46125</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
         <v>45020</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>45020</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45567</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>44952</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>44952</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>45812</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>45090</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>46062</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>46126</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>46126</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45208</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45968</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>44704</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41642,7 +41642,7 @@
         <v>45646</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44540</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45140</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>45971</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45971</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45971</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45813</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45971</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>44704</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>45973</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45973</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>45973</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>45020</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45974</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>45973</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42772,7 +42772,7 @@
         <v>45973</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>46126</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>46100</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45642</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>45632</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>45974</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45062</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45663</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>44964</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45439</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45166</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45610</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>44729</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45429</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>45980</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45980</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>45979</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>46127</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>46134</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45646</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>46134</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45981</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>46133</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>45142</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45142</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>45616</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>45985</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>45985</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45617</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>45985</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45986</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45100,7 +45100,7 @@
         <v>44999</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45173,7 +45173,7 @@
         <v>45985</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>45985</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45771</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45397,7 +45397,7 @@
         <v>44739</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45987</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>45636</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>46136</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>46135</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>44795</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         <v>46136</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45034</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>46112</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45817</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45993</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46215,7 +46215,7 @@
         <v>45994</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>46140</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>45995</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>46038</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>46048</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>45999</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45544</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45041</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45817</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46892,7 +46892,7 @@
         <v>46000</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>46000</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45636</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>46140</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45817</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>44987</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45250</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47418,7 +47418,7 @@
         <v>44797</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47496,7 +47496,7 @@
         <v>45625</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47569,7 +47569,7 @@
         <v>46006</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>46003</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>46139</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         <v>46006</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45610</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47939,7 +47939,7 @@
         <v>46008</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>46019</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>44985</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48168,7 +48168,7 @@
         <v>45509</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>46030</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>44895</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48392,7 +48392,7 @@
         <v>44830</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>46021</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48538,7 +48538,7 @@
         <v>46048</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48611,7 +48611,7 @@
         <v>45489</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>46054</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>46033</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>44789</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45824</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>46136</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>46026</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>45617</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>45273</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>45170</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45758</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45915</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45826</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>46043</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45826</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49746,7 +49746,7 @@
         <v>46043</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49819,7 +49819,7 @@
         <v>45525</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49897,7 +49897,7 @@
         <v>45824</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49975,7 +49975,7 @@
         <v>46021</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>46073</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50121,7 +50121,7 @@
         <v>46048</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45177</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>45624</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50350,7 +50350,7 @@
         <v>46098</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50423,7 +50423,7 @@
         <v>46070</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45825</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>44788</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>46055</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>45072</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50788,7 +50788,7 @@
         <v>45068</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50861,7 +50861,7 @@
         <v>46069</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45789</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>46031</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51090,7 +51090,7 @@
         <v>45951</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51163,7 +51163,7 @@
         <v>45827</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51241,7 +51241,7 @@
         <v>45880</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51319,7 +51319,7 @@
         <v>46084</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45231</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45884</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>46146</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51616,7 +51616,7 @@
         <v>44960</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51694,7 +51694,7 @@
         <v>46055</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>46119</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51840,7 +51840,7 @@
         <v>46030</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>46038</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51986,7 +51986,7 @@
         <v>46146</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>46035</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>46146</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52205,7 +52205,7 @@
         <v>46146</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52278,7 +52278,7 @@
         <v>44573</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>45044</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         <v>45832</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52497,7 +52497,7 @@
         <v>46078</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52570,7 +52570,7 @@
         <v>46149</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52643,7 +52643,7 @@
         <v>45832</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45148</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45832</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52872,7 +52872,7 @@
         <v>46149</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>46035</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>46128</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>46052</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>46026</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45037</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>45541</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>45646</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>46042</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>46119</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53607,7 +53607,7 @@
         <v>45222</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>46155</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53758,7 +53758,7 @@
         <v>44900</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53836,7 +53836,7 @@
         <v>46100</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53909,7 +53909,7 @@
         <v>44869</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53982,7 +53982,7 @@
         <v>46155</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45297</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>46155</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54206,7 +54206,7 @@
         <v>46157</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54284,7 +54284,7 @@
         <v>45555</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54357,7 +54357,7 @@
         <v>45573</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54430,7 +54430,7 @@
         <v>46160</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54503,7 +54503,7 @@
         <v>45835</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54581,7 +54581,7 @@
         <v>44964</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45835</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54732,7 +54732,7 @@
         <v>45835</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>44783</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45103</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54956,7 +54956,7 @@
         <v>46136</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55029,7 +55029,7 @@
         <v>45840</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45554</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55180,7 +55180,7 @@
         <v>45839</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55258,7 +55258,7 @@
         <v>46111</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>45841</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55409,7 +55409,7 @@
         <v>46051</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55482,7 +55482,7 @@
         <v>45841</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55560,7 +55560,7 @@
         <v>46043</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55633,7 +55633,7 @@
         <v>46161</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55706,7 +55706,7 @@
         <v>45841</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55784,7 +55784,7 @@
         <v>45644</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45846</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55940,7 +55940,7 @@
         <v>45846</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56018,7 +56018,7 @@
         <v>44512</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56096,7 +56096,7 @@
         <v>46164</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>46163</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>46164</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56325,7 +56325,7 @@
         <v>45848</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56403,7 +56403,7 @@
         <v>45397</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45848</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56549,7 +56549,7 @@
         <v>46168</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>46167</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56695,7 +56695,7 @@
         <v>45287</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56768,7 +56768,7 @@
         <v>45848</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>44952</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45622</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>46167</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57080,7 +57080,7 @@
         <v>46167</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57153,7 +57153,7 @@
         <v>45455</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57231,7 +57231,7 @@
         <v>46169</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>45695</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57377,7 +57377,7 @@
         <v>45079</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57455,7 +57455,7 @@
         <v>46030</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57528,7 +57528,7 @@
         <v>45860</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57606,7 +57606,7 @@
         <v>45859</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57679,7 +57679,7 @@
         <v>46171</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45271</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>46171</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>45860</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57976,7 +57976,7 @@
         <v>44938</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58049,7 +58049,7 @@
         <v>46043</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>46029</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58195,7 +58195,7 @@
         <v>46170</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>44998</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58346,7 +58346,7 @@
         <v>46171</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58419,7 +58419,7 @@
         <v>45289</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58492,7 +58492,7 @@
         <v>46170</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58565,7 +58565,7 @@
         <v>46175</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58638,7 +58638,7 @@
         <v>45604</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58716,7 +58716,7 @@
         <v>46035</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58789,7 +58789,7 @@
         <v>46175</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58867,7 +58867,7 @@
         <v>44502</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45058</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59013,7 +59013,7 @@
         <v>45041</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59091,7 +59091,7 @@
         <v>44628</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>45601</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59237,7 +59237,7 @@
         <v>46176</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59315,7 +59315,7 @@
         <v>45306</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>45141</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59461,7 +59461,7 @@
         <v>45343</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         <v>44601</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59612,7 +59612,7 @@
         <v>46177</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59690,7 +59690,7 @@
         <v>46042</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59763,7 +59763,7 @@
         <v>46136</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59836,7 +59836,7 @@
         <v>46079</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59909,7 +59909,7 @@
         <v>46177</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59982,7 +59982,7 @@
         <v>45754</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60060,7 +60060,7 @@
         <v>46084</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60133,7 +60133,7 @@
         <v>45120</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60206,7 +60206,7 @@
         <v>45463</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>45525</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>46181</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>46181</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60518,7 +60518,7 @@
         <v>46051</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>46043</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60664,7 +60664,7 @@
         <v>45566</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60737,7 +60737,7 @@
         <v>46179</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60810,7 +60810,7 @@
         <v>45596</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60883,7 +60883,7 @@
         <v>46178</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>44601</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61034,7 +61034,7 @@
         <v>45618</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>45271</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>45642</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61258,7 +61258,7 @@
         <v>45076</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>44603</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61404,7 +61404,7 @@
         <v>46183</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61477,7 +61477,7 @@
         <v>46182</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>44616</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61628,7 +61628,7 @@
         <v>46185</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61706,7 +61706,7 @@
         <v>46184</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>45149</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>46185</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45170</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>44503</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>45063</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62159,7 +62159,7 @@
         <v>46188</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45618</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>46188</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62388,7 +62388,7 @@
         <v>45902</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62461,7 +62461,7 @@
         <v>46188</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62534,7 +62534,7 @@
         <v>45533</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62612,7 +62612,7 @@
         <v>45545</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62685,7 +62685,7 @@
         <v>45545</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62763,7 +62763,7 @@
         <v>46188</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62836,7 +62836,7 @@
         <v>45422</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62914,7 +62914,7 @@
         <v>45593</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>46188</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63060,7 +63060,7 @@
         <v>46188</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63133,7 +63133,7 @@
         <v>45539</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63206,7 +63206,7 @@
         <v>45574</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63279,7 +63279,7 @@
         <v>45618</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63357,7 +63357,7 @@
         <v>46195</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63430,7 +63430,7 @@
         <v>46195</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63503,7 +63503,7 @@
         <v>46195</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63576,7 +63576,7 @@
         <v>45188</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>44551</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63727,7 +63727,7 @@
         <v>45733</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63805,7 +63805,7 @@
         <v>46197</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63878,7 +63878,7 @@
         <v>44596</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63951,7 +63951,7 @@
         <v>46196</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64029,7 +64029,7 @@
         <v>45719</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64107,7 +64107,7 @@
         <v>45631</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64180,7 +64180,7 @@
         <v>45631</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64253,7 +64253,7 @@
         <v>45175</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64326,7 +64326,7 @@
         <v>46196</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64399,7 +64399,7 @@
         <v>46196</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>45173</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64550,7 +64550,7 @@
         <v>46198</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64628,7 +64628,7 @@
         <v>45170</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64706,7 +64706,7 @@
         <v>46178</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
         <v>45880</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64857,7 +64857,7 @@
         <v>45628</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64935,7 +64935,7 @@
         <v>44644</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65008,7 +65008,7 @@
         <v>45631</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65086,7 +65086,7 @@
         <v>46198</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>46198</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>45309</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65310,7 +65310,7 @@
         <v>45642</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65383,7 +65383,7 @@
         <v>46198</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65456,7 +65456,7 @@
         <v>45701</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65534,7 +65534,7 @@
         <v>45622</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65612,7 +65612,7 @@
         <v>45686</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65690,7 +65690,7 @@
         <v>45499</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65763,7 +65763,7 @@
         <v>45644</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65841,7 +65841,7 @@
         <v>45881</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65914,7 +65914,7 @@
         <v>45622</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65992,7 +65992,7 @@
         <v>44607</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66065,7 +66065,7 @@
         <v>46202</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66138,7 +66138,7 @@
         <v>45882</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66216,7 +66216,7 @@
         <v>45204</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66289,7 +66289,7 @@
         <v>45545</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66362,7 +66362,7 @@
         <v>45603</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66440,7 +66440,7 @@
         <v>45131</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66513,7 +66513,7 @@
         <v>45884</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45615</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66659,7 +66659,7 @@
         <v>44859</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66732,7 +66732,7 @@
         <v>46204</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66810,7 +66810,7 @@
         <v>45883</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66883,7 +66883,7 @@
         <v>45671</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66961,7 +66961,7 @@
         <v>45695</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67034,7 +67034,7 @@
         <v>46251</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67112,7 +67112,7 @@
         <v>46209</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67185,7 +67185,7 @@
         <v>46206</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67258,7 +67258,7 @@
         <v>46206</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67331,7 +67331,7 @@
         <v>45636</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67409,7 +67409,7 @@
         <v>45197</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67487,7 +67487,7 @@
         <v>44547</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67560,7 +67560,7 @@
         <v>46206</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67633,7 +67633,7 @@
         <v>45639</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67706,7 +67706,7 @@
         <v>46209</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67779,7 +67779,7 @@
         <v>46209</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67852,7 +67852,7 @@
         <v>45691</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67925,7 +67925,7 @@
         <v>46209</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67998,7 +67998,7 @@
         <v>45687</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68071,7 +68071,7 @@
         <v>46253</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68149,7 +68149,7 @@
         <v>45222</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68222,7 +68222,7 @@
         <v>45219</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68300,7 +68300,7 @@
         <v>46253</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68378,7 +68378,7 @@
         <v>46253</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68456,7 +68456,7 @@
         <v>45622</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68534,7 +68534,7 @@
         <v>45622</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68607,7 +68607,7 @@
         <v>46066</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68680,7 +68680,7 @@
         <v>46253</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68753,7 +68753,7 @@
         <v>44699</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68826,7 +68826,7 @@
         <v>44679</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68904,7 +68904,7 @@
         <v>44678</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68982,7 +68982,7 @@
         <v>45149</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69055,7 +69055,7 @@
         <v>46255</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69128,7 +69128,7 @@
         <v>46213</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69201,7 +69201,7 @@
         <v>45216</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69274,7 +69274,7 @@
         <v>46213</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69347,7 +69347,7 @@
         <v>44686</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69425,7 +69425,7 @@
         <v>46254</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69503,7 +69503,7 @@
         <v>46043</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69576,7 +69576,7 @@
         <v>46213</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69649,7 +69649,7 @@
         <v>46258</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69722,7 +69722,7 @@
         <v>45642</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69795,7 +69795,7 @@
         <v>46184</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69868,7 +69868,7 @@
         <v>45511</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69941,7 +69941,7 @@
         <v>44763</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70019,7 +70019,7 @@
         <v>46259</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70092,7 +70092,7 @@
         <v>44748</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70165,7 +70165,7 @@
         <v>46259</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70243,7 +70243,7 @@
         <v>45741</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70316,7 +70316,7 @@
         <v>46262</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70389,7 +70389,7 @@
         <v>45154</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70462,7 +70462,7 @@
         <v>44768</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70540,7 +70540,7 @@
         <v>45236</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70618,7 +70618,7 @@
         <v>45259</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70691,7 +70691,7 @@
         <v>46184</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70764,7 +70764,7 @@
         <v>46261</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70837,7 +70837,7 @@
         <v>46184</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70910,7 +70910,7 @@
         <v>44608</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70983,7 +70983,7 @@
         <v>44720</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71056,7 +71056,7 @@
         <v>45169</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71129,7 +71129,7 @@
         <v>45729</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71202,7 +71202,7 @@
         <v>45175</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71275,7 +71275,7 @@
         <v>45775</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71353,7 +71353,7 @@
         <v>45762</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71431,7 +71431,7 @@
         <v>46220</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71509,7 +71509,7 @@
         <v>46223</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71587,7 +71587,7 @@
         <v>46220</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71660,7 +71660,7 @@
         <v>46223</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71733,7 +71733,7 @@
         <v>45189</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71811,7 +71811,7 @@
         <v>46265</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71889,7 +71889,7 @@
         <v>46220</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71967,7 +71967,7 @@
         <v>46220</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72040,7 +72040,7 @@
         <v>44777</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72118,7 +72118,7 @@
         <v>44808</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72191,7 +72191,7 @@
         <v>46007</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72264,7 +72264,7 @@
         <v>46007</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72337,7 +72337,7 @@
         <v>45313</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72410,7 +72410,7 @@
         <v>44595</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72483,7 +72483,7 @@
         <v>46226</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72556,7 +72556,7 @@
         <v>46269</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72629,7 +72629,7 @@
         <v>44811</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72702,7 +72702,7 @@
         <v>44811</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72775,7 +72775,7 @@
         <v>46227</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72848,7 +72848,7 @@
         <v>46272</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72921,7 +72921,7 @@
         <v>46272</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72994,7 +72994,7 @@
         <v>44797</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73072,7 +73072,7 @@
         <v>45196</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73145,7 +73145,7 @@
         <v>46226</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73218,7 +73218,7 @@
         <v>46274</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73291,7 +73291,7 @@
         <v>46273</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73364,7 +73364,7 @@
         <v>44886</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73442,7 +73442,7 @@
         <v>44886</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73520,7 +73520,7 @@
         <v>46273</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73598,7 +73598,7 @@
         <v>44967</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73676,7 +73676,7 @@
         <v>46231</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73749,7 +73749,7 @@
         <v>46273</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73822,7 +73822,7 @@
         <v>44783</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73895,7 +73895,7 @@
         <v>46275</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73968,7 +73968,7 @@
         <v>46274</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74041,7 +74041,7 @@
         <v>45019</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74114,7 +74114,7 @@
         <v>45345</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74192,7 +74192,7 @@
         <v>45345</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74265,7 +74265,7 @@
         <v>45243</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74338,7 +74338,7 @@
         <v>46280</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74411,7 +74411,7 @@
         <v>44868</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74489,7 +74489,7 @@
         <v>45399</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74562,7 +74562,7 @@
         <v>46280</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74635,7 +74635,7 @@
         <v>46234</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74713,7 +74713,7 @@
         <v>45429</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74786,7 +74786,7 @@
         <v>45532</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74859,7 +74859,7 @@
         <v>46282</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74932,7 +74932,7 @@
         <v>46238</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75005,7 +75005,7 @@
         <v>46184</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75078,7 +75078,7 @@
         <v>45425</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75151,7 +75151,7 @@
         <v>45641</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75224,7 +75224,7 @@
         <v>44965</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75297,7 +75297,7 @@
         <v>45743</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75375,7 +75375,7 @@
         <v>46185</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75453,7 +75453,7 @@
         <v>46283</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75526,7 +75526,7 @@
         <v>46241</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75599,7 +75599,7 @@
         <v>45489</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75677,7 +75677,7 @@
         <v>46288</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75755,7 +75755,7 @@
         <v>44824</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75828,7 +75828,7 @@
         <v>44806</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75901,7 +75901,7 @@
         <v>44652</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75974,7 +75974,7 @@
         <v>46288</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76052,7 +76052,7 @@
         <v>45187</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76125,7 +76125,7 @@
         <v>45336</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76198,7 +76198,7 @@
         <v>46244</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76271,7 +76271,7 @@
         <v>45568</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76344,7 +76344,7 @@
         <v>46244</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76417,7 +76417,7 @@
         <v>45246</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76490,7 +76490,7 @@
         <v>45539</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76563,7 +76563,7 @@
         <v>45607</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76636,7 +76636,7 @@
         <v>46289</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76709,7 +76709,7 @@
         <v>45089</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76782,7 +76782,7 @@
         <v>45733</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76860,7 +76860,7 @@
         <v>46289</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76938,7 +76938,7 @@
         <v>45544</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77011,7 +77011,7 @@
         <v>45607</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77084,7 +77084,7 @@
         <v>44690</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77157,7 +77157,7 @@
         <v>45382</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77230,7 +77230,7 @@
         <v>45422</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77308,7 +77308,7 @@
         <v>45604</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77386,7 +77386,7 @@
         <v>45546</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77459,7 +77459,7 @@
         <v>45546</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77532,7 +77532,7 @@
         <v>45554</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77605,7 +77605,7 @@
         <v>45622</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77683,7 +77683,7 @@
         <v>45770</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77756,7 +77756,7 @@
         <v>45770</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77829,7 +77829,7 @@
         <v>45252</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77902,7 +77902,7 @@
         <v>45680</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77975,7 +77975,7 @@
         <v>45037</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78048,7 +78048,7 @@
         <v>45001</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78121,7 +78121,7 @@
         <v>45434</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78199,7 +78199,7 @@
         <v>45373</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78277,7 +78277,7 @@
         <v>45497</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78355,7 +78355,7 @@
         <v>45163</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78433,7 +78433,7 @@
         <v>45428</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78511,7 +78511,7 @@
         <v>44874</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78589,7 +78589,7 @@
         <v>45617</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78667,7 +78667,7 @@
         <v>45357</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78740,7 +78740,7 @@
         <v>45559</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78818,7 +78818,7 @@
         <v>45019</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78891,7 +78891,7 @@
         <v>45303</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78964,7 +78964,7 @@
         <v>45667</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79037,7 +79037,7 @@
         <v>45670</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79115,7 +79115,7 @@
         <v>45670</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79193,7 +79193,7 @@
         <v>45677</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79271,7 +79271,7 @@
         <v>45621</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79349,7 +79349,7 @@
         <v>45635</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79427,7 +79427,7 @@
         <v>45089</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79500,7 +79500,7 @@
         <v>45607</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79573,7 +79573,7 @@
         <v>45617</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79651,7 +79651,7 @@
         <v>45758</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79724,7 +79724,7 @@
         <v>45232</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79797,7 +79797,7 @@
         <v>45636</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79870,7 +79870,7 @@
         <v>45719</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79948,7 +79948,7 @@
         <v>45169</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80026,7 +80026,7 @@
         <v>45726</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80099,7 +80099,7 @@
         <v>45622</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80172,7 +80172,7 @@
         <v>44781</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80245,7 +80245,7 @@
         <v>45623</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80318,7 +80318,7 @@
         <v>45124</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80391,7 +80391,7 @@
         <v>45103</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80469,7 +80469,7 @@
         <v>44938</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80547,7 +80547,7 @@
         <v>44908</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80625,7 +80625,7 @@
         <v>45537</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80703,7 +80703,7 @@
         <v>44907</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80781,7 +80781,7 @@
         <v>44713</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80854,7 +80854,7 @@
         <v>45546</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80927,7 +80927,7 @@
         <v>45579</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81000,7 +81000,7 @@
         <v>45632</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81078,7 +81078,7 @@
         <v>45636</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81151,7 +81151,7 @@
         <v>45777</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81229,7 +81229,7 @@
         <v>45783</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81302,7 +81302,7 @@
         <v>45763</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81380,7 +81380,7 @@
         <v>45763</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81458,7 +81458,7 @@
         <v>44999</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81531,7 +81531,7 @@
         <v>45784</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81604,7 +81604,7 @@
         <v>45498</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81682,7 +81682,7 @@
         <v>45120</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81755,7 +81755,7 @@
         <v>45786</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81833,7 +81833,7 @@
         <v>44525</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81911,7 +81911,7 @@
         <v>45754</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81989,7 +81989,7 @@
         <v>45786</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82067,7 +82067,7 @@
         <v>45791</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82140,7 +82140,7 @@
         <v>45758</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82218,7 +82218,7 @@
         <v>45792</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82291,7 +82291,7 @@
         <v>45791</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82364,7 +82364,7 @@
         <v>45055</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82437,7 +82437,7 @@
         <v>45236</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82515,7 +82515,7 @@
         <v>44788</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82588,7 +82588,7 @@
         <v>45791</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82661,7 +82661,7 @@
         <v>45790</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82734,7 +82734,7 @@
         <v>45650</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82807,7 +82807,7 @@
         <v>45238</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82885,7 +82885,7 @@
         <v>45238</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82963,7 +82963,7 @@
         <v>44538</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83041,7 +83041,7 @@
         <v>45238</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83119,7 +83119,7 @@
         <v>45670</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83197,7 +83197,7 @@
         <v>45238</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83275,7 +83275,7 @@
         <v>45670</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83353,7 +83353,7 @@
         <v>45238</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83431,7 +83431,7 @@
         <v>44929</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83509,7 +83509,7 @@
         <v>45238</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83587,7 +83587,7 @@
         <v>45386</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83660,7 +83660,7 @@
         <v>45238</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83738,7 +83738,7 @@
         <v>45238</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83816,7 +83816,7 @@
         <v>45670</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83894,7 +83894,7 @@
         <v>45238</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83972,7 +83972,7 @@
         <v>45238</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84050,7 +84050,7 @@
         <v>45238</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84128,7 +84128,7 @@
         <v>45670</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84206,7 +84206,7 @@
         <v>45238</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84284,7 +84284,7 @@
         <v>45670</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84362,7 +84362,7 @@
         <v>45670</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84460,7 +84460,7 @@
         <v>46083</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -601,7 +601,7 @@
         <v>45979</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45664</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44643</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45238</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45245</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45960</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>44771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>46019</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45502</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>44840</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>46073</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45950</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>45734</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>45091</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>46057</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45595</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45219</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44545</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>45544</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45323</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45670</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>46034</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46043</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>46070</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45686</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>46114</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>45994</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>45502</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45297</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>44690</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>46244</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45295</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>44884</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45106</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45670</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45728</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44594</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44685</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45478</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45631</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>45791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>44951</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>45799</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45029</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>45931</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>45056</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>45971</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45979</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45995</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44673</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45834</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>44586</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45296</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>46085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>46177</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>46182</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45741</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>45072</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>45673</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44711</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>46038</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45320</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>45734</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>45775</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>45763</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44959</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>44825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44767</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>44711</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44774</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>44876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>44547</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44686</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44781</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44765</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44605</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44713</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>44475</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44823</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44879</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44831</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44816</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44722</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44741</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44812</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44546</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44502</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44473</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44651</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44509</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44739</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>44692</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>44691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>44797</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44544</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>44853</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44545</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44634</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>44732</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44490</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44525</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44830</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44620</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44692</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44743</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>44840</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44711</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44764</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44552</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44728</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44831</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>44728</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44502</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44571</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44820</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44586</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44530</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44503</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44728</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44785</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>44566</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44711</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44704</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44684</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>44734</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>44728</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44659</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>44692</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45726</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45163</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45775</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45041</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45188</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>44692</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>45644</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45041</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44862</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45289</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45103</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>44886</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>45631</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>45139</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44503</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>45625</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>45068</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>44599</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>45352</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>45573</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>44894</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45170</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>44994</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45642</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>45070</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44900</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45786</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45169</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45786</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44601</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>44525</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45621</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>46003</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>45001</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>44795</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45622</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44830</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45345</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45345</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>44895</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>44788</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45758</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>46006</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45790</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45791</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>46006</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45762</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44783</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45884</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>46008</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45533</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45610</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45791</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45691</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>45791</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45754</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45950</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45253</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>45888</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45309</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45149</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45888</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>46021</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45343</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45890</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>44886</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>46024</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>45336</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>46026</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>45055</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>45855</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45897</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>45897</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45896</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>46030</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45861</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45896</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45896</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45896</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>46031</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45897</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45898</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>46030</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>45397</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>46030</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>46034</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45903</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>46035</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>46035</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>45566</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>44806</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>46037</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>45559</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45622</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>46037</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>46037</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45793</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>46041</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>45904</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>45236</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45904</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>46038</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45908</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>45792</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>46038</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>45909</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>46039</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>46043</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>45306</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>46043</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>45908</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>46043</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>46043</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>46043</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>46043</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>46043</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>45793</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>46042</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>46042</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>46042</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>46043</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>46043</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45796</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45911</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>46044</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>45191</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46044</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>46044</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>46045</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>46045</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45796</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45680</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45915</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>46045</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>46044</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>46044</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44945</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>45915</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>46069</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>46048</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>46048</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45555</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45569</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45917</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>46048</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45799</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>46048</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45463</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45540</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45586</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>45532</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45917</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>45917</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45799</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>46051</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>46051</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45919</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>46050</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45802</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45802</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>46050</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>46050</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>45799</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45802</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46050</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>46051</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>46051</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>45511</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>44953</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45918</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45918</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45918</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>46053</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>46055</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>45923</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45646</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>46055</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>46055</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>46052</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>46053</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>45924</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>46056</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45924</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>45925</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>46057</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>46057</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>46057</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>46056</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>45297</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>46079</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45912</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>45426</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45176</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>46062</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>46062</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>46062</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45931</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>46062</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>46062</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45425</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>46062</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>46063</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45499</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>46062</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>46063</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>44873</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>46064</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>46064</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>46065</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45931</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>46064</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>46064</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>46065</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>46064</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>46069</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>45936</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>46066</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45554</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>46069</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45936</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45936</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45936</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>45306</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45037</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>46066</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45937</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>46069</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45938</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45938</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>45938</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45938</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>46030</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44678</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>45562</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>46071</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>46071</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>45939</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>46071</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>45938</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>45938</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>46070</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45938</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45938</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45938</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>46070</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>45637</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>45939</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>46071</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>46071</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>45670</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33296,7 +33296,7 @@
         <v>45622</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>45622</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45938</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>46070</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>45937</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>45939</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>45939</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>46073</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45938</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>46072</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>46072</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>46073</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>46072</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>46076</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>45946</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>45947</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46073</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>46076</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>45946</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>44960</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>45946</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45947</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>46078</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45947</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>46079</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>45259</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45309</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45938</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45950</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>44560</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35521,7 +35521,7 @@
         <v>46079</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>46079</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>45243</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>45950</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>46080</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>45950</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>45951</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>45623</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>46084</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>45196</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36256,7 +36256,7 @@
         <v>45419</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45183</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45812</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>46084</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>46084</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>46084</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>46084</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36772,7 +36772,7 @@
         <v>46084</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>45642</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36918,7 +36918,7 @@
         <v>45946</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44781</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>45646</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>45813</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>46086</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>45812</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45236</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37439,7 +37439,7 @@
         <v>45189</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44907</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44998</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>46043</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>46087</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>45958</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>46087</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>46090</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>46090</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>45959</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45148</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45960</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>45758</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>46092</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>46031</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44608</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>45965</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45545</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>45120</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         <v>45663</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>45817</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>45817</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>44811</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>46093</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45541</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>45131</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>45817</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>45971</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45971</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45271</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>46098</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>46098</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>46098</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39923,7 +39923,7 @@
         <v>45971</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>46097</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45968</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>46098</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>45971</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>46099</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>45973</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45216</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>45973</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>44768</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>45973</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>45973</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>45973</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45089</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45974</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>46104</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>46104</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>46125</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>45974</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>44540</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45463</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45979</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45671</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
         <v>45677</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>45981</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>45980</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45980</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>46107</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45646</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>46111</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>45985</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>46111</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>46111</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>46112</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>46112</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>46112</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>46111</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>46111</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42787,7 +42787,7 @@
         <v>46111</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>45184</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42938,7 +42938,7 @@
         <v>45985</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43011,7 +43011,7 @@
         <v>45985</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
         <v>44664</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43162,7 +43162,7 @@
         <v>45985</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43235,7 +43235,7 @@
         <v>45986</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>45176</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43386,7 +43386,7 @@
         <v>45985</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43459,7 +43459,7 @@
         <v>45987</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43532,7 +43532,7 @@
         <v>46113</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43610,7 +43610,7 @@
         <v>46113</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>45824</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45596</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>46118</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>46120</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>46119</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>46119</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>46120</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>46119</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>45103</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>46120</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>46120</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>46120</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>46120</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>45825</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>46120</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>45993</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>45166</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>44573</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         <v>44945</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>46122</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45168,7 +45168,7 @@
         <v>45497</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>46126</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45324,7 +45324,7 @@
         <v>45223</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45397,7 +45397,7 @@
         <v>46126</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>45995</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>46062</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45621,7 +45621,7 @@
         <v>45826</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>46125</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45772,7 +45772,7 @@
         <v>46126</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>44729</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>46100</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>45994</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>45827</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>45999</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>45525</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>45434</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45826</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>44748</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46527,7 +46527,7 @@
         <v>45044</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46600,7 +46600,7 @@
         <v>46000</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>45701</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>46133</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46824,7 +46824,7 @@
         <v>46000</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>46127</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46970,7 +46970,7 @@
         <v>45832</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47043,7 +47043,7 @@
         <v>46112</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>45832</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45832</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45771</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>46134</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>45835</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>46134</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45835</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>45835</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>45636</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47803,7 +47803,7 @@
         <v>45232</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47876,7 +47876,7 @@
         <v>46136</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47949,7 +47949,7 @@
         <v>45839</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45554</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
         <v>46030</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48173,7 +48173,7 @@
         <v>46073</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>46021</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>45169</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48392,7 +48392,7 @@
         <v>45840</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
         <v>44886</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45546</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45546</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>45841</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48772,7 +48772,7 @@
         <v>45841</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48850,7 +48850,7 @@
         <v>45915</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45841</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49001,7 +49001,7 @@
         <v>46043</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>46019</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45259</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>46033</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45824</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45846</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>45610</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45846</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45848</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>44874</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>45848</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>44833</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49912,7 +49912,7 @@
         <v>45848</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49985,7 +49985,7 @@
         <v>45170</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50063,7 +50063,7 @@
         <v>44607</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50136,7 +50136,7 @@
         <v>44824</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50209,7 +50209,7 @@
         <v>44644</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50282,7 +50282,7 @@
         <v>45324</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>46139</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>46048</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>45566</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>46136</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50652,7 +50652,7 @@
         <v>45489</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50725,7 +50725,7 @@
         <v>46043</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50798,7 +50798,7 @@
         <v>46136</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50871,7 +50871,7 @@
         <v>45695</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>46135</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>45544</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51095,7 +51095,7 @@
         <v>45509</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51168,7 +51168,7 @@
         <v>45860</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>45860</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51319,7 +51319,7 @@
         <v>45859</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45641</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45642</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>46048</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>46026</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51684,7 +51684,7 @@
         <v>45951</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51757,7 +51757,7 @@
         <v>45884</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>46055</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51908,7 +51908,7 @@
         <v>44964</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51986,7 +51986,7 @@
         <v>45579</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>46021</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>46140</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>45429</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45429</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52356,7 +52356,7 @@
         <v>46031</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>44788</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52507,7 +52507,7 @@
         <v>46084</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52580,7 +52580,7 @@
         <v>44915</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52653,7 +52653,7 @@
         <v>45042</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>46054</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         <v>45537</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>46070</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>46048</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53028,7 +53028,7 @@
         <v>45880</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53106,7 +53106,7 @@
         <v>45618</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53179,7 +53179,7 @@
         <v>46140</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>46098</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53325,7 +53325,7 @@
         <v>46038</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53398,7 +53398,7 @@
         <v>45789</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53476,7 +53476,7 @@
         <v>45313</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53549,7 +53549,7 @@
         <v>45712</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53627,7 +53627,7 @@
         <v>45089</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45079</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53778,7 +53778,7 @@
         <v>45250</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53851,7 +53851,7 @@
         <v>45208</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53924,7 +53924,7 @@
         <v>45043</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53997,7 +53997,7 @@
         <v>46146</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54070,7 +54070,7 @@
         <v>44832</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>46119</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54216,7 +54216,7 @@
         <v>46146</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         <v>46035</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
         <v>45222</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54435,7 +54435,7 @@
         <v>44686</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54513,7 +54513,7 @@
         <v>44601</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54586,7 +54586,7 @@
         <v>45741</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>46146</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54732,7 +54732,7 @@
         <v>46146</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>46038</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>44704</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54956,7 +54956,7 @@
         <v>46055</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55029,7 +55029,7 @@
         <v>45636</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55102,7 +55102,7 @@
         <v>46030</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55175,7 +55175,7 @@
         <v>45141</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55248,7 +55248,7 @@
         <v>46149</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>46149</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55394,7 +55394,7 @@
         <v>44652</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>46078</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45297</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55618,7 +55618,7 @@
         <v>45624</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>46128</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>45729</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55837,7 +55837,7 @@
         <v>45743</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55915,7 +55915,7 @@
         <v>45222</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55988,7 +55988,7 @@
         <v>46155</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56061,7 +56061,7 @@
         <v>46119</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45303</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56207,7 +56207,7 @@
         <v>44783</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>46042</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56353,7 +56353,7 @@
         <v>46155</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>46026</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>46155</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>46035</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56650,7 +56650,7 @@
         <v>45568</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56723,7 +56723,7 @@
         <v>46052</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         <v>45545</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56869,7 +56869,7 @@
         <v>45537</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>45273</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57025,7 +57025,7 @@
         <v>46157</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45748</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57181,7 +57181,7 @@
         <v>46161</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>44616</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57327,7 +57327,7 @@
         <v>46160</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45020</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45020</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45197</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57634,7 +57634,7 @@
         <v>44987</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57707,7 +57707,7 @@
         <v>46043</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57780,7 +57780,7 @@
         <v>45428</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57858,7 +57858,7 @@
         <v>46163</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45607</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58004,7 +58004,7 @@
         <v>46051</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58077,7 +58077,7 @@
         <v>46136</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58150,7 +58150,7 @@
         <v>46111</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58223,7 +58223,7 @@
         <v>45631</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45618</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58374,7 +58374,7 @@
         <v>45546</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58447,7 +58447,7 @@
         <v>46164</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58525,7 +58525,7 @@
         <v>46167</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>44512</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58676,7 +58676,7 @@
         <v>46164</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         <v>45246</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58827,7 +58827,7 @@
         <v>46167</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58900,7 +58900,7 @@
         <v>45628</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58978,7 +58978,7 @@
         <v>44811</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59051,7 +59051,7 @@
         <v>45603</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59124,7 +59124,7 @@
         <v>45603</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>46169</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>44790</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>45579</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59416,7 +59416,7 @@
         <v>45881</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59489,7 +59489,7 @@
         <v>46168</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>45399</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59635,7 +59635,7 @@
         <v>45635</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59713,7 +59713,7 @@
         <v>45525</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59791,7 +59791,7 @@
         <v>46170</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>45880</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59947,7 +59947,7 @@
         <v>45537</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60025,7 +60025,7 @@
         <v>46170</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60098,7 +60098,7 @@
         <v>46035</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60171,7 +60171,7 @@
         <v>45883</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45880</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>46029</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60390,7 +60390,7 @@
         <v>46030</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60463,7 +60463,7 @@
         <v>45882</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60541,7 +60541,7 @@
         <v>46171</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60614,7 +60614,7 @@
         <v>45622</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60687,7 +60687,7 @@
         <v>45622</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         <v>45667</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60833,7 +60833,7 @@
         <v>45670</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>46171</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>46171</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61062,7 +61062,7 @@
         <v>45287</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61135,7 +61135,7 @@
         <v>45455</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61213,7 +61213,7 @@
         <v>46043</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61286,7 +61286,7 @@
         <v>46176</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>45883</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>44596</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61510,7 +61510,7 @@
         <v>46175</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61583,7 +61583,7 @@
         <v>46175</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61661,7 +61661,7 @@
         <v>46136</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61734,7 +61734,7 @@
         <v>45884</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61807,7 +61807,7 @@
         <v>46051</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61880,7 +61880,7 @@
         <v>46043</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>46042</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>46079</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62099,7 +62099,7 @@
         <v>46177</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62177,7 +62177,7 @@
         <v>46178</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62255,7 +62255,7 @@
         <v>46179</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62328,7 +62328,7 @@
         <v>46177</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62401,7 +62401,7 @@
         <v>44777</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62479,7 +62479,7 @@
         <v>45754</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62557,7 +62557,7 @@
         <v>45566</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62630,7 +62630,7 @@
         <v>46084</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62703,7 +62703,7 @@
         <v>45758</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62781,7 +62781,7 @@
         <v>46181</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62859,7 +62859,7 @@
         <v>46182</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62937,7 +62937,7 @@
         <v>45618</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63015,7 +63015,7 @@
         <v>45686</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63093,7 +63093,7 @@
         <v>46181</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63171,7 +63171,7 @@
         <v>46183</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63244,7 +63244,7 @@
         <v>46184</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63322,7 +63322,7 @@
         <v>46188</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63395,7 +63395,7 @@
         <v>46188</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63473,7 +63473,7 @@
         <v>44552</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63546,7 +63546,7 @@
         <v>46185</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>45604</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63697,7 +63697,7 @@
         <v>46188</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63775,7 +63775,7 @@
         <v>46188</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63848,7 +63848,7 @@
         <v>44797</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63926,7 +63926,7 @@
         <v>46185</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64004,7 +64004,7 @@
         <v>46188</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64077,7 +64077,7 @@
         <v>45532</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64150,7 +64150,7 @@
         <v>44812</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64228,7 +64228,7 @@
         <v>45902</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64301,7 +64301,7 @@
         <v>45601</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64374,7 +64374,7 @@
         <v>45499</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64447,7 +64447,7 @@
         <v>45140</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64520,7 +64520,7 @@
         <v>46195</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64593,7 +64593,7 @@
         <v>46196</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64666,7 +64666,7 @@
         <v>46195</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
         <v>46195</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64812,7 +64812,7 @@
         <v>45231</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>46196</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64963,7 +64963,7 @@
         <v>46196</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65041,7 +65041,7 @@
         <v>45671</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65119,7 +65119,7 @@
         <v>46198</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65197,7 +65197,7 @@
         <v>46198</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65270,7 +65270,7 @@
         <v>46178</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65343,7 +65343,7 @@
         <v>46197</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65416,7 +65416,7 @@
         <v>45090</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65489,7 +65489,7 @@
         <v>44797</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>46198</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65640,7 +65640,7 @@
         <v>45072</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65713,7 +65713,7 @@
         <v>44960</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65791,7 +65791,7 @@
         <v>45170</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65869,7 +65869,7 @@
         <v>45121</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65942,7 +65942,7 @@
         <v>46204</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66020,7 +66020,7 @@
         <v>46206</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66093,7 +66093,7 @@
         <v>46206</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66166,7 +66166,7 @@
         <v>46206</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>45058</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66312,7 +66312,7 @@
         <v>45541</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66390,7 +66390,7 @@
         <v>46209</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66463,7 +66463,7 @@
         <v>46209</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66536,7 +66536,7 @@
         <v>46209</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66609,7 +66609,7 @@
         <v>46209</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66682,7 +66682,7 @@
         <v>45733</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66760,7 +66760,7 @@
         <v>45757</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66838,7 +66838,7 @@
         <v>45373</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66916,7 +66916,7 @@
         <v>46213</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66989,7 +66989,7 @@
         <v>45636</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67067,7 +67067,7 @@
         <v>46213</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67140,7 +67140,7 @@
         <v>46066</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67213,7 +67213,7 @@
         <v>45034</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67291,7 +67291,7 @@
         <v>44690</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67364,7 +67364,7 @@
         <v>46259</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67442,7 +67442,7 @@
         <v>46259</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67515,7 +67515,7 @@
         <v>46213</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67588,7 +67588,7 @@
         <v>46258</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67661,7 +67661,7 @@
         <v>46043</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67734,7 +67734,7 @@
         <v>46184</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67807,7 +67807,7 @@
         <v>45579</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67880,7 +67880,7 @@
         <v>45140</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67953,7 +67953,7 @@
         <v>46184</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68026,7 +68026,7 @@
         <v>46184</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68099,7 +68099,7 @@
         <v>45204</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68172,7 +68172,7 @@
         <v>46261</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68245,7 +68245,7 @@
         <v>45631</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68318,7 +68318,7 @@
         <v>46220</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68391,7 +68391,7 @@
         <v>44930</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68469,7 +68469,7 @@
         <v>44938</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68547,7 +68547,7 @@
         <v>46220</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68625,7 +68625,7 @@
         <v>46265</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68703,7 +68703,7 @@
         <v>46262</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68776,7 +68776,7 @@
         <v>44960</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68849,7 +68849,7 @@
         <v>46220</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68927,7 +68927,7 @@
         <v>46220</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69000,7 +69000,7 @@
         <v>45364</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69078,7 +69078,7 @@
         <v>45539</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69151,7 +69151,7 @@
         <v>45358</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69229,7 +69229,7 @@
         <v>44952</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69307,7 +69307,7 @@
         <v>46223</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69385,7 +69385,7 @@
         <v>46007</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69458,7 +69458,7 @@
         <v>45582</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69536,7 +69536,7 @@
         <v>46226</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69609,7 +69609,7 @@
         <v>46269</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69682,7 +69682,7 @@
         <v>46007</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69755,7 +69755,7 @@
         <v>46226</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69828,7 +69828,7 @@
         <v>44713</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69901,7 +69901,7 @@
         <v>46227</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69974,7 +69974,7 @@
         <v>44765</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70047,7 +70047,7 @@
         <v>46273</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70125,7 +70125,7 @@
         <v>46272</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70198,7 +70198,7 @@
         <v>46273</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70271,7 +70271,7 @@
         <v>45545</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70349,7 +70349,7 @@
         <v>46272</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70422,7 +70422,7 @@
         <v>46273</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70495,7 +70495,7 @@
         <v>46275</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70568,7 +70568,7 @@
         <v>46274</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70641,7 +70641,7 @@
         <v>46274</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70714,7 +70714,7 @@
         <v>46234</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70792,7 +70792,7 @@
         <v>45637</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70865,7 +70865,7 @@
         <v>45063</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70943,7 +70943,7 @@
         <v>46280</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71016,7 +71016,7 @@
         <v>45037</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71089,7 +71089,7 @@
         <v>45149</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71162,7 +71162,7 @@
         <v>46280</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71235,7 +71235,7 @@
         <v>45175</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71308,7 +71308,7 @@
         <v>44900</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71386,7 +71386,7 @@
         <v>44900</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71464,7 +71464,7 @@
         <v>46238</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71537,7 +71537,7 @@
         <v>44704</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71610,7 +71610,7 @@
         <v>45607</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71688,7 +71688,7 @@
         <v>45607</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71766,7 +71766,7 @@
         <v>45616</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71839,7 +71839,7 @@
         <v>45590</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71912,7 +71912,7 @@
         <v>44763</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71990,7 +71990,7 @@
         <v>45154</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72063,7 +72063,7 @@
         <v>45504</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72136,7 +72136,7 @@
         <v>45219</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72214,7 +72214,7 @@
         <v>45695</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72287,7 +72287,7 @@
         <v>46283</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72360,7 +72360,7 @@
         <v>46184</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72433,7 +72433,7 @@
         <v>44679</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72511,7 +72511,7 @@
         <v>45617</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72589,7 +72589,7 @@
         <v>44628</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72662,7 +72662,7 @@
         <v>46282</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72735,7 +72735,7 @@
         <v>45607</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72808,7 +72808,7 @@
         <v>46185</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72886,7 +72886,7 @@
         <v>45617</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72964,7 +72964,7 @@
         <v>45719</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73042,7 +73042,7 @@
         <v>45729</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73120,7 +73120,7 @@
         <v>44739</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73193,7 +73193,7 @@
         <v>46244</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73266,7 +73266,7 @@
         <v>45574</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73339,7 +73339,7 @@
         <v>45173</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73412,7 +73412,7 @@
         <v>45644</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73490,7 +73490,7 @@
         <v>44938</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73563,7 +73563,7 @@
         <v>46244</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73636,7 +73636,7 @@
         <v>45187</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73709,7 +73709,7 @@
         <v>46241</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73782,7 +73782,7 @@
         <v>46288</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73860,7 +73860,7 @@
         <v>46289</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73938,7 +73938,7 @@
         <v>45062</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74011,7 +74011,7 @@
         <v>44952</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74089,7 +74089,7 @@
         <v>44952</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74167,7 +74167,7 @@
         <v>45513</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74245,7 +74245,7 @@
         <v>46288</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74323,7 +74323,7 @@
         <v>44551</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74396,7 +74396,7 @@
         <v>46289</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74469,7 +74469,7 @@
         <v>45142</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74547,7 +74547,7 @@
         <v>45142</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74625,7 +74625,7 @@
         <v>45462</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74698,7 +74698,7 @@
         <v>45770</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74771,7 +74771,7 @@
         <v>44868</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74849,7 +74849,7 @@
         <v>45252</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74922,7 +74922,7 @@
         <v>45603</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75000,7 +75000,7 @@
         <v>46293</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75078,7 +75078,7 @@
         <v>45489</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75156,7 +75156,7 @@
         <v>46293</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75234,7 +75234,7 @@
         <v>45463</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75312,7 +75312,7 @@
         <v>45617</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75390,7 +75390,7 @@
         <v>44869</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75463,7 +75463,7 @@
         <v>45687</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75536,7 +75536,7 @@
         <v>44999</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75609,7 +75609,7 @@
         <v>44965</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75682,7 +75682,7 @@
         <v>46251</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75760,7 +75760,7 @@
         <v>44939</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75833,7 +75833,7 @@
         <v>46100</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75906,7 +75906,7 @@
         <v>45639</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75979,7 +75979,7 @@
         <v>45020</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76057,7 +76057,7 @@
         <v>46198</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76135,7 +76135,7 @@
         <v>45271</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76213,7 +76213,7 @@
         <v>46294</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76291,7 +76291,7 @@
         <v>45642</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76364,7 +76364,7 @@
         <v>46099</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76442,7 +76442,7 @@
         <v>45632</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76520,7 +76520,7 @@
         <v>46069</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76593,7 +76593,7 @@
         <v>46231</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76666,7 +76666,7 @@
         <v>44547</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76739,7 +76739,7 @@
         <v>46202</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76812,7 +76812,7 @@
         <v>45223</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76890,7 +76890,7 @@
         <v>46253</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76963,7 +76963,7 @@
         <v>46254</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77041,7 +77041,7 @@
         <v>44589</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77114,7 +77114,7 @@
         <v>45593</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77187,7 +77187,7 @@
         <v>44985</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77265,7 +77265,7 @@
         <v>45622</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77343,7 +77343,7 @@
         <v>46296</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77421,7 +77421,7 @@
         <v>46071</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77494,7 +77494,7 @@
         <v>45372</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77572,7 +77572,7 @@
         <v>45019</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77645,7 +77645,7 @@
         <v>45770</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77718,7 +77718,7 @@
         <v>46253</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77796,7 +77796,7 @@
         <v>46255</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77869,7 +77869,7 @@
         <v>44720</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77942,7 +77942,7 @@
         <v>46253</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78020,7 +78020,7 @@
         <v>46272</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78093,7 +78093,7 @@
         <v>46253</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78171,7 +78171,7 @@
         <v>45382</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78244,7 +78244,7 @@
         <v>44844</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78322,7 +78322,7 @@
         <v>44967</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78400,7 +78400,7 @@
         <v>44943</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78473,7 +78473,7 @@
         <v>45567</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78546,7 +78546,7 @@
         <v>45636</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78624,7 +78624,7 @@
         <v>45624</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78697,7 +78697,7 @@
         <v>45632</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78775,7 +78775,7 @@
         <v>45763</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78853,7 +78853,7 @@
         <v>45271</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78926,7 +78926,7 @@
         <v>44808</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78999,7 +78999,7 @@
         <v>45019</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79072,7 +79072,7 @@
         <v>44603</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79145,7 +79145,7 @@
         <v>45622</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79218,7 +79218,7 @@
         <v>44967</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79291,7 +79291,7 @@
         <v>44967</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79364,7 +79364,7 @@
         <v>45544</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79437,7 +79437,7 @@
         <v>45617</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79515,7 +79515,7 @@
         <v>44907</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79593,7 +79593,7 @@
         <v>45539</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79666,7 +79666,7 @@
         <v>45604</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79744,7 +79744,7 @@
         <v>45607</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79817,7 +79817,7 @@
         <v>45545</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79895,7 +79895,7 @@
         <v>45422</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79973,7 +79973,7 @@
         <v>45618</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80051,7 +80051,7 @@
         <v>45076</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80124,7 +80124,7 @@
         <v>45439</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80197,7 +80197,7 @@
         <v>44699</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80270,7 +80270,7 @@
         <v>45357</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80343,7 +80343,7 @@
         <v>45175</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80416,7 +80416,7 @@
         <v>45733</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80494,7 +80494,7 @@
         <v>45615</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80567,7 +80567,7 @@
         <v>44964</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80645,7 +80645,7 @@
         <v>44908</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80723,7 +80723,7 @@
         <v>45422</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80801,7 +80801,7 @@
         <v>45506</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80879,7 +80879,7 @@
         <v>44595</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80952,7 +80952,7 @@
         <v>45622</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81030,7 +81030,7 @@
         <v>45622</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81108,7 +81108,7 @@
         <v>45177</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81186,7 +81186,7 @@
         <v>45719</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81264,7 +81264,7 @@
         <v>45260</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81337,7 +81337,7 @@
         <v>45687</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81410,7 +81410,7 @@
         <v>45741</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81483,7 +81483,7 @@
         <v>44859</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81556,7 +81556,7 @@
         <v>45545</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81629,7 +81629,7 @@
         <v>44502</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81702,7 +81702,7 @@
         <v>45124</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81775,7 +81775,7 @@
         <v>44789</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81848,7 +81848,7 @@
         <v>44789</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81921,7 +81921,7 @@
         <v>45489</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81999,7 +81999,7 @@
         <v>45301</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82072,7 +82072,7 @@
         <v>45636</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82145,7 +82145,7 @@
         <v>45763</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82218,7 +82218,7 @@
         <v>45777</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82296,7 +82296,7 @@
         <v>45763</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82374,7 +82374,7 @@
         <v>45763</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82452,7 +82452,7 @@
         <v>45783</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82525,7 +82525,7 @@
         <v>44999</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82598,7 +82598,7 @@
         <v>45498</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82676,7 +82676,7 @@
         <v>45784</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82749,7 +82749,7 @@
         <v>45120</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82822,7 +82822,7 @@
         <v>45650</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82895,7 +82895,7 @@
         <v>45238</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82973,7 +82973,7 @@
         <v>45238</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83051,7 +83051,7 @@
         <v>44538</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83129,7 +83129,7 @@
         <v>45238</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83207,7 +83207,7 @@
         <v>45670</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83285,7 +83285,7 @@
         <v>45238</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83363,7 +83363,7 @@
         <v>45670</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83441,7 +83441,7 @@
         <v>45238</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83519,7 +83519,7 @@
         <v>44929</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83597,7 +83597,7 @@
         <v>45238</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83675,7 +83675,7 @@
         <v>45386</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83748,7 +83748,7 @@
         <v>45238</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83826,7 +83826,7 @@
         <v>45238</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83904,7 +83904,7 @@
         <v>45670</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83982,7 +83982,7 @@
         <v>45238</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84060,7 +84060,7 @@
         <v>45238</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84138,7 +84138,7 @@
         <v>45238</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84216,7 +84216,7 @@
         <v>45670</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84294,7 +84294,7 @@
         <v>45238</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84372,7 +84372,7 @@
         <v>45670</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84450,7 +84450,7 @@
         <v>45670</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84548,7 +84548,7 @@
         <v>46083</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -601,7 +601,7 @@
         <v>45979</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45664</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44643</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45238</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45245</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45960</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>44771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>46019</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45502</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>44840</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>46073</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45950</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>45734</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>45091</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>46057</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45595</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45219</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44545</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>45544</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45323</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45670</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>46034</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46043</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>46070</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45686</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>46114</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>45994</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>45502</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45297</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>44690</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>46244</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45295</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>44884</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45106</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45670</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45728</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44594</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44685</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45478</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45631</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>45791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>44951</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>45799</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45029</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>45931</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>45056</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>45971</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45979</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45995</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44673</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45834</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>44586</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45296</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>46085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>46177</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>46182</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45741</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>45072</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>45673</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44711</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>46038</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45320</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>45734</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>45775</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>45763</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44959</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>44825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44767</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>44711</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44774</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>44876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>44547</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44686</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44781</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44765</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44605</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44713</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>44475</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44823</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44879</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44831</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44816</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44722</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44741</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44812</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44546</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44502</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44473</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44651</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44509</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44739</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>44692</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>44691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>44797</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44544</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>44853</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44545</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44634</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>44732</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44490</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44525</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44830</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44620</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44692</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44743</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>44840</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44711</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44764</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44552</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44728</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44831</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>44728</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44502</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44571</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44820</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44586</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44530</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44503</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44728</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44785</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>44566</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44711</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44704</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44684</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>44734</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>44728</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44659</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>44692</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45726</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45163</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45775</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45041</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45188</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>44692</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>45644</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45041</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44862</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45289</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45103</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>44886</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>45631</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>45139</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44503</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>45625</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>45068</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>44599</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>45352</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>45573</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>44894</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45170</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>44994</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45642</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>45070</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44900</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45786</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45169</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45786</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>44601</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>44525</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45621</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>46003</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>45001</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>44795</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45622</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44830</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45345</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45345</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>44895</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>44788</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45758</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>46006</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45790</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45791</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>46006</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45762</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44783</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45884</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>46008</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45533</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45610</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45791</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45691</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>45791</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45754</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45950</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45253</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>45888</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45309</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45149</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45888</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>46021</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45343</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45890</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>44886</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>46024</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>45336</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>46026</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>45055</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>45855</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45897</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>45897</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45896</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>46030</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45861</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45896</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45896</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45896</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>46031</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45897</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45898</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>46030</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>45397</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>46030</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>46034</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45903</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>46035</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>46035</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>45566</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>44806</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>46037</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>45559</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45622</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>46037</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>46037</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45793</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>46041</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>45904</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>45236</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45904</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>46038</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45908</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>45792</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>46038</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>45909</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>46039</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>46043</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>45306</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>46043</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>45908</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>46043</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>46043</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>46043</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>46043</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>46043</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>45793</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>46042</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>46042</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>46042</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>46043</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>46043</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45796</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45911</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>46044</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>45191</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46044</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>46044</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>46045</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>46045</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45796</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45680</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45915</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>46045</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>46044</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>46044</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44945</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>45915</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>46069</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>46048</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>46048</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45555</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45569</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45917</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>46048</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45799</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>46048</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45463</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45540</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45586</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>45532</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45917</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>45917</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45799</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>46051</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>46051</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45919</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>46050</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45802</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45802</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>46050</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>46050</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>45799</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45802</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46050</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>46051</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>46051</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>45511</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>44953</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45918</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45918</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45918</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>46053</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>46055</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>45923</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45646</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>46055</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>46055</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>46052</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>46053</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>45924</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>46056</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45924</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>45925</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>46057</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>46057</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>46057</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>46056</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>45297</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>46079</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45912</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>45426</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45176</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>46062</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>46062</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>46062</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45931</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>46062</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>46062</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45425</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>46062</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>46063</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45499</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>46062</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>46063</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>44873</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>46064</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>46064</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>46065</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45931</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>46064</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>46064</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>46065</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>46064</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>46069</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>45936</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>46066</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45554</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>46069</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45936</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45936</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45936</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>45306</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45037</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>46066</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45937</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>46069</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45938</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45938</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>45938</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45938</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>46030</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44678</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>45562</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>46071</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>46071</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>45939</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>46071</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>45938</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>45938</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>46070</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45938</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45938</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45938</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>46070</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>45637</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>45939</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>46071</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>46071</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>45670</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33296,7 +33296,7 @@
         <v>45622</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>45622</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45938</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>46070</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>45937</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>45939</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>45939</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>46073</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45938</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>46072</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>46072</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>46073</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>46072</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>46076</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>45946</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>45947</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46073</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>46076</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>45946</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>44960</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>45946</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45947</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>46078</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45947</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>46079</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>45259</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45309</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45938</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45950</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>44560</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35521,7 +35521,7 @@
         <v>46079</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>46079</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>45243</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>45950</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>46080</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>45950</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>45951</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>45623</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>46084</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>45196</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36256,7 +36256,7 @@
         <v>45419</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45183</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45812</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>46084</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>46084</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>46084</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>46084</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36772,7 +36772,7 @@
         <v>46084</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>45642</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36918,7 +36918,7 @@
         <v>45946</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44781</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>45646</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>45813</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>46086</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>45812</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45236</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37439,7 +37439,7 @@
         <v>45189</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37517,7 +37517,7 @@
         <v>44907</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44998</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>46043</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>46087</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>45958</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>46087</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>46090</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>46090</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>45959</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45148</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45960</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>45758</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>46092</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>46031</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44608</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>45965</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45545</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>45120</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         <v>45663</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>45817</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>45817</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>44811</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>46093</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45541</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>45131</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>45817</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>45971</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45971</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45271</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>46098</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>46098</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>46098</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39923,7 +39923,7 @@
         <v>45971</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>46097</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45968</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>46098</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>45971</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>46099</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>45973</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45216</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>45973</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>44768</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>45973</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>45973</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>45973</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45089</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45974</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>46104</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>46104</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>46125</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>45974</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>44540</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45463</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45979</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45671</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
         <v>45677</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>45981</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>45980</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45980</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>46107</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45646</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>46111</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>45985</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>46111</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>46111</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>46112</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>46112</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>46112</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>46111</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>46111</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42787,7 +42787,7 @@
         <v>46111</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>45184</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42938,7 +42938,7 @@
         <v>45985</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43011,7 +43011,7 @@
         <v>45985</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
         <v>44664</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43162,7 +43162,7 @@
         <v>45985</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43235,7 +43235,7 @@
         <v>45986</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>45176</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43386,7 +43386,7 @@
         <v>45985</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43459,7 +43459,7 @@
         <v>45987</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43532,7 +43532,7 @@
         <v>46113</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43610,7 +43610,7 @@
         <v>46113</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>45824</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45596</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>46118</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>46120</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>46119</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>46119</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>46120</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>46119</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>45103</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>46120</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>46120</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>46120</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>46120</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>45825</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>46120</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>45993</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>45166</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>44573</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         <v>44945</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>46122</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45168,7 +45168,7 @@
         <v>45497</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>46126</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45324,7 +45324,7 @@
         <v>45223</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45397,7 +45397,7 @@
         <v>46126</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>45995</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>46062</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45621,7 +45621,7 @@
         <v>45826</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>46125</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45772,7 +45772,7 @@
         <v>46126</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>44729</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>46100</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>45994</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>45827</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>45999</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>45525</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>45434</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45826</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>44748</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46527,7 +46527,7 @@
         <v>45044</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46600,7 +46600,7 @@
         <v>46000</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46673,7 +46673,7 @@
         <v>45701</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>46133</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46824,7 +46824,7 @@
         <v>46000</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>46127</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46970,7 +46970,7 @@
         <v>45832</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47043,7 +47043,7 @@
         <v>46112</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>45832</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45832</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45771</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>46134</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>45835</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>46134</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45835</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>45835</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>45636</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47803,7 +47803,7 @@
         <v>45232</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47876,7 +47876,7 @@
         <v>46136</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47949,7 +47949,7 @@
         <v>45839</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45554</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
         <v>46030</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48173,7 +48173,7 @@
         <v>46073</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>46021</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>45169</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48392,7 +48392,7 @@
         <v>45840</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
         <v>44886</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45546</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45546</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>45841</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48772,7 +48772,7 @@
         <v>45841</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48850,7 +48850,7 @@
         <v>45915</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45841</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49001,7 +49001,7 @@
         <v>46043</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>46019</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45259</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>46033</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45824</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45846</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>45610</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45846</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45848</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>44874</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>45848</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>44833</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49912,7 +49912,7 @@
         <v>45848</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49985,7 +49985,7 @@
         <v>45170</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50063,7 +50063,7 @@
         <v>44607</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50136,7 +50136,7 @@
         <v>44824</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50209,7 +50209,7 @@
         <v>44644</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50282,7 +50282,7 @@
         <v>45324</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>46139</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>46048</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>45566</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>46136</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50652,7 +50652,7 @@
         <v>45489</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50725,7 +50725,7 @@
         <v>46043</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50798,7 +50798,7 @@
         <v>46136</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50871,7 +50871,7 @@
         <v>45695</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>46135</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>45544</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51095,7 +51095,7 @@
         <v>45509</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51168,7 +51168,7 @@
         <v>45860</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>45860</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51319,7 +51319,7 @@
         <v>45859</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45641</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45642</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>46048</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>46026</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51684,7 +51684,7 @@
         <v>45951</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51757,7 +51757,7 @@
         <v>45884</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>46055</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51908,7 +51908,7 @@
         <v>44964</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51986,7 +51986,7 @@
         <v>45579</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>46021</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>46140</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>45429</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45429</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52356,7 +52356,7 @@
         <v>46031</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>44788</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52507,7 +52507,7 @@
         <v>46084</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52580,7 +52580,7 @@
         <v>44915</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52653,7 +52653,7 @@
         <v>45042</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>46054</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         <v>45537</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>46070</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>46048</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53028,7 +53028,7 @@
         <v>45880</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53106,7 +53106,7 @@
         <v>45618</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53179,7 +53179,7 @@
         <v>46140</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>46098</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53325,7 +53325,7 @@
         <v>46038</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53398,7 +53398,7 @@
         <v>45789</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53476,7 +53476,7 @@
         <v>45313</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53549,7 +53549,7 @@
         <v>45712</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53627,7 +53627,7 @@
         <v>45089</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45079</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53778,7 +53778,7 @@
         <v>45250</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53851,7 +53851,7 @@
         <v>45208</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53924,7 +53924,7 @@
         <v>45043</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53997,7 +53997,7 @@
         <v>46146</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54070,7 +54070,7 @@
         <v>44832</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>46119</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54216,7 +54216,7 @@
         <v>46146</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         <v>46035</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
         <v>45222</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54435,7 +54435,7 @@
         <v>44686</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54513,7 +54513,7 @@
         <v>44601</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54586,7 +54586,7 @@
         <v>45741</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>46146</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54732,7 +54732,7 @@
         <v>46146</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>46038</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>44704</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54956,7 +54956,7 @@
         <v>46055</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55029,7 +55029,7 @@
         <v>45636</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55102,7 +55102,7 @@
         <v>46030</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55175,7 +55175,7 @@
         <v>45141</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55248,7 +55248,7 @@
         <v>46149</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>46149</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55394,7 +55394,7 @@
         <v>44652</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>46078</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45297</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55618,7 +55618,7 @@
         <v>45624</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>46128</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>45729</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55837,7 +55837,7 @@
         <v>45743</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55915,7 +55915,7 @@
         <v>45222</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55988,7 +55988,7 @@
         <v>46155</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56061,7 +56061,7 @@
         <v>46119</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45303</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56207,7 +56207,7 @@
         <v>44783</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>46042</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56353,7 +56353,7 @@
         <v>46155</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>46026</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>46155</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>46035</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56650,7 +56650,7 @@
         <v>45568</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56723,7 +56723,7 @@
         <v>46052</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         <v>45545</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56869,7 +56869,7 @@
         <v>45537</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>45273</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57025,7 +57025,7 @@
         <v>46157</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45748</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57181,7 +57181,7 @@
         <v>46161</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>44616</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57327,7 +57327,7 @@
         <v>46160</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45020</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45020</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45197</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57634,7 +57634,7 @@
         <v>44987</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57707,7 +57707,7 @@
         <v>46043</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57780,7 +57780,7 @@
         <v>45428</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57858,7 +57858,7 @@
         <v>46163</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45607</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58004,7 +58004,7 @@
         <v>46051</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58077,7 +58077,7 @@
         <v>46136</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58150,7 +58150,7 @@
         <v>46111</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58223,7 +58223,7 @@
         <v>45631</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45618</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58374,7 +58374,7 @@
         <v>45546</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58447,7 +58447,7 @@
         <v>46164</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58525,7 +58525,7 @@
         <v>46167</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>44512</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58676,7 +58676,7 @@
         <v>46164</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         <v>45246</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58827,7 +58827,7 @@
         <v>46167</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58900,7 +58900,7 @@
         <v>45628</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58978,7 +58978,7 @@
         <v>44811</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59051,7 +59051,7 @@
         <v>45603</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59124,7 +59124,7 @@
         <v>45603</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>46169</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>44790</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>45579</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59416,7 +59416,7 @@
         <v>45881</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59489,7 +59489,7 @@
         <v>46168</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>45399</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59635,7 +59635,7 @@
         <v>45635</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59713,7 +59713,7 @@
         <v>45525</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59791,7 +59791,7 @@
         <v>46170</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>45880</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59947,7 +59947,7 @@
         <v>45537</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60025,7 +60025,7 @@
         <v>46170</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60098,7 +60098,7 @@
         <v>46035</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60171,7 +60171,7 @@
         <v>45883</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45880</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>46029</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60390,7 +60390,7 @@
         <v>46030</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60463,7 +60463,7 @@
         <v>45882</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60541,7 +60541,7 @@
         <v>46171</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60614,7 +60614,7 @@
         <v>45622</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60687,7 +60687,7 @@
         <v>45622</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         <v>45667</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60833,7 +60833,7 @@
         <v>45670</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>46171</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>46171</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61062,7 +61062,7 @@
         <v>45287</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61135,7 +61135,7 @@
         <v>45455</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61213,7 +61213,7 @@
         <v>46043</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61286,7 +61286,7 @@
         <v>46176</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>45883</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>44596</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61510,7 +61510,7 @@
         <v>46175</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61583,7 +61583,7 @@
         <v>46175</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61661,7 +61661,7 @@
         <v>46136</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61734,7 +61734,7 @@
         <v>45884</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61807,7 +61807,7 @@
         <v>46051</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61880,7 +61880,7 @@
         <v>46043</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>46042</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>46079</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62099,7 +62099,7 @@
         <v>46177</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62177,7 +62177,7 @@
         <v>46178</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62255,7 +62255,7 @@
         <v>46179</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62328,7 +62328,7 @@
         <v>46177</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62401,7 +62401,7 @@
         <v>44777</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62479,7 +62479,7 @@
         <v>45754</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62557,7 +62557,7 @@
         <v>45566</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62630,7 +62630,7 @@
         <v>46084</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62703,7 +62703,7 @@
         <v>45758</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62781,7 +62781,7 @@
         <v>46181</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62859,7 +62859,7 @@
         <v>46182</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62937,7 +62937,7 @@
         <v>45618</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63015,7 +63015,7 @@
         <v>45686</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63093,7 +63093,7 @@
         <v>46181</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63171,7 +63171,7 @@
         <v>46183</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63244,7 +63244,7 @@
         <v>46184</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63322,7 +63322,7 @@
         <v>46188</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63395,7 +63395,7 @@
         <v>46188</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63473,7 +63473,7 @@
         <v>44552</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63546,7 +63546,7 @@
         <v>46185</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>45604</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63697,7 +63697,7 @@
         <v>46188</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63775,7 +63775,7 @@
         <v>46188</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63848,7 +63848,7 @@
         <v>44797</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63926,7 +63926,7 @@
         <v>46185</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64004,7 +64004,7 @@
         <v>46188</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64077,7 +64077,7 @@
         <v>45532</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64150,7 +64150,7 @@
         <v>44812</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64228,7 +64228,7 @@
         <v>45902</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64301,7 +64301,7 @@
         <v>45601</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64374,7 +64374,7 @@
         <v>45499</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64447,7 +64447,7 @@
         <v>45140</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64520,7 +64520,7 @@
         <v>46195</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64593,7 +64593,7 @@
         <v>46196</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64666,7 +64666,7 @@
         <v>46195</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
         <v>46195</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64812,7 +64812,7 @@
         <v>45231</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>46196</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64963,7 +64963,7 @@
         <v>46196</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65041,7 +65041,7 @@
         <v>45671</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65119,7 +65119,7 @@
         <v>46198</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65197,7 +65197,7 @@
         <v>46198</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65270,7 +65270,7 @@
         <v>46178</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65343,7 +65343,7 @@
         <v>46197</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65416,7 +65416,7 @@
         <v>45090</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65489,7 +65489,7 @@
         <v>44797</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>46198</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65640,7 +65640,7 @@
         <v>45072</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65713,7 +65713,7 @@
         <v>44960</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65791,7 +65791,7 @@
         <v>45170</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65869,7 +65869,7 @@
         <v>45121</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65942,7 +65942,7 @@
         <v>46204</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66020,7 +66020,7 @@
         <v>46206</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66093,7 +66093,7 @@
         <v>46206</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66166,7 +66166,7 @@
         <v>46206</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>45058</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66312,7 +66312,7 @@
         <v>45541</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66390,7 +66390,7 @@
         <v>46209</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66463,7 +66463,7 @@
         <v>46209</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66536,7 +66536,7 @@
         <v>46209</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66609,7 +66609,7 @@
         <v>46209</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66682,7 +66682,7 @@
         <v>45733</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66760,7 +66760,7 @@
         <v>45757</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66838,7 +66838,7 @@
         <v>45373</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66916,7 +66916,7 @@
         <v>46213</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66989,7 +66989,7 @@
         <v>45636</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67067,7 +67067,7 @@
         <v>46213</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67140,7 +67140,7 @@
         <v>46066</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67213,7 +67213,7 @@
         <v>45034</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67291,7 +67291,7 @@
         <v>44690</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67364,7 +67364,7 @@
         <v>46259</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67442,7 +67442,7 @@
         <v>46259</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67515,7 +67515,7 @@
         <v>46213</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67588,7 +67588,7 @@
         <v>46258</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67661,7 +67661,7 @@
         <v>46043</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67734,7 +67734,7 @@
         <v>46184</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67807,7 +67807,7 @@
         <v>45579</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67880,7 +67880,7 @@
         <v>45140</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67953,7 +67953,7 @@
         <v>46184</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68026,7 +68026,7 @@
         <v>46184</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68099,7 +68099,7 @@
         <v>45204</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68172,7 +68172,7 @@
         <v>46261</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68245,7 +68245,7 @@
         <v>45631</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68318,7 +68318,7 @@
         <v>46220</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68391,7 +68391,7 @@
         <v>44930</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68469,7 +68469,7 @@
         <v>44938</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68547,7 +68547,7 @@
         <v>46220</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68625,7 +68625,7 @@
         <v>46265</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68703,7 +68703,7 @@
         <v>46262</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68776,7 +68776,7 @@
         <v>44960</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68849,7 +68849,7 @@
         <v>46220</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68927,7 +68927,7 @@
         <v>46220</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69000,7 +69000,7 @@
         <v>45364</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69078,7 +69078,7 @@
         <v>45539</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69151,7 +69151,7 @@
         <v>45358</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69229,7 +69229,7 @@
         <v>44952</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69307,7 +69307,7 @@
         <v>46223</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69385,7 +69385,7 @@
         <v>46007</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69458,7 +69458,7 @@
         <v>45582</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69536,7 +69536,7 @@
         <v>46226</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69609,7 +69609,7 @@
         <v>46269</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69682,7 +69682,7 @@
         <v>46007</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69755,7 +69755,7 @@
         <v>46226</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69828,7 +69828,7 @@
         <v>44713</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69901,7 +69901,7 @@
         <v>46227</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69974,7 +69974,7 @@
         <v>44765</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70047,7 +70047,7 @@
         <v>46273</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70125,7 +70125,7 @@
         <v>46272</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70198,7 +70198,7 @@
         <v>46273</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70271,7 +70271,7 @@
         <v>45545</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70349,7 +70349,7 @@
         <v>46272</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70422,7 +70422,7 @@
         <v>46273</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70495,7 +70495,7 @@
         <v>46275</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70568,7 +70568,7 @@
         <v>46274</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70641,7 +70641,7 @@
         <v>46274</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70714,7 +70714,7 @@
         <v>46234</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70792,7 +70792,7 @@
         <v>45637</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70865,7 +70865,7 @@
         <v>45063</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70943,7 +70943,7 @@
         <v>46280</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71016,7 +71016,7 @@
         <v>45037</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71089,7 +71089,7 @@
         <v>45149</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71162,7 +71162,7 @@
         <v>46280</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71235,7 +71235,7 @@
         <v>45175</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71308,7 +71308,7 @@
         <v>44900</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71386,7 +71386,7 @@
         <v>44900</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71464,7 +71464,7 @@
         <v>46238</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71537,7 +71537,7 @@
         <v>44704</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71610,7 +71610,7 @@
         <v>45607</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71688,7 +71688,7 @@
         <v>45607</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71766,7 +71766,7 @@
         <v>45616</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71839,7 +71839,7 @@
         <v>45590</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71912,7 +71912,7 @@
         <v>44763</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71990,7 +71990,7 @@
         <v>45154</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72063,7 +72063,7 @@
         <v>45504</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72136,7 +72136,7 @@
         <v>45219</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72214,7 +72214,7 @@
         <v>45695</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72287,7 +72287,7 @@
         <v>46283</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72360,7 +72360,7 @@
         <v>46184</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72433,7 +72433,7 @@
         <v>44679</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72511,7 +72511,7 @@
         <v>45617</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72589,7 +72589,7 @@
         <v>44628</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72662,7 +72662,7 @@
         <v>46282</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72735,7 +72735,7 @@
         <v>45607</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72808,7 +72808,7 @@
         <v>46185</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72886,7 +72886,7 @@
         <v>45617</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72964,7 +72964,7 @@
         <v>45719</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73042,7 +73042,7 @@
         <v>45729</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73120,7 +73120,7 @@
         <v>44739</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73193,7 +73193,7 @@
         <v>46244</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73266,7 +73266,7 @@
         <v>45574</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73339,7 +73339,7 @@
         <v>45173</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73412,7 +73412,7 @@
         <v>45644</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73490,7 +73490,7 @@
         <v>44938</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73563,7 +73563,7 @@
         <v>46244</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73636,7 +73636,7 @@
         <v>45187</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73709,7 +73709,7 @@
         <v>46241</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73782,7 +73782,7 @@
         <v>46288</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73860,7 +73860,7 @@
         <v>46289</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73938,7 +73938,7 @@
         <v>45062</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74011,7 +74011,7 @@
         <v>44952</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74089,7 +74089,7 @@
         <v>44952</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74167,7 +74167,7 @@
         <v>45513</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74245,7 +74245,7 @@
         <v>46288</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74323,7 +74323,7 @@
         <v>44551</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74396,7 +74396,7 @@
         <v>46289</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74469,7 +74469,7 @@
         <v>45142</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74547,7 +74547,7 @@
         <v>45142</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74625,7 +74625,7 @@
         <v>45462</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74698,7 +74698,7 @@
         <v>45770</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74771,7 +74771,7 @@
         <v>44868</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74849,7 +74849,7 @@
         <v>45252</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74922,7 +74922,7 @@
         <v>45603</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75000,7 +75000,7 @@
         <v>46293</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75078,7 +75078,7 @@
         <v>45489</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75156,7 +75156,7 @@
         <v>46293</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75234,7 +75234,7 @@
         <v>45463</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75312,7 +75312,7 @@
         <v>45617</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75390,7 +75390,7 @@
         <v>44869</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75463,7 +75463,7 @@
         <v>45687</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75536,7 +75536,7 @@
         <v>44999</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75609,7 +75609,7 @@
         <v>44965</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75682,7 +75682,7 @@
         <v>46251</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75760,7 +75760,7 @@
         <v>44939</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75833,7 +75833,7 @@
         <v>46100</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75906,7 +75906,7 @@
         <v>45639</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75979,7 +75979,7 @@
         <v>45020</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76057,7 +76057,7 @@
         <v>46198</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76135,7 +76135,7 @@
         <v>45271</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76213,7 +76213,7 @@
         <v>46294</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76291,7 +76291,7 @@
         <v>45642</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76364,7 +76364,7 @@
         <v>46099</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76442,7 +76442,7 @@
         <v>45632</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76520,7 +76520,7 @@
         <v>46069</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76593,7 +76593,7 @@
         <v>46231</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76666,7 +76666,7 @@
         <v>44547</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76739,7 +76739,7 @@
         <v>46202</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76812,7 +76812,7 @@
         <v>45223</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76890,7 +76890,7 @@
         <v>46253</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76963,7 +76963,7 @@
         <v>46254</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77041,7 +77041,7 @@
         <v>44589</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77114,7 +77114,7 @@
         <v>45593</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77187,7 +77187,7 @@
         <v>44985</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77265,7 +77265,7 @@
         <v>45622</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77343,7 +77343,7 @@
         <v>46296</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77421,7 +77421,7 @@
         <v>46071</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77494,7 +77494,7 @@
         <v>45372</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77572,7 +77572,7 @@
         <v>45019</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77645,7 +77645,7 @@
         <v>45770</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77718,7 +77718,7 @@
         <v>46253</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77796,7 +77796,7 @@
         <v>46255</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77869,7 +77869,7 @@
         <v>44720</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77942,7 +77942,7 @@
         <v>46253</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78020,7 +78020,7 @@
         <v>46272</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78093,7 +78093,7 @@
         <v>46253</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78171,7 +78171,7 @@
         <v>45382</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78244,7 +78244,7 @@
         <v>44844</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78322,7 +78322,7 @@
         <v>44967</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78400,7 +78400,7 @@
         <v>44943</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78473,7 +78473,7 @@
         <v>45567</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78546,7 +78546,7 @@
         <v>45636</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78624,7 +78624,7 @@
         <v>45624</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78697,7 +78697,7 @@
         <v>45632</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78775,7 +78775,7 @@
         <v>45763</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78853,7 +78853,7 @@
         <v>45271</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78926,7 +78926,7 @@
         <v>44808</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78999,7 +78999,7 @@
         <v>45019</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79072,7 +79072,7 @@
         <v>44603</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79145,7 +79145,7 @@
         <v>45622</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79218,7 +79218,7 @@
         <v>44967</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79291,7 +79291,7 @@
         <v>44967</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79364,7 +79364,7 @@
         <v>45544</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79437,7 +79437,7 @@
         <v>45617</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79515,7 +79515,7 @@
         <v>44907</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79593,7 +79593,7 @@
         <v>45539</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79666,7 +79666,7 @@
         <v>45604</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79744,7 +79744,7 @@
         <v>45607</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79817,7 +79817,7 @@
         <v>45545</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79895,7 +79895,7 @@
         <v>45422</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79973,7 +79973,7 @@
         <v>45618</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80051,7 +80051,7 @@
         <v>45076</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80124,7 +80124,7 @@
         <v>45439</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80197,7 +80197,7 @@
         <v>44699</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80270,7 +80270,7 @@
         <v>45357</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80343,7 +80343,7 @@
         <v>45175</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80416,7 +80416,7 @@
         <v>45733</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80494,7 +80494,7 @@
         <v>45615</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80567,7 +80567,7 @@
         <v>44964</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80645,7 +80645,7 @@
         <v>44908</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80723,7 +80723,7 @@
         <v>45422</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80801,7 +80801,7 @@
         <v>45506</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80879,7 +80879,7 @@
         <v>44595</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80952,7 +80952,7 @@
         <v>45622</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81030,7 +81030,7 @@
         <v>45622</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81108,7 +81108,7 @@
         <v>45177</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81186,7 +81186,7 @@
         <v>45719</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81264,7 +81264,7 @@
         <v>45260</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81337,7 +81337,7 @@
         <v>45687</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81410,7 +81410,7 @@
         <v>45741</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81483,7 +81483,7 @@
         <v>44859</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81556,7 +81556,7 @@
         <v>45545</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81629,7 +81629,7 @@
         <v>44502</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81702,7 +81702,7 @@
         <v>45124</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81775,7 +81775,7 @@
         <v>44789</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81848,7 +81848,7 @@
         <v>44789</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81921,7 +81921,7 @@
         <v>45489</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81999,7 +81999,7 @@
         <v>45301</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82072,7 +82072,7 @@
         <v>45636</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82145,7 +82145,7 @@
         <v>45763</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82218,7 +82218,7 @@
         <v>45777</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82296,7 +82296,7 @@
         <v>45763</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82374,7 +82374,7 @@
         <v>45763</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82452,7 +82452,7 @@
         <v>45783</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82525,7 +82525,7 @@
         <v>44999</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82598,7 +82598,7 @@
         <v>45498</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82676,7 +82676,7 @@
         <v>45784</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82749,7 +82749,7 @@
         <v>45120</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82822,7 +82822,7 @@
         <v>45650</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82895,7 +82895,7 @@
         <v>45238</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82973,7 +82973,7 @@
         <v>45238</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83051,7 +83051,7 @@
         <v>44538</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83129,7 +83129,7 @@
         <v>45238</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83207,7 +83207,7 @@
         <v>45670</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83285,7 +83285,7 @@
         <v>45238</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83363,7 +83363,7 @@
         <v>45670</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83441,7 +83441,7 @@
         <v>45238</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83519,7 +83519,7 @@
         <v>44929</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83597,7 +83597,7 @@
         <v>45238</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83675,7 +83675,7 @@
         <v>45386</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83748,7 +83748,7 @@
         <v>45238</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83826,7 +83826,7 @@
         <v>45238</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83904,7 +83904,7 @@
         <v>45670</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83982,7 +83982,7 @@
         <v>45238</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84060,7 +84060,7 @@
         <v>45238</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84138,7 +84138,7 @@
         <v>45238</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84216,7 +84216,7 @@
         <v>45670</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84294,7 +84294,7 @@
         <v>45238</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84372,7 +84372,7 @@
         <v>45670</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84450,7 +84450,7 @@
         <v>45670</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84548,7 +84548,7 @@
         <v>46083</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -601,7 +601,7 @@
         <v>45979</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45664</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44643</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45238</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45245</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45960</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45296</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>45478</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>44771</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>46019</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45502</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>44840</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>45734</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45950</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45091</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>46057</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45219</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45595</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>46073</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44545</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>45544</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45323</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45670</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45106</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>45297</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45295</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44884</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45686</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>45502</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>46114</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45994</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>46034</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>46043</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>46043</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>46070</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>46244</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45670</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45728</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44594</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44685</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45296</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>45478</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>44964</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45763</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>45791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45029</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44951</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45631</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>44673</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45799</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45931</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44586</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45673</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44711</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>45834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>45971</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>45320</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>45979</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>45056</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45775</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45734</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>45995</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45072</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>45741</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>46085</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>46177</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>46182</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>46038</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44959</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>44825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44767</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>44711</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44774</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>44876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>44547</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44686</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44781</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44765</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44605</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44713</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>44823</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44879</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44722</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44831</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44816</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44812</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44741</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44546</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>44502</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>44651</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44509</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44552</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44490</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44732</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44739</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44502</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44571</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>44692</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44525</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>44728</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>44691</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44797</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44544</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>44820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44853</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>44830</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44586</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44620</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44728</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>44785</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44692</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44743</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44530</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>44711</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44840</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>44503</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>44764</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>44711</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>44545</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>44728</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44566</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>44634</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44704</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>44692</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>44684</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45044</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>44734</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>45428</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>44728</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>45741</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45148</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44874</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45617</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45037</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45541</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45357</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45419</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45646</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44886</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>44844</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45559</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>44790</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44900</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45364</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45019</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45303</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44869</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45712</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45297</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45667</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45670</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>45670</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>45555</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45573</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>45677</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45324</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44789</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>44765</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>45043</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>45621</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45426</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>44964</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44783</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45103</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45562</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>45635</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45566</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45089</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45183</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45644</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45763</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44512</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44832</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45541</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45397</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45287</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>44833</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45607</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45617</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45758</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44952</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45622</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45884</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45455</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>44812</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45463</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45232</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>45636</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45719</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>45883</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>45489</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>45169</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44552</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45726</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45622</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45139</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45880</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>44781</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45623</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45884</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45124</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45883</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45103</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45079</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>44862</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45888</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45140</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45271</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45537</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44938</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44938</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>44998</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45888</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45289</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44908</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45890</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45604</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45513</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45504</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>45537</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>44907</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>44502</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45058</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45603</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45603</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>44945</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45041</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45855</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45499</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45896</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45861</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45896</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45896</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45896</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>45897</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45897</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45897</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>45898</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>44713</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45176</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45546</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45579</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45632</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>44939</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44930</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44628</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45601</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45904</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45622</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>44994</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45618</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>45306</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45729</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>45141</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>45343</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45903</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>44560</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>44601</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45636</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45904</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45908</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>45545</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>45908</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45352</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>45042</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>45120</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>45463</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>45909</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45537</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45525</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45777</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>45622</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>45566</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>44599</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45566</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>45596</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>45911</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44601</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>45618</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45271</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45642</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>45783</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>45763</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45763</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45076</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>44603</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>44999</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45915</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>45784</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>45358</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45915</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>44616</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>44900</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>44900</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45498</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>45917</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>45301</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>45149</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>45917</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45917</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45184</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45170</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44503</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45120</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45918</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>44664</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>45918</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>45918</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>45063</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45618</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45533</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45545</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45545</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45422</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45593</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45919</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45260</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45786</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45924</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45462</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>44525</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45923</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>45539</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45754</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>45924</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>45748</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>45579</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45786</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45671</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>45574</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45925</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45791</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45687</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45618</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45758</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45792</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45791</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45055</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>45236</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>45188</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44659</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45506</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>44788</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45791</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45637</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45790</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>44692</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44551</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>45733</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45796</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>44596</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45793</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>45719</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45912</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45631</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>45631</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31737,7 +31737,7 @@
         <v>45175</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>45173</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45170</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>45628</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>44644</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>45631</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>45569</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45191</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>45793</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>45796</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>45309</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>45642</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>45701</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45622</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45686</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>44967</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>44967</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>45499</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>45644</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>45463</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>45931</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>44943</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45532</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45931</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>44915</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45540</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45622</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>44607</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45372</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>45586</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45936</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45936</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>45936</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>45253</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>45799</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>44589</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>45204</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>45936</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>45545</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>44907</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45603</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45131</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>45799</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>45757</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>45799</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>45615</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>44859</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>45802</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>45671</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45937</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>45802</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45176</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>45695</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>45802</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>44953</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>45937</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35940,7 +35940,7 @@
         <v>45636</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>45223</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45197</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>44547</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>45306</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45938</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>44873</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>45938</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45938</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>45607</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>45607</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44960</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45590</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45938</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>45938</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45938</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>45070</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>44894</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>45639</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>45691</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>45938</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>45938</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45259</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45309</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>45938</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>45938</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45938</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>45687</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>45939</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45939</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>45939</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45939</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>45222</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>45622</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>45812</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45219</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45624</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45622</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>45622</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45946</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>45812</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45946</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45946</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45646</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>44540</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39270,7 +39270,7 @@
         <v>45813</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>45223</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>44699</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>44679</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>45663</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39645,7 +39645,7 @@
         <v>44678</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39723,7 +39723,7 @@
         <v>45149</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>45947</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39874,7 +39874,7 @@
         <v>45817</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45121</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45817</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40103,7 +40103,7 @@
         <v>45817</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45271</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>45582</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45579</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>45950</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45947</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45216</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>44686</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>45947</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45824</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45763</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>45826</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>44960</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41087,7 +41087,7 @@
         <v>45637</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45950</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>45826</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>45950</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>45020</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>45020</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>45642</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>45951</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>45567</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>44952</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>45825</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41910,7 +41910,7 @@
         <v>44952</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>45090</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45208</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>44704</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45827</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45511</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>45140</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>44763</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45832</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>44748</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45938</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45741</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45832</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>45832</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>44704</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>45958</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>45946</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43186,7 +43186,7 @@
         <v>45020</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>45960</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>45959</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>45642</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45632</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45154</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>45062</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>44768</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45236</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>45259</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>44964</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>45439</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45166</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45610</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>45835</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45835</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45835</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>45429</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45965</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45840</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>45646</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>44608</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45142</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45142</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45008,7 +45008,7 @@
         <v>45616</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45081,7 +45081,7 @@
         <v>45554</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45839</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>44720</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>45169</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45968</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45729</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>45841</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>45617</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45841</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>44999</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45841</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44739</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>45846</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>45846</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45971</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>45971</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45636</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45971</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45175</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>44795</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46591,7 +46591,7 @@
         <v>45775</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45971</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>45762</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>45848</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46903,7 +46903,7 @@
         <v>45973</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45848</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>45189</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45034</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>45973</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>45848</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>45973</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45974</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45973</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>45973</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>45974</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>44777</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>44808</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>45695</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>45860</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45859</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>45544</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48179,7 +48179,7 @@
         <v>45041</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45860</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>45313</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>45636</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>44595</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>44987</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>44811</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>44811</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48773,7 +48773,7 @@
         <v>44797</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45625</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48924,7 +48924,7 @@
         <v>45980</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45980</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>45979</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>44797</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45196</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>44985</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>44886</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>44886</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>44895</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>44830</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>44967</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>45489</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>44789</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45981</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>44783</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45880</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45617</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>45019</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45273</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>45881</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45882</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45345</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45345</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45170</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45758</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50834,7 +50834,7 @@
         <v>45243</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45985</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>46098</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45985</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>46098</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>46099</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>46098</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>46098</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45525</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>44868</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>45985</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45986</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>45399</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>45985</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45985</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>46125</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>46104</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>46104</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45429</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>45177</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52324,7 +52324,7 @@
         <v>45624</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45532</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52470,7 +52470,7 @@
         <v>45072</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>46107</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52621,7 +52621,7 @@
         <v>45068</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>45987</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52767,7 +52767,7 @@
         <v>46111</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>45425</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         <v>46111</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45641</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>45231</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>46111</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         <v>46111</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>46111</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>44960</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>46111</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53527,7 +53527,7 @@
         <v>46112</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53605,7 +53605,7 @@
         <v>46112</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53678,7 +53678,7 @@
         <v>46113</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53756,7 +53756,7 @@
         <v>46113</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53829,7 +53829,7 @@
         <v>44965</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53902,7 +53902,7 @@
         <v>44573</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>46112</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>45743</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>46119</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54199,7 +54199,7 @@
         <v>46118</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54272,7 +54272,7 @@
         <v>46119</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54345,7 +54345,7 @@
         <v>46119</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>46120</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>46120</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54564,7 +54564,7 @@
         <v>46120</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54637,7 +54637,7 @@
         <v>46120</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54710,7 +54710,7 @@
         <v>46120</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54783,7 +54783,7 @@
         <v>46120</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54856,7 +54856,7 @@
         <v>45993</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54934,7 +54934,7 @@
         <v>46120</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45994</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55080,7 +55080,7 @@
         <v>46122</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55153,7 +55153,7 @@
         <v>45995</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>46125</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>46062</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>46126</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>46126</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55528,7 +55528,7 @@
         <v>45999</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55601,7 +55601,7 @@
         <v>46000</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55674,7 +55674,7 @@
         <v>46000</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55747,7 +55747,7 @@
         <v>46126</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>46100</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>45489</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>44824</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>44806</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         <v>44652</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45187</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56268,7 +56268,7 @@
         <v>45336</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56341,7 +56341,7 @@
         <v>44729</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>46134</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56492,7 +56492,7 @@
         <v>46134</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>46006</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56643,7 +56643,7 @@
         <v>46133</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>46003</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45568</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56862,7 +56862,7 @@
         <v>46006</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56935,7 +56935,7 @@
         <v>45246</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45771</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>46008</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57164,7 +57164,7 @@
         <v>45539</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>46136</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57310,7 +57310,7 @@
         <v>45607</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57383,7 +57383,7 @@
         <v>46135</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57456,7 +57456,7 @@
         <v>45089</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57529,7 +57529,7 @@
         <v>45733</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57607,7 +57607,7 @@
         <v>46136</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>46112</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         <v>45544</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57826,7 +57826,7 @@
         <v>46140</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57899,7 +57899,7 @@
         <v>46038</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57972,7 +57972,7 @@
         <v>45950</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58050,7 +58050,7 @@
         <v>45607</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58123,7 +58123,7 @@
         <v>44690</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58196,7 +58196,7 @@
         <v>45382</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58269,7 +58269,7 @@
         <v>45422</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58347,7 +58347,7 @@
         <v>45604</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58425,7 +58425,7 @@
         <v>46021</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>46048</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58581,7 +58581,7 @@
         <v>45546</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58654,7 +58654,7 @@
         <v>45546</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58727,7 +58727,7 @@
         <v>46024</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58800,7 +58800,7 @@
         <v>46026</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58873,7 +58873,7 @@
         <v>45554</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         <v>46030</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59019,7 +59019,7 @@
         <v>45622</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59097,7 +59097,7 @@
         <v>46140</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59175,7 +59175,7 @@
         <v>46030</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59248,7 +59248,7 @@
         <v>46030</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45770</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59394,7 +59394,7 @@
         <v>45770</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59467,7 +59467,7 @@
         <v>45250</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>46139</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59613,7 +59613,7 @@
         <v>45610</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>46034</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59764,7 +59764,7 @@
         <v>46031</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>46035</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59910,7 +59910,7 @@
         <v>46019</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>45509</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60056,7 +60056,7 @@
         <v>46030</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>46035</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60202,7 +60202,7 @@
         <v>46021</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60275,7 +60275,7 @@
         <v>46048</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>46038</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60421,7 +60421,7 @@
         <v>46037</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60494,7 +60494,7 @@
         <v>46054</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60567,7 +60567,7 @@
         <v>46037</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60640,7 +60640,7 @@
         <v>46037</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60713,7 +60713,7 @@
         <v>46038</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>46042</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60859,7 +60859,7 @@
         <v>46042</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60932,7 +60932,7 @@
         <v>46039</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61005,7 +61005,7 @@
         <v>46042</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61078,7 +61078,7 @@
         <v>46033</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61151,7 +61151,7 @@
         <v>46041</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61224,7 +61224,7 @@
         <v>46043</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45252</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61370,7 +61370,7 @@
         <v>46043</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61443,7 +61443,7 @@
         <v>46136</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61516,7 +61516,7 @@
         <v>46043</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61589,7 +61589,7 @@
         <v>46044</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>46043</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61735,7 +61735,7 @@
         <v>46026</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61808,7 +61808,7 @@
         <v>46044</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61881,7 +61881,7 @@
         <v>46043</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61954,7 +61954,7 @@
         <v>45680</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62027,7 +62027,7 @@
         <v>46043</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62100,7 +62100,7 @@
         <v>46043</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>46044</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62246,7 +62246,7 @@
         <v>46044</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62319,7 +62319,7 @@
         <v>46043</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62392,7 +62392,7 @@
         <v>46043</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>46044</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62538,7 +62538,7 @@
         <v>45037</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62611,7 +62611,7 @@
         <v>45915</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62684,7 +62684,7 @@
         <v>45001</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62757,7 +62757,7 @@
         <v>46048</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62830,7 +62830,7 @@
         <v>46048</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62903,7 +62903,7 @@
         <v>46048</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62976,7 +62976,7 @@
         <v>46045</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63049,7 +63049,7 @@
         <v>46043</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63122,7 +63122,7 @@
         <v>46043</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63195,7 +63195,7 @@
         <v>45824</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>46045</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>46021</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63419,7 +63419,7 @@
         <v>45434</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>46048</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>46073</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63643,7 +63643,7 @@
         <v>45373</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63721,7 +63721,7 @@
         <v>46069</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63794,7 +63794,7 @@
         <v>46045</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63867,7 +63867,7 @@
         <v>46050</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63945,7 +63945,7 @@
         <v>46048</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64023,7 +64023,7 @@
         <v>46098</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64096,7 +64096,7 @@
         <v>45497</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64174,7 +64174,7 @@
         <v>46070</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64247,7 +64247,7 @@
         <v>46050</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>46050</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64398,7 +64398,7 @@
         <v>44788</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64471,7 +64471,7 @@
         <v>45163</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64549,7 +64549,7 @@
         <v>46055</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64622,7 +64622,7 @@
         <v>46050</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64700,7 +64700,7 @@
         <v>46052</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64773,7 +64773,7 @@
         <v>46051</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64846,7 +64846,7 @@
         <v>46051</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64919,7 +64919,7 @@
         <v>46051</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64992,7 +64992,7 @@
         <v>46051</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65065,7 +65065,7 @@
         <v>46056</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65138,7 +65138,7 @@
         <v>46053</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65211,7 +65211,7 @@
         <v>46053</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65284,7 +65284,7 @@
         <v>46056</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65357,7 +65357,7 @@
         <v>46055</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65430,7 +65430,7 @@
         <v>46055</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65508,7 +65508,7 @@
         <v>46055</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65586,7 +65586,7 @@
         <v>46057</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65659,7 +65659,7 @@
         <v>46057</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65732,7 +65732,7 @@
         <v>46057</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65805,7 +65805,7 @@
         <v>45789</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65883,7 +65883,7 @@
         <v>46062</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65956,7 +65956,7 @@
         <v>46031</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66034,7 +66034,7 @@
         <v>45951</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66107,7 +66107,7 @@
         <v>46062</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66180,7 +66180,7 @@
         <v>45297</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66258,7 +66258,7 @@
         <v>46062</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66331,7 +66331,7 @@
         <v>45880</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66409,7 +66409,7 @@
         <v>46062</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66487,7 +66487,7 @@
         <v>46062</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66560,7 +66560,7 @@
         <v>46084</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66633,7 +66633,7 @@
         <v>46062</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66706,7 +66706,7 @@
         <v>45884</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66784,7 +66784,7 @@
         <v>46062</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66857,7 +66857,7 @@
         <v>46146</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66930,7 +66930,7 @@
         <v>46055</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67003,7 +67003,7 @@
         <v>46064</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67076,7 +67076,7 @@
         <v>46063</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67149,7 +67149,7 @@
         <v>46064</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67222,7 +67222,7 @@
         <v>46064</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67295,7 +67295,7 @@
         <v>46119</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67368,7 +67368,7 @@
         <v>46030</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67441,7 +67441,7 @@
         <v>46038</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67514,7 +67514,7 @@
         <v>46146</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67587,7 +67587,7 @@
         <v>46035</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67660,7 +67660,7 @@
         <v>46064</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67733,7 +67733,7 @@
         <v>46064</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67806,7 +67806,7 @@
         <v>46146</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67879,7 +67879,7 @@
         <v>46146</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67952,7 +67952,7 @@
         <v>46063</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68025,7 +68025,7 @@
         <v>46066</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68103,7 +68103,7 @@
         <v>46066</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68176,7 +68176,7 @@
         <v>46065</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68249,7 +68249,7 @@
         <v>46065</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68327,7 +68327,7 @@
         <v>46069</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68400,7 +68400,7 @@
         <v>46069</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68473,7 +68473,7 @@
         <v>46070</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68546,7 +68546,7 @@
         <v>46070</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68619,7 +68619,7 @@
         <v>46149</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68692,7 +68692,7 @@
         <v>46070</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68765,7 +68765,7 @@
         <v>46149</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68838,7 +68838,7 @@
         <v>46069</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68911,7 +68911,7 @@
         <v>46071</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68984,7 +68984,7 @@
         <v>46071</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69057,7 +69057,7 @@
         <v>46071</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69130,7 +69130,7 @@
         <v>46071</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69203,7 +69203,7 @@
         <v>46071</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69276,7 +69276,7 @@
         <v>46072</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69349,7 +69349,7 @@
         <v>46030</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69427,7 +69427,7 @@
         <v>46035</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69500,7 +69500,7 @@
         <v>46072</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69578,7 +69578,7 @@
         <v>46072</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69651,7 +69651,7 @@
         <v>46076</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69724,7 +69724,7 @@
         <v>46128</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69797,7 +69797,7 @@
         <v>46052</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69870,7 +69870,7 @@
         <v>46026</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69943,7 +69943,7 @@
         <v>46073</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70016,7 +70016,7 @@
         <v>46076</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70089,7 +70089,7 @@
         <v>46073</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70162,7 +70162,7 @@
         <v>46042</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70235,7 +70235,7 @@
         <v>46119</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70308,7 +70308,7 @@
         <v>46078</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70381,7 +70381,7 @@
         <v>45222</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70454,7 +70454,7 @@
         <v>46079</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70527,7 +70527,7 @@
         <v>46079</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70605,7 +70605,7 @@
         <v>46073</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70678,7 +70678,7 @@
         <v>46079</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70751,7 +70751,7 @@
         <v>46080</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70829,7 +70829,7 @@
         <v>46155</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70907,7 +70907,7 @@
         <v>46084</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70980,7 +70980,7 @@
         <v>46084</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71053,7 +71053,7 @@
         <v>46084</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71126,7 +71126,7 @@
         <v>46084</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71199,7 +71199,7 @@
         <v>46084</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71272,7 +71272,7 @@
         <v>46084</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71345,7 +71345,7 @@
         <v>46155</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71418,7 +71418,7 @@
         <v>46087</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71491,7 +71491,7 @@
         <v>46087</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71564,7 +71564,7 @@
         <v>46155</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71637,7 +71637,7 @@
         <v>46043</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71710,7 +71710,7 @@
         <v>46086</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71783,7 +71783,7 @@
         <v>46090</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71856,7 +71856,7 @@
         <v>45545</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71934,7 +71934,7 @@
         <v>46157</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72012,7 +72012,7 @@
         <v>46090</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72085,7 +72085,7 @@
         <v>46160</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72158,7 +72158,7 @@
         <v>46092</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72236,7 +72236,7 @@
         <v>46136</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72309,7 +72309,7 @@
         <v>46093</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72382,7 +72382,7 @@
         <v>46111</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72455,7 +72455,7 @@
         <v>46097</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72528,7 +72528,7 @@
         <v>46051</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72601,7 +72601,7 @@
         <v>46043</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72674,7 +72674,7 @@
         <v>46161</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72747,7 +72747,7 @@
         <v>46164</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72825,7 +72825,7 @@
         <v>46163</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72898,7 +72898,7 @@
         <v>46164</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72976,7 +72976,7 @@
         <v>46168</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73049,7 +73049,7 @@
         <v>46167</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73122,7 +73122,7 @@
         <v>46167</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73195,7 +73195,7 @@
         <v>46169</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73268,7 +73268,7 @@
         <v>46030</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73341,7 +73341,7 @@
         <v>46171</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73419,7 +73419,7 @@
         <v>46171</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73492,7 +73492,7 @@
         <v>46043</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73565,7 +73565,7 @@
         <v>46029</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73638,7 +73638,7 @@
         <v>46170</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73716,7 +73716,7 @@
         <v>46171</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73789,7 +73789,7 @@
         <v>46170</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73862,7 +73862,7 @@
         <v>46175</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73935,7 +73935,7 @@
         <v>46035</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74008,7 +74008,7 @@
         <v>46175</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74086,7 +74086,7 @@
         <v>46176</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74164,7 +74164,7 @@
         <v>46177</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74242,7 +74242,7 @@
         <v>46042</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74315,7 +74315,7 @@
         <v>46079</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74388,7 +74388,7 @@
         <v>46177</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74461,7 +74461,7 @@
         <v>45754</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74539,7 +74539,7 @@
         <v>46084</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74612,7 +74612,7 @@
         <v>46181</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74690,7 +74690,7 @@
         <v>46181</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74768,7 +74768,7 @@
         <v>46051</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74841,7 +74841,7 @@
         <v>46043</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74914,7 +74914,7 @@
         <v>46179</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74987,7 +74987,7 @@
         <v>46178</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75065,7 +75065,7 @@
         <v>46183</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75138,7 +75138,7 @@
         <v>46182</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75216,7 +75216,7 @@
         <v>46185</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75294,7 +75294,7 @@
         <v>46184</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75372,7 +75372,7 @@
         <v>46185</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75445,7 +75445,7 @@
         <v>46188</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75523,7 +75523,7 @@
         <v>46188</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75601,7 +75601,7 @@
         <v>45902</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75674,7 +75674,7 @@
         <v>46188</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75747,7 +75747,7 @@
         <v>46188</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75820,7 +75820,7 @@
         <v>46188</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75893,7 +75893,7 @@
         <v>46195</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75966,7 +75966,7 @@
         <v>46195</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76039,7 +76039,7 @@
         <v>46195</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76112,7 +76112,7 @@
         <v>46197</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76185,7 +76185,7 @@
         <v>46196</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76263,7 +76263,7 @@
         <v>46196</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76336,7 +76336,7 @@
         <v>46196</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76414,7 +76414,7 @@
         <v>46178</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76487,7 +76487,7 @@
         <v>46198</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76560,7 +76560,7 @@
         <v>46198</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76638,7 +76638,7 @@
         <v>46198</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76711,7 +76711,7 @@
         <v>46204</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76789,7 +76789,7 @@
         <v>46209</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76862,7 +76862,7 @@
         <v>46206</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76935,7 +76935,7 @@
         <v>46206</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77008,7 +77008,7 @@
         <v>46206</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77081,7 +77081,7 @@
         <v>46209</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77154,7 +77154,7 @@
         <v>46209</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77227,7 +77227,7 @@
         <v>46209</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77300,7 +77300,7 @@
         <v>46066</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77373,7 +77373,7 @@
         <v>46213</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77446,7 +77446,7 @@
         <v>46213</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77519,7 +77519,7 @@
         <v>46043</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77592,7 +77592,7 @@
         <v>46213</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77665,7 +77665,7 @@
         <v>46184</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77738,7 +77738,7 @@
         <v>46184</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77811,7 +77811,7 @@
         <v>46220</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77889,7 +77889,7 @@
         <v>46223</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77967,7 +77967,7 @@
         <v>46220</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78040,7 +78040,7 @@
         <v>46265</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78118,7 +78118,7 @@
         <v>46220</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78196,7 +78196,7 @@
         <v>46220</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78269,7 +78269,7 @@
         <v>46007</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78342,7 +78342,7 @@
         <v>46007</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78415,7 +78415,7 @@
         <v>46226</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78488,7 +78488,7 @@
         <v>46269</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78561,7 +78561,7 @@
         <v>46272</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78634,7 +78634,7 @@
         <v>46272</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78707,7 +78707,7 @@
         <v>46226</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78780,7 +78780,7 @@
         <v>46274</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78853,7 +78853,7 @@
         <v>46273</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78926,7 +78926,7 @@
         <v>46273</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79004,7 +79004,7 @@
         <v>46273</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79077,7 +79077,7 @@
         <v>46275</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79150,7 +79150,7 @@
         <v>46274</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79223,7 +79223,7 @@
         <v>46280</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79296,7 +79296,7 @@
         <v>46280</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79369,7 +79369,7 @@
         <v>46234</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79447,7 +79447,7 @@
         <v>46282</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79520,7 +79520,7 @@
         <v>46238</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79593,7 +79593,7 @@
         <v>46184</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79666,7 +79666,7 @@
         <v>46185</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79744,7 +79744,7 @@
         <v>46283</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79817,7 +79817,7 @@
         <v>46241</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79890,7 +79890,7 @@
         <v>46288</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79968,7 +79968,7 @@
         <v>46288</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80046,7 +80046,7 @@
         <v>46244</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80119,7 +80119,7 @@
         <v>46244</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80192,7 +80192,7 @@
         <v>46289</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80265,7 +80265,7 @@
         <v>46289</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80343,7 +80343,7 @@
         <v>46069</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80416,7 +80416,7 @@
         <v>46198</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80494,7 +80494,7 @@
         <v>46231</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80567,7 +80567,7 @@
         <v>46294</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80645,7 +80645,7 @@
         <v>46293</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80723,7 +80723,7 @@
         <v>46100</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80796,7 +80796,7 @@
         <v>46293</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80874,7 +80874,7 @@
         <v>46099</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80952,7 +80952,7 @@
         <v>46251</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81030,7 +81030,7 @@
         <v>46253</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81108,7 +81108,7 @@
         <v>46253</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81181,7 +81181,7 @@
         <v>46253</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81259,7 +81259,7 @@
         <v>46296</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81337,7 +81337,7 @@
         <v>46253</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81415,7 +81415,7 @@
         <v>46272</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81488,7 +81488,7 @@
         <v>46202</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81561,7 +81561,7 @@
         <v>46071</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81634,7 +81634,7 @@
         <v>46136</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81707,7 +81707,7 @@
         <v>46255</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81780,7 +81780,7 @@
         <v>46254</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81858,7 +81858,7 @@
         <v>46300</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81936,7 +81936,7 @@
         <v>46127</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -82009,7 +82009,7 @@
         <v>46300</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82087,7 +82087,7 @@
         <v>46302</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82160,7 +82160,7 @@
         <v>46259</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82233,7 +82233,7 @@
         <v>46078</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82306,7 +82306,7 @@
         <v>46184</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82379,7 +82379,7 @@
         <v>46258</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82452,7 +82452,7 @@
         <v>46259</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82530,7 +82530,7 @@
         <v>46079</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82603,7 +82603,7 @@
         <v>46302</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82681,7 +82681,7 @@
         <v>46302</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82759,7 +82759,7 @@
         <v>46302</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82832,7 +82832,7 @@
         <v>46261</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82905,7 +82905,7 @@
         <v>46227</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82978,7 +82978,7 @@
         <v>46031</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83051,7 +83051,7 @@
         <v>46262</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83124,7 +83124,7 @@
         <v>45238</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83202,7 +83202,7 @@
         <v>45238</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83280,7 +83280,7 @@
         <v>44538</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83358,7 +83358,7 @@
         <v>45238</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83436,7 +83436,7 @@
         <v>45670</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83514,7 +83514,7 @@
         <v>45238</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83592,7 +83592,7 @@
         <v>45670</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83670,7 +83670,7 @@
         <v>45238</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83748,7 +83748,7 @@
         <v>44929</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83826,7 +83826,7 @@
         <v>45238</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83904,7 +83904,7 @@
         <v>45386</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83977,7 +83977,7 @@
         <v>45238</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84055,7 +84055,7 @@
         <v>45238</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84133,7 +84133,7 @@
         <v>45670</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84211,7 +84211,7 @@
         <v>45238</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84289,7 +84289,7 @@
         <v>45238</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84367,7 +84367,7 @@
         <v>45238</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84445,7 +84445,7 @@
         <v>45670</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84523,7 +84523,7 @@
         <v>45238</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84601,7 +84601,7 @@
         <v>45670</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84679,7 +84679,7 @@
         <v>45670</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84777,7 +84777,7 @@
         <v>46083</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -84855,7 +84855,7 @@
         <v>45650</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -601,7 +601,7 @@
         <v>45979</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45664</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44643</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45238</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45245</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45960</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45296</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>45478</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>44771</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>46019</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45502</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>44840</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>45734</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45950</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45091</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>46057</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45219</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45595</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>46073</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44545</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>45544</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45323</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45670</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45106</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>45297</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45295</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44884</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45686</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>45502</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>46114</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45994</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>46034</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>46043</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>46043</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>46070</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>46244</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45670</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45728</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44594</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44685</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45296</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>45478</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>44964</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45763</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>45791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45029</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44951</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45631</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>44673</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45799</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45931</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44586</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45673</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44711</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>45834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>45971</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>45320</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>45979</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>45056</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45775</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45734</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>45995</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45072</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>45741</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>46085</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>46177</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>46182</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>46038</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44959</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>44825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44767</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>44711</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44774</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>44876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>44547</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44686</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44781</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44765</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44605</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44713</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>44823</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44879</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44722</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44831</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44816</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44812</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44741</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44546</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>44502</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>44651</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44509</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44552</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44490</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44732</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44739</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44502</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44571</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>44692</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44525</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>44728</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>44691</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44797</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44544</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>44820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44853</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>44830</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44586</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44620</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44728</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>44785</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44692</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44743</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44530</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>44711</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44840</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>44503</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>44764</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>44711</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>44545</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>44728</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44566</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>44634</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44704</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>44692</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>44684</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45044</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>44734</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>45428</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>44728</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>45741</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45148</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44874</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45617</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45037</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45541</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45357</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45419</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45646</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44886</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>44844</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45559</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>44790</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44900</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45364</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45019</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45303</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44869</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45712</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45297</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45667</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45670</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>45670</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>45555</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45573</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>45677</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45324</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44789</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>44765</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>45043</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>45621</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45426</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>44964</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44783</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45103</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45562</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>45635</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45566</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45089</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45183</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45644</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45763</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>44945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44512</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44832</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45541</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45397</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45287</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>44833</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45607</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45617</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45758</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44952</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45622</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45884</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45455</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>44812</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45463</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45232</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>45636</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45719</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>45883</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>45489</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>45169</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44552</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45726</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45622</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45139</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45880</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>44781</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45623</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45884</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45124</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45883</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45103</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45079</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>44862</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45888</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45140</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45271</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45537</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44938</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44938</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>44998</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45888</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45289</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44908</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45890</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45604</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45513</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45504</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>45537</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>44907</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>44502</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45058</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45603</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45603</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>44945</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45041</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45855</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45499</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45896</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45861</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45896</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45896</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45896</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>45897</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45897</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45897</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>45898</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>44713</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45176</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45546</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45579</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45632</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>44939</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44930</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44628</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45601</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45904</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45622</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>44994</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45618</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>45306</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45729</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>45141</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>45343</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45903</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>44560</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>44601</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45636</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45904</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45908</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>45545</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>45908</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45352</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>45042</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>45120</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>45463</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>45909</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45537</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45525</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45777</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>45622</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>45566</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>44599</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45566</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>45596</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>45911</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44601</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>45618</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45271</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45642</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>45783</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>45763</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45763</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45076</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>44603</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>44999</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45915</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>45784</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>45358</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45915</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>44616</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>44900</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>44900</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45498</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>45917</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>45301</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>45149</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>45917</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45917</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45184</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45170</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44503</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45120</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45918</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>44664</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>45918</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>45918</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>45063</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45618</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45533</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45545</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45545</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45422</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45593</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45919</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45260</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45786</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45924</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45462</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>44525</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45923</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>45539</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45754</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>45924</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>45748</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>45579</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45786</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45671</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>45574</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45925</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45791</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45687</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45618</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45758</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45792</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45791</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45055</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>45236</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>45188</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44659</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45506</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>44788</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45791</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45637</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45790</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>44692</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44551</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>45733</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45796</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>44596</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45793</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>45719</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45912</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45631</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>45631</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31737,7 +31737,7 @@
         <v>45175</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>45173</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45170</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>45628</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>44644</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>45631</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>45569</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45191</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>45793</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>45796</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>45309</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>45642</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>45701</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45622</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45686</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>44967</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>44967</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>45499</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>45644</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>45463</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>45931</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>44943</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45532</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45931</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>44915</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45540</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45622</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>44607</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45372</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>45586</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45936</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45936</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>45936</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>45253</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>45799</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>44589</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>45204</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>45936</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>45545</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>44907</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45603</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45131</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>45799</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>45757</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>45799</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>45615</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>44859</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>45802</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>45671</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45937</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>45802</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45176</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>45695</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>45802</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>44953</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>45937</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35940,7 +35940,7 @@
         <v>45636</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>45223</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45197</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>44547</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>45306</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45938</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>44873</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>45938</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>45938</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>45607</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>45607</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44960</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45590</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45938</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>45938</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45938</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>45070</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>44894</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>45639</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>45691</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>45938</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>45938</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45259</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45309</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>45938</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>45938</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45938</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>45687</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>45939</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45939</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>45939</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45939</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>45222</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>45622</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>45812</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45219</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45624</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45622</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>45622</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45946</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>45812</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45946</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45946</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45646</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>44540</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39270,7 +39270,7 @@
         <v>45813</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>45223</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>44699</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>44679</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>45663</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39645,7 +39645,7 @@
         <v>44678</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39723,7 +39723,7 @@
         <v>45149</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>45947</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39874,7 +39874,7 @@
         <v>45817</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45121</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45817</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40103,7 +40103,7 @@
         <v>45817</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45271</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>45582</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45579</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>45950</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45947</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45216</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>44686</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>45947</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45824</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45763</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>45826</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>44960</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41087,7 +41087,7 @@
         <v>45637</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45950</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>45826</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>45950</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>45020</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>45020</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>45642</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>45951</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>45567</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>44952</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>45825</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41910,7 +41910,7 @@
         <v>44952</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>45090</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45208</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>44704</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45827</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45511</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>45140</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>44763</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45832</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>44748</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45938</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45741</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45832</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>45832</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>44704</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>45958</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>45946</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43186,7 +43186,7 @@
         <v>45020</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>45960</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>45959</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>45642</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45632</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45154</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>45062</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>44768</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45236</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>45259</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>44964</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>45439</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45166</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44175,7 +44175,7 @@
         <v>45610</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>45835</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45835</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45835</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>45429</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45965</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45840</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>45646</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>44608</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45142</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45142</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45008,7 +45008,7 @@
         <v>45616</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45081,7 +45081,7 @@
         <v>45554</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45839</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>44720</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>45169</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45968</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45729</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>45841</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>45617</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45841</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>44999</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45841</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44739</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>45846</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>45846</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45971</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>45971</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45636</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45971</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45175</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>44795</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46591,7 +46591,7 @@
         <v>45775</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45971</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>45762</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>45848</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46903,7 +46903,7 @@
         <v>45973</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45848</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>45189</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45034</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>45973</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>45848</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>45973</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45974</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45973</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>45973</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>45974</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>44777</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>44808</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>45695</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>45860</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45859</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>45544</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48179,7 +48179,7 @@
         <v>45041</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45860</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>45313</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>45636</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>44595</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>44987</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>44811</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>44811</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48773,7 +48773,7 @@
         <v>44797</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45625</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48924,7 +48924,7 @@
         <v>45980</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>45980</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>45979</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>44797</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45196</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>44985</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>44886</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>44886</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>44895</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>44830</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>44967</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>45489</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>44789</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45981</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>44783</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45880</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45617</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>45019</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45273</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>45881</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45882</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45345</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45345</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45170</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45758</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50834,7 +50834,7 @@
         <v>45243</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45985</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>46098</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45985</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>46098</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>46099</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>46098</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>46098</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45525</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>44868</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>45985</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45986</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>45399</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>45985</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45985</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>46125</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>46104</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>46104</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45429</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>45177</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52324,7 +52324,7 @@
         <v>45624</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45532</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52470,7 +52470,7 @@
         <v>45072</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>46107</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52621,7 +52621,7 @@
         <v>45068</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>45987</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52767,7 +52767,7 @@
         <v>46111</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>45425</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         <v>46111</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45641</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>45231</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>46111</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         <v>46111</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>46111</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>44960</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>46111</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53527,7 +53527,7 @@
         <v>46112</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53605,7 +53605,7 @@
         <v>46112</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53678,7 +53678,7 @@
         <v>46113</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53756,7 +53756,7 @@
         <v>46113</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53829,7 +53829,7 @@
         <v>44965</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53902,7 +53902,7 @@
         <v>44573</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>46112</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>45743</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>46119</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54199,7 +54199,7 @@
         <v>46118</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54272,7 +54272,7 @@
         <v>46119</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54345,7 +54345,7 @@
         <v>46119</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>46120</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>46120</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54564,7 +54564,7 @@
         <v>46120</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54637,7 +54637,7 @@
         <v>46120</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54710,7 +54710,7 @@
         <v>46120</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54783,7 +54783,7 @@
         <v>46120</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54856,7 +54856,7 @@
         <v>45993</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54934,7 +54934,7 @@
         <v>46120</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45994</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55080,7 +55080,7 @@
         <v>46122</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55153,7 +55153,7 @@
         <v>45995</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>46125</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>46062</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>46126</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>46126</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55528,7 +55528,7 @@
         <v>45999</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55601,7 +55601,7 @@
         <v>46000</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55674,7 +55674,7 @@
         <v>46000</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55747,7 +55747,7 @@
         <v>46126</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>46100</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>45489</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>44824</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>44806</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         <v>44652</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45187</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56268,7 +56268,7 @@
         <v>45336</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56341,7 +56341,7 @@
         <v>44729</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>46134</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56492,7 +56492,7 @@
         <v>46134</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>46006</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56643,7 +56643,7 @@
         <v>46133</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>46003</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45568</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56862,7 +56862,7 @@
         <v>46006</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56935,7 +56935,7 @@
         <v>45246</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45771</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>46008</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57164,7 +57164,7 @@
         <v>45539</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>46136</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57310,7 +57310,7 @@
         <v>45607</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57383,7 +57383,7 @@
         <v>46135</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57456,7 +57456,7 @@
         <v>45089</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57529,7 +57529,7 @@
         <v>45733</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57607,7 +57607,7 @@
         <v>46136</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>46112</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         <v>45544</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57826,7 +57826,7 @@
         <v>46140</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57899,7 +57899,7 @@
         <v>46038</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57972,7 +57972,7 @@
         <v>45950</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58050,7 +58050,7 @@
         <v>45607</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58123,7 +58123,7 @@
         <v>44690</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58196,7 +58196,7 @@
         <v>45382</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58269,7 +58269,7 @@
         <v>45422</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58347,7 +58347,7 @@
         <v>45604</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58425,7 +58425,7 @@
         <v>46021</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>46048</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58581,7 +58581,7 @@
         <v>45546</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58654,7 +58654,7 @@
         <v>45546</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58727,7 +58727,7 @@
         <v>46024</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58800,7 +58800,7 @@
         <v>46026</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58873,7 +58873,7 @@
         <v>45554</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         <v>46030</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59019,7 +59019,7 @@
         <v>45622</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59097,7 +59097,7 @@
         <v>46140</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59175,7 +59175,7 @@
         <v>46030</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59248,7 +59248,7 @@
         <v>46030</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45770</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59394,7 +59394,7 @@
         <v>45770</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59467,7 +59467,7 @@
         <v>45250</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>46139</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59613,7 +59613,7 @@
         <v>45610</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>46034</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59764,7 +59764,7 @@
         <v>46031</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>46035</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59910,7 +59910,7 @@
         <v>46019</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>45509</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60056,7 +60056,7 @@
         <v>46030</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>46035</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60202,7 +60202,7 @@
         <v>46021</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60275,7 +60275,7 @@
         <v>46048</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>46038</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60421,7 +60421,7 @@
         <v>46037</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60494,7 +60494,7 @@
         <v>46054</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60567,7 +60567,7 @@
         <v>46037</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60640,7 +60640,7 @@
         <v>46037</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60713,7 +60713,7 @@
         <v>46038</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>46042</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60859,7 +60859,7 @@
         <v>46042</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60932,7 +60932,7 @@
         <v>46039</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61005,7 +61005,7 @@
         <v>46042</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61078,7 +61078,7 @@
         <v>46033</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61151,7 +61151,7 @@
         <v>46041</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61224,7 +61224,7 @@
         <v>46043</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45252</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61370,7 +61370,7 @@
         <v>46043</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61443,7 +61443,7 @@
         <v>46136</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61516,7 +61516,7 @@
         <v>46043</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61589,7 +61589,7 @@
         <v>46044</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>46043</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61735,7 +61735,7 @@
         <v>46026</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61808,7 +61808,7 @@
         <v>46044</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61881,7 +61881,7 @@
         <v>46043</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61954,7 +61954,7 @@
         <v>45680</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62027,7 +62027,7 @@
         <v>46043</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62100,7 +62100,7 @@
         <v>46043</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>46044</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62246,7 +62246,7 @@
         <v>46044</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62319,7 +62319,7 @@
         <v>46043</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62392,7 +62392,7 @@
         <v>46043</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>46044</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62538,7 +62538,7 @@
         <v>45037</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62611,7 +62611,7 @@
         <v>45915</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62684,7 +62684,7 @@
         <v>45001</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62757,7 +62757,7 @@
         <v>46048</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62830,7 +62830,7 @@
         <v>46048</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62903,7 +62903,7 @@
         <v>46048</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62976,7 +62976,7 @@
         <v>46045</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63049,7 +63049,7 @@
         <v>46043</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63122,7 +63122,7 @@
         <v>46043</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63195,7 +63195,7 @@
         <v>45824</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>46045</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>46021</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63419,7 +63419,7 @@
         <v>45434</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>46048</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>46073</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63643,7 +63643,7 @@
         <v>45373</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63721,7 +63721,7 @@
         <v>46069</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63794,7 +63794,7 @@
         <v>46045</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63867,7 +63867,7 @@
         <v>46050</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63945,7 +63945,7 @@
         <v>46048</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64023,7 +64023,7 @@
         <v>46098</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64096,7 +64096,7 @@
         <v>45497</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64174,7 +64174,7 @@
         <v>46070</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64247,7 +64247,7 @@
         <v>46050</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>46050</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64398,7 +64398,7 @@
         <v>44788</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64471,7 +64471,7 @@
         <v>45163</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64549,7 +64549,7 @@
         <v>46055</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64622,7 +64622,7 @@
         <v>46050</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64700,7 +64700,7 @@
         <v>46052</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64773,7 +64773,7 @@
         <v>46051</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64846,7 +64846,7 @@
         <v>46051</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64919,7 +64919,7 @@
         <v>46051</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64992,7 +64992,7 @@
         <v>46051</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65065,7 +65065,7 @@
         <v>46056</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65138,7 +65138,7 @@
         <v>46053</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65211,7 +65211,7 @@
         <v>46053</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65284,7 +65284,7 @@
         <v>46056</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65357,7 +65357,7 @@
         <v>46055</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65430,7 +65430,7 @@
         <v>46055</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65508,7 +65508,7 @@
         <v>46055</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65586,7 +65586,7 @@
         <v>46057</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65659,7 +65659,7 @@
         <v>46057</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65732,7 +65732,7 @@
         <v>46057</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65805,7 +65805,7 @@
         <v>45789</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65883,7 +65883,7 @@
         <v>46062</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65956,7 +65956,7 @@
         <v>46031</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66034,7 +66034,7 @@
         <v>45951</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66107,7 +66107,7 @@
         <v>46062</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66180,7 +66180,7 @@
         <v>45297</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66258,7 +66258,7 @@
         <v>46062</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66331,7 +66331,7 @@
         <v>45880</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66409,7 +66409,7 @@
         <v>46062</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66487,7 +66487,7 @@
         <v>46062</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66560,7 +66560,7 @@
         <v>46084</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66633,7 +66633,7 @@
         <v>46062</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66706,7 +66706,7 @@
         <v>45884</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66784,7 +66784,7 @@
         <v>46062</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66857,7 +66857,7 @@
         <v>46146</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66930,7 +66930,7 @@
         <v>46055</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67003,7 +67003,7 @@
         <v>46064</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67076,7 +67076,7 @@
         <v>46063</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -67149,7 +67149,7 @@
         <v>46064</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67222,7 +67222,7 @@
         <v>46064</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67295,7 +67295,7 @@
         <v>46119</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67368,7 +67368,7 @@
         <v>46030</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67441,7 +67441,7 @@
         <v>46038</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67514,7 +67514,7 @@
         <v>46146</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67587,7 +67587,7 @@
         <v>46035</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67660,7 +67660,7 @@
         <v>46064</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67733,7 +67733,7 @@
         <v>46064</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67806,7 +67806,7 @@
         <v>46146</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67879,7 +67879,7 @@
         <v>46146</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67952,7 +67952,7 @@
         <v>46063</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -68025,7 +68025,7 @@
         <v>46066</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -68103,7 +68103,7 @@
         <v>46066</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68176,7 +68176,7 @@
         <v>46065</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68249,7 +68249,7 @@
         <v>46065</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68327,7 +68327,7 @@
         <v>46069</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68400,7 +68400,7 @@
         <v>46069</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68473,7 +68473,7 @@
         <v>46070</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68546,7 +68546,7 @@
         <v>46070</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68619,7 +68619,7 @@
         <v>46149</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68692,7 +68692,7 @@
         <v>46070</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68765,7 +68765,7 @@
         <v>46149</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68838,7 +68838,7 @@
         <v>46069</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68911,7 +68911,7 @@
         <v>46071</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68984,7 +68984,7 @@
         <v>46071</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -69057,7 +69057,7 @@
         <v>46071</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -69130,7 +69130,7 @@
         <v>46071</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69203,7 +69203,7 @@
         <v>46071</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69276,7 +69276,7 @@
         <v>46072</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69349,7 +69349,7 @@
         <v>46030</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69427,7 +69427,7 @@
         <v>46035</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69500,7 +69500,7 @@
         <v>46072</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69578,7 +69578,7 @@
         <v>46072</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69651,7 +69651,7 @@
         <v>46076</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69724,7 +69724,7 @@
         <v>46128</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69797,7 +69797,7 @@
         <v>46052</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69870,7 +69870,7 @@
         <v>46026</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69943,7 +69943,7 @@
         <v>46073</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -70016,7 +70016,7 @@
         <v>46076</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -70089,7 +70089,7 @@
         <v>46073</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70162,7 +70162,7 @@
         <v>46042</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70235,7 +70235,7 @@
         <v>46119</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70308,7 +70308,7 @@
         <v>46078</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70381,7 +70381,7 @@
         <v>45222</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70454,7 +70454,7 @@
         <v>46079</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70527,7 +70527,7 @@
         <v>46079</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70605,7 +70605,7 @@
         <v>46073</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70678,7 +70678,7 @@
         <v>46079</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70751,7 +70751,7 @@
         <v>46080</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70829,7 +70829,7 @@
         <v>46155</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70907,7 +70907,7 @@
         <v>46084</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70980,7 +70980,7 @@
         <v>46084</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -71053,7 +71053,7 @@
         <v>46084</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -71126,7 +71126,7 @@
         <v>46084</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71199,7 +71199,7 @@
         <v>46084</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71272,7 +71272,7 @@
         <v>46084</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71345,7 +71345,7 @@
         <v>46155</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71418,7 +71418,7 @@
         <v>46087</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71491,7 +71491,7 @@
         <v>46087</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71564,7 +71564,7 @@
         <v>46155</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71637,7 +71637,7 @@
         <v>46043</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71710,7 +71710,7 @@
         <v>46086</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71783,7 +71783,7 @@
         <v>46090</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71856,7 +71856,7 @@
         <v>45545</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71934,7 +71934,7 @@
         <v>46157</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -72012,7 +72012,7 @@
         <v>46090</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -72085,7 +72085,7 @@
         <v>46160</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72158,7 +72158,7 @@
         <v>46092</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72236,7 +72236,7 @@
         <v>46136</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72309,7 +72309,7 @@
         <v>46093</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72382,7 +72382,7 @@
         <v>46111</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72455,7 +72455,7 @@
         <v>46097</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72528,7 +72528,7 @@
         <v>46051</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72601,7 +72601,7 @@
         <v>46043</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72674,7 +72674,7 @@
         <v>46161</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72747,7 +72747,7 @@
         <v>46164</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72825,7 +72825,7 @@
         <v>46163</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72898,7 +72898,7 @@
         <v>46164</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72976,7 +72976,7 @@
         <v>46168</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -73049,7 +73049,7 @@
         <v>46167</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73122,7 +73122,7 @@
         <v>46167</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73195,7 +73195,7 @@
         <v>46169</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73268,7 +73268,7 @@
         <v>46030</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73341,7 +73341,7 @@
         <v>46171</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73419,7 +73419,7 @@
         <v>46171</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73492,7 +73492,7 @@
         <v>46043</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73565,7 +73565,7 @@
         <v>46029</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73638,7 +73638,7 @@
         <v>46170</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73716,7 +73716,7 @@
         <v>46171</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73789,7 +73789,7 @@
         <v>46170</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73862,7 +73862,7 @@
         <v>46175</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73935,7 +73935,7 @@
         <v>46035</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -74008,7 +74008,7 @@
         <v>46175</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74086,7 +74086,7 @@
         <v>46176</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74164,7 +74164,7 @@
         <v>46177</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74242,7 +74242,7 @@
         <v>46042</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74315,7 +74315,7 @@
         <v>46079</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74388,7 +74388,7 @@
         <v>46177</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74461,7 +74461,7 @@
         <v>45754</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74539,7 +74539,7 @@
         <v>46084</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74612,7 +74612,7 @@
         <v>46181</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74690,7 +74690,7 @@
         <v>46181</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74768,7 +74768,7 @@
         <v>46051</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74841,7 +74841,7 @@
         <v>46043</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74914,7 +74914,7 @@
         <v>46179</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74987,7 +74987,7 @@
         <v>46178</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -75065,7 +75065,7 @@
         <v>46183</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75138,7 +75138,7 @@
         <v>46182</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75216,7 +75216,7 @@
         <v>46185</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75294,7 +75294,7 @@
         <v>46184</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75372,7 +75372,7 @@
         <v>46185</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75445,7 +75445,7 @@
         <v>46188</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75523,7 +75523,7 @@
         <v>46188</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75601,7 +75601,7 @@
         <v>45902</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75674,7 +75674,7 @@
         <v>46188</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75747,7 +75747,7 @@
         <v>46188</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75820,7 +75820,7 @@
         <v>46188</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75893,7 +75893,7 @@
         <v>46195</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75966,7 +75966,7 @@
         <v>46195</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -76039,7 +76039,7 @@
         <v>46195</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76112,7 +76112,7 @@
         <v>46197</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76185,7 +76185,7 @@
         <v>46196</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76263,7 +76263,7 @@
         <v>46196</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76336,7 +76336,7 @@
         <v>46196</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76414,7 +76414,7 @@
         <v>46178</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76487,7 +76487,7 @@
         <v>46198</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76560,7 +76560,7 @@
         <v>46198</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76638,7 +76638,7 @@
         <v>46198</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76711,7 +76711,7 @@
         <v>46204</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76789,7 +76789,7 @@
         <v>46209</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76862,7 +76862,7 @@
         <v>46206</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76935,7 +76935,7 @@
         <v>46206</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -77008,7 +77008,7 @@
         <v>46206</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77081,7 +77081,7 @@
         <v>46209</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77154,7 +77154,7 @@
         <v>46209</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77227,7 +77227,7 @@
         <v>46209</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77300,7 +77300,7 @@
         <v>46066</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77373,7 +77373,7 @@
         <v>46213</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77446,7 +77446,7 @@
         <v>46213</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77519,7 +77519,7 @@
         <v>46043</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77592,7 +77592,7 @@
         <v>46213</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77665,7 +77665,7 @@
         <v>46184</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77738,7 +77738,7 @@
         <v>46184</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77811,7 +77811,7 @@
         <v>46220</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77889,7 +77889,7 @@
         <v>46223</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77967,7 +77967,7 @@
         <v>46220</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -78040,7 +78040,7 @@
         <v>46265</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78118,7 +78118,7 @@
         <v>46220</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78196,7 +78196,7 @@
         <v>46220</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78269,7 +78269,7 @@
         <v>46007</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78342,7 +78342,7 @@
         <v>46007</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78415,7 +78415,7 @@
         <v>46226</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78488,7 +78488,7 @@
         <v>46269</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78561,7 +78561,7 @@
         <v>46272</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78634,7 +78634,7 @@
         <v>46272</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78707,7 +78707,7 @@
         <v>46226</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78780,7 +78780,7 @@
         <v>46274</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78853,7 +78853,7 @@
         <v>46273</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78926,7 +78926,7 @@
         <v>46273</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -79004,7 +79004,7 @@
         <v>46273</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79077,7 +79077,7 @@
         <v>46275</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79150,7 +79150,7 @@
         <v>46274</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79223,7 +79223,7 @@
         <v>46280</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79296,7 +79296,7 @@
         <v>46280</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79369,7 +79369,7 @@
         <v>46234</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79447,7 +79447,7 @@
         <v>46282</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79520,7 +79520,7 @@
         <v>46238</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79593,7 +79593,7 @@
         <v>46184</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79666,7 +79666,7 @@
         <v>46185</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79744,7 +79744,7 @@
         <v>46283</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79817,7 +79817,7 @@
         <v>46241</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79890,7 +79890,7 @@
         <v>46288</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79968,7 +79968,7 @@
         <v>46288</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80046,7 +80046,7 @@
         <v>46244</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80119,7 +80119,7 @@
         <v>46244</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80192,7 +80192,7 @@
         <v>46289</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80265,7 +80265,7 @@
         <v>46289</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80343,7 +80343,7 @@
         <v>46069</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80416,7 +80416,7 @@
         <v>46198</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80494,7 +80494,7 @@
         <v>46231</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80567,7 +80567,7 @@
         <v>46294</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80645,7 +80645,7 @@
         <v>46293</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80723,7 +80723,7 @@
         <v>46100</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80796,7 +80796,7 @@
         <v>46293</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80874,7 +80874,7 @@
         <v>46099</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80952,7 +80952,7 @@
         <v>46251</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81030,7 +81030,7 @@
         <v>46253</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81108,7 +81108,7 @@
         <v>46253</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81181,7 +81181,7 @@
         <v>46253</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81259,7 +81259,7 @@
         <v>46296</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81337,7 +81337,7 @@
         <v>46253</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81415,7 +81415,7 @@
         <v>46272</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81488,7 +81488,7 @@
         <v>46202</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81561,7 +81561,7 @@
         <v>46071</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81634,7 +81634,7 @@
         <v>46136</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81707,7 +81707,7 @@
         <v>46255</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81780,7 +81780,7 @@
         <v>46254</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81858,7 +81858,7 @@
         <v>46300</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81936,7 +81936,7 @@
         <v>46127</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -82009,7 +82009,7 @@
         <v>46300</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82087,7 +82087,7 @@
         <v>46302</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82160,7 +82160,7 @@
         <v>46259</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82233,7 +82233,7 @@
         <v>46078</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82306,7 +82306,7 @@
         <v>46184</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82379,7 +82379,7 @@
         <v>46258</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82452,7 +82452,7 @@
         <v>46259</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82530,7 +82530,7 @@
         <v>46079</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82603,7 +82603,7 @@
         <v>46302</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82681,7 +82681,7 @@
         <v>46302</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82759,7 +82759,7 @@
         <v>46302</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82832,7 +82832,7 @@
         <v>46261</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82905,7 +82905,7 @@
         <v>46227</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82978,7 +82978,7 @@
         <v>46031</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83051,7 +83051,7 @@
         <v>46262</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83124,7 +83124,7 @@
         <v>45238</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83202,7 +83202,7 @@
         <v>45238</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83280,7 +83280,7 @@
         <v>44538</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83358,7 +83358,7 @@
         <v>45238</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83436,7 +83436,7 @@
         <v>45670</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83514,7 +83514,7 @@
         <v>45238</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83592,7 +83592,7 @@
         <v>45670</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83670,7 +83670,7 @@
         <v>45238</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83748,7 +83748,7 @@
         <v>44929</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83826,7 +83826,7 @@
         <v>45238</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83904,7 +83904,7 @@
         <v>45386</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83977,7 +83977,7 @@
         <v>45238</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84055,7 +84055,7 @@
         <v>45238</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84133,7 +84133,7 @@
         <v>45670</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84211,7 +84211,7 @@
         <v>45238</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84289,7 +84289,7 @@
         <v>45238</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84367,7 +84367,7 @@
         <v>45238</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84445,7 +84445,7 @@
         <v>45670</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84523,7 +84523,7 @@
         <v>45238</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84601,7 +84601,7 @@
         <v>45670</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84679,7 +84679,7 @@
         <v>45670</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84777,7 +84777,7 @@
         <v>46083</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -84855,7 +84855,7 @@
         <v>45650</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -601,7 +601,7 @@
         <v>45979</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45664</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44643</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45238</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45245</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45960</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>44771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>46019</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45502</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>44840</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>45734</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>45091</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45595</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>45950</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45981</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45219</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>46073</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45544</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44972</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45323</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45670</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45686</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>45502</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45297</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>45994</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46034</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>46043</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>46043</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>46070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>46114</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>45295</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>44884</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45106</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>46244</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45670</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45728</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44594</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44685</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45478</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45631</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>44951</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45029</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>45056</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44964</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44673</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>45931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>44586</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45296</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45971</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>45979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>45995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>46085</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>46177</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45741</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>46182</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>45072</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45673</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45320</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>45734</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>46038</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>45775</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45763</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45791</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45799</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>45834</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44959</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>44825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44767</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>44711</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44774</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>44876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>44547</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44686</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44781</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44765</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44605</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44713</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>44823</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44879</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44722</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44816</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44831</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44741</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44812</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44546</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>44502</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>44651</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44509</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44739</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>44692</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>44691</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44797</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44544</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44853</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44545</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>44634</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>44732</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>44490</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44525</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44830</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44692</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44620</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44743</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44711</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44840</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44764</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44552</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44728</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>44831</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44728</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44571</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>44502</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>44820</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>44586</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>44728</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>44530</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>44503</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44711</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>44566</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44785</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44704</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>44684</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>44728</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>44692</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44659</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>45163</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>45775</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>44692</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45644</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45289</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45103</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45726</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44886</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45573</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45041</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45188</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>44503</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45068</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>45041</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44862</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45625</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>44599</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45631</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>45139</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>44894</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45352</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>45170</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>44994</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45642</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>45070</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45169</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>44601</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>44830</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>45621</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45345</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>45345</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>44895</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>44900</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45001</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45762</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>44783</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45691</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45253</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44795</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45309</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45149</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45533</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45610</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45622</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45336</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>45343</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>44886</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45397</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45566</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>44806</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45559</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45622</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45306</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45680</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45555</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44945</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45511</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>45646</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45426</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45176</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44678</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45562</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45037</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>45554</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45637</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>45670</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45622</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45622</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>44560</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45196</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>45243</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45419</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45623</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45425</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45183</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45236</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45189</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>44907</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44998</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>45148</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>45642</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>44781</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45758</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>44608</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45120</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45541</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44811</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45131</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45271</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45216</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44768</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45463</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45089</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45671</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>45677</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45646</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45184</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45499</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45883</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>45915</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>46043</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>46019</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>46033</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>45884</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>44664</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45824</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45176</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>45610</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45596</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45884</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45103</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45166</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44573</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44945</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45497</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>45223</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>46139</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45888</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>46048</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>46136</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>45888</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>45525</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45434</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>44748</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45890</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>46043</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45044</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45701</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>46136</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>46135</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>45855</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>45897</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>45897</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45896</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>45861</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45896</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45896</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>45896</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45509</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45897</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>45898</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>46048</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>46026</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>45951</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45884</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>46055</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>46021</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>46140</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>46031</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44788</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>46084</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>46054</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>45903</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>46070</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>46048</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45880</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>46140</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>46098</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>46038</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>45904</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45789</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>45904</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>45908</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45636</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45232</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45909</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45908</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45250</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45911</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>45915</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>45169</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>44886</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45546</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>45546</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45915</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>46146</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>45917</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>46119</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45917</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>46146</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>46035</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45917</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45919</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>46146</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45918</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45918</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45259</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45918</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>46146</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>46038</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45923</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>46055</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>44874</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>46030</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45924</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>44833</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45924</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>45925</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45170</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>44607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>46149</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>46149</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>44824</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44644</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>45912</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>45931</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>46128</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>45931</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>45222</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45936</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>45936</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>45936</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30381,7 +30381,7 @@
         <v>45936</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>45324</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45937</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>45938</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>45566</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30746,7 +30746,7 @@
         <v>45938</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>45938</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>45938</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>45939</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>45938</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>45938</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45489</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45938</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>45938</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>45938</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45939</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45938</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>45544</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>45937</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>45939</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>45939</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>45938</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>46155</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32065,7 +32065,7 @@
         <v>46119</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45946</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45947</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45946</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>45641</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>45946</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45642</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>45947</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45947</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45938</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>46042</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45950</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>46155</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45950</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>46026</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>45950</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45951</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>44964</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>46155</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45579</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>46035</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45429</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45429</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45946</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>46052</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>46157</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44915</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45042</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45537</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>45958</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>45959</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>45960</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>46161</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45618</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>45965</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>46160</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>45313</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>45712</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>45089</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45079</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45971</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>45971</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45208</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>46043</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45043</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>45971</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>45968</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45971</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>44832</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>46163</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>45973</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45973</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45973</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45222</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45973</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>45973</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>44686</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>44601</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45741</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>46051</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44704</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>45974</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>45636</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>46136</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36832,7 +36832,7 @@
         <v>45974</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         <v>45979</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
         <v>45141</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37056,7 +37056,7 @@
         <v>46111</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44652</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>45297</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45624</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45729</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>45743</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>45981</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45980</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45980</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>46164</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>46167</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45985</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>45303</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>44783</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>45985</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>45568</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45985</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>45985</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45986</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>46164</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45545</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45537</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45985</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45987</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>45273</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>46167</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>45748</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>44616</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>46169</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45020</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45020</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45197</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>45993</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>44987</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45428</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45607</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45995</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45994</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>45999</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45631</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>45618</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45546</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>46000</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>46168</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>44512</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40421,7 +40421,7 @@
         <v>46000</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>45246</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>46003</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>46170</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>46170</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>45628</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>44811</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>45603</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45603</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>44790</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45579</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>46006</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>46006</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45399</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>45635</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45525</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>45537</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>46035</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>46008</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>45622</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45622</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45667</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45670</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45287</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>45455</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45950</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>44596</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>46029</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42510,7 +42510,7 @@
         <v>46030</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42583,7 +42583,7 @@
         <v>46171</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>46171</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>44777</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>46021</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>46171</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>46043</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>45566</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>46024</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>46026</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45758</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>46176</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>45618</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45686</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>46030</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>46031</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>46030</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>46030</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>46175</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>46034</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>46175</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>44552</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>45604</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>46035</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>46035</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>46037</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>46037</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>46051</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46043</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>46042</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>46037</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44818,7 +44818,7 @@
         <v>46079</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44891,7 +44891,7 @@
         <v>46041</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>46038</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>46038</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>46039</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>46177</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>46178</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>46043</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>44797</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>46043</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>46043</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>46043</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>46043</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>46043</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>46043</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45928,7 +45928,7 @@
         <v>46179</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46001,7 +46001,7 @@
         <v>46177</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>46042</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>45532</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>46042</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>46042</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>46043</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>46043</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46512,7 +46512,7 @@
         <v>44812</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>46044</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>46044</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45754</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>46044</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>46045</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46960,7 +46960,7 @@
         <v>46045</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>46045</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>46044</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>46044</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45601</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>46069</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47398,7 +47398,7 @@
         <v>46048</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>46048</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>46084</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47617,7 +47617,7 @@
         <v>45499</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>46048</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>45140</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
         <v>46048</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>46051</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>46051</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>46050</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>46050</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>46050</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>46050</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>46051</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>46051</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>46181</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>46053</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48659,7 +48659,7 @@
         <v>46055</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45231</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48810,7 +48810,7 @@
         <v>46055</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48888,7 +48888,7 @@
         <v>46055</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>46052</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49034,7 +49034,7 @@
         <v>46053</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>46182</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>46056</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>46057</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>46181</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49409,7 +49409,7 @@
         <v>46057</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>46057</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45671</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49633,7 +49633,7 @@
         <v>46056</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49706,7 +49706,7 @@
         <v>45297</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49784,7 +49784,7 @@
         <v>46183</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
         <v>46062</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>46062</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50003,7 +50003,7 @@
         <v>46062</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>46062</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>46062</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>46062</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>46063</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>46062</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>45090</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50519,7 +50519,7 @@
         <v>46063</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>44797</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>46064</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50743,7 +50743,7 @@
         <v>46064</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>46065</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>46064</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>46064</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>46065</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>46064</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>46069</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51259,7 +51259,7 @@
         <v>46066</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51332,7 +51332,7 @@
         <v>46184</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>46069</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51483,7 +51483,7 @@
         <v>45072</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>46188</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>46066</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         <v>46069</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>46188</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51858,7 +51858,7 @@
         <v>46030</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51936,7 +51936,7 @@
         <v>46071</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>46071</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>46071</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52155,7 +52155,7 @@
         <v>46070</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52228,7 +52228,7 @@
         <v>46070</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>46185</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>46071</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52447,7 +52447,7 @@
         <v>46071</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>46070</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>46073</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52666,7 +52666,7 @@
         <v>46072</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>46072</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>46188</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>46188</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52963,7 +52963,7 @@
         <v>46073</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53036,7 +53036,7 @@
         <v>46072</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53114,7 +53114,7 @@
         <v>44960</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>46076</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53265,7 +53265,7 @@
         <v>45170</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>45121</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>46073</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53489,7 +53489,7 @@
         <v>46076</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53562,7 +53562,7 @@
         <v>46078</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>46079</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>46185</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>46079</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>46188</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>46079</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>46080</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54088,7 +54088,7 @@
         <v>46084</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45058</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54234,7 +54234,7 @@
         <v>46084</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54307,7 +54307,7 @@
         <v>46084</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>46084</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54453,7 +54453,7 @@
         <v>46084</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54526,7 +54526,7 @@
         <v>46084</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54599,7 +54599,7 @@
         <v>45541</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54677,7 +54677,7 @@
         <v>46086</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>46043</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>46087</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
         <v>45733</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54974,7 +54974,7 @@
         <v>46087</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55047,7 +55047,7 @@
         <v>45757</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55125,7 +55125,7 @@
         <v>46090</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55198,7 +55198,7 @@
         <v>45902</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55271,7 +55271,7 @@
         <v>46090</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55344,7 +55344,7 @@
         <v>45373</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55422,7 +55422,7 @@
         <v>45636</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55500,7 +55500,7 @@
         <v>46092</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55578,7 +55578,7 @@
         <v>45545</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55656,7 +55656,7 @@
         <v>45034</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>44690</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55807,7 +55807,7 @@
         <v>46093</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55880,7 +55880,7 @@
         <v>46098</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55953,7 +55953,7 @@
         <v>46098</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56026,7 +56026,7 @@
         <v>46098</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>46195</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>46097</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>46098</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>46099</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>46196</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56479,7 +56479,7 @@
         <v>45579</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>45140</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>46195</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56698,7 +56698,7 @@
         <v>46195</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>46104</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>46104</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56917,7 +56917,7 @@
         <v>46125</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56990,7 +56990,7 @@
         <v>46196</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57068,7 +57068,7 @@
         <v>45204</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57141,7 +57141,7 @@
         <v>46196</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57219,7 +57219,7 @@
         <v>45631</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>46107</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>44930</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         <v>44938</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57526,7 +57526,7 @@
         <v>46111</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57604,7 +57604,7 @@
         <v>46111</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57677,7 +57677,7 @@
         <v>46111</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>46112</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57828,7 +57828,7 @@
         <v>46112</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>46112</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57979,7 +57979,7 @@
         <v>46111</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>46111</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58135,7 +58135,7 @@
         <v>46111</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58213,7 +58213,7 @@
         <v>46198</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>44960</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58364,7 +58364,7 @@
         <v>46198</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>46178</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58510,7 +58510,7 @@
         <v>46197</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58583,7 +58583,7 @@
         <v>45364</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>46113</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58739,7 +58739,7 @@
         <v>46113</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58812,7 +58812,7 @@
         <v>45539</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58885,7 +58885,7 @@
         <v>46198</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58958,7 +58958,7 @@
         <v>46118</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59031,7 +59031,7 @@
         <v>46120</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59104,7 +59104,7 @@
         <v>46119</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59177,7 +59177,7 @@
         <v>46119</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59250,7 +59250,7 @@
         <v>46120</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59323,7 +59323,7 @@
         <v>46119</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45358</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59474,7 +59474,7 @@
         <v>46120</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59547,7 +59547,7 @@
         <v>46120</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59620,7 +59620,7 @@
         <v>46120</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59693,7 +59693,7 @@
         <v>46120</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59766,7 +59766,7 @@
         <v>44952</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>46120</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59917,7 +59917,7 @@
         <v>46122</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>46126</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60068,7 +60068,7 @@
         <v>46126</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60146,7 +60146,7 @@
         <v>46062</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60219,7 +60219,7 @@
         <v>46125</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60292,7 +60292,7 @@
         <v>45582</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>46126</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60448,7 +60448,7 @@
         <v>44729</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60521,7 +60521,7 @@
         <v>46100</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60594,7 +60594,7 @@
         <v>44713</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>44765</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>46133</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60813,7 +60813,7 @@
         <v>45545</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60891,7 +60891,7 @@
         <v>46112</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60964,7 +60964,7 @@
         <v>45771</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61042,7 +61042,7 @@
         <v>46134</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61120,7 +61120,7 @@
         <v>46134</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61198,7 +61198,7 @@
         <v>45637</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61271,7 +61271,7 @@
         <v>45063</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61349,7 +61349,7 @@
         <v>46204</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61427,7 +61427,7 @@
         <v>46136</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61500,7 +61500,7 @@
         <v>45037</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61573,7 +61573,7 @@
         <v>45149</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61646,7 +61646,7 @@
         <v>45175</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>46030</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61792,7 +61792,7 @@
         <v>46073</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61865,7 +61865,7 @@
         <v>46021</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61938,7 +61938,7 @@
         <v>46206</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62011,7 +62011,7 @@
         <v>44900</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62089,7 +62089,7 @@
         <v>44900</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62167,7 +62167,7 @@
         <v>44704</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62240,7 +62240,7 @@
         <v>45607</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62318,7 +62318,7 @@
         <v>45607</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62396,7 +62396,7 @@
         <v>45616</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62469,7 +62469,7 @@
         <v>46206</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62542,7 +62542,7 @@
         <v>46206</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62615,7 +62615,7 @@
         <v>45590</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62688,7 +62688,7 @@
         <v>44763</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62766,7 +62766,7 @@
         <v>45154</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62839,7 +62839,7 @@
         <v>45504</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62912,7 +62912,7 @@
         <v>45219</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62990,7 +62990,7 @@
         <v>45695</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63063,7 +63063,7 @@
         <v>46209</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63136,7 +63136,7 @@
         <v>44679</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63214,7 +63214,7 @@
         <v>45617</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63292,7 +63292,7 @@
         <v>44628</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63365,7 +63365,7 @@
         <v>46209</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63438,7 +63438,7 @@
         <v>46209</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63511,7 +63511,7 @@
         <v>46209</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63584,7 +63584,7 @@
         <v>45607</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63657,7 +63657,7 @@
         <v>46213</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63730,7 +63730,7 @@
         <v>46213</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63803,7 +63803,7 @@
         <v>45617</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63881,7 +63881,7 @@
         <v>45719</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63959,7 +63959,7 @@
         <v>46066</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64032,7 +64032,7 @@
         <v>45729</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64110,7 +64110,7 @@
         <v>44739</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64183,7 +64183,7 @@
         <v>46213</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64256,7 +64256,7 @@
         <v>46043</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64329,7 +64329,7 @@
         <v>45574</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64402,7 +64402,7 @@
         <v>45173</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64475,7 +64475,7 @@
         <v>45644</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64553,7 +64553,7 @@
         <v>46184</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64626,7 +64626,7 @@
         <v>46184</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64699,7 +64699,7 @@
         <v>44938</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64772,7 +64772,7 @@
         <v>45187</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64845,7 +64845,7 @@
         <v>46220</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64918,7 +64918,7 @@
         <v>46220</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64996,7 +64996,7 @@
         <v>46220</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65074,7 +65074,7 @@
         <v>46220</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65147,7 +65147,7 @@
         <v>45062</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65220,7 +65220,7 @@
         <v>46223</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65298,7 +65298,7 @@
         <v>46226</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65371,7 +65371,7 @@
         <v>44952</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65449,7 +65449,7 @@
         <v>44952</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65527,7 +65527,7 @@
         <v>46226</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65600,7 +65600,7 @@
         <v>45513</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65678,7 +65678,7 @@
         <v>44551</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65751,7 +65751,7 @@
         <v>45142</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65829,7 +65829,7 @@
         <v>46273</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65907,7 +65907,7 @@
         <v>45142</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65985,7 +65985,7 @@
         <v>46272</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66058,7 +66058,7 @@
         <v>46273</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66131,7 +66131,7 @@
         <v>46272</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66204,7 +66204,7 @@
         <v>45462</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66277,7 +66277,7 @@
         <v>45770</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66350,7 +66350,7 @@
         <v>46273</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66423,7 +66423,7 @@
         <v>44868</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66501,7 +66501,7 @@
         <v>46275</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66574,7 +66574,7 @@
         <v>46274</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66647,7 +66647,7 @@
         <v>45252</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66720,7 +66720,7 @@
         <v>46274</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66793,7 +66793,7 @@
         <v>45603</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66871,7 +66871,7 @@
         <v>45489</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66949,7 +66949,7 @@
         <v>45463</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67027,7 +67027,7 @@
         <v>45617</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67105,7 +67105,7 @@
         <v>44869</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67178,7 +67178,7 @@
         <v>46234</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67256,7 +67256,7 @@
         <v>45687</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67329,7 +67329,7 @@
         <v>44999</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67402,7 +67402,7 @@
         <v>44965</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67475,7 +67475,7 @@
         <v>44939</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67548,7 +67548,7 @@
         <v>45639</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67621,7 +67621,7 @@
         <v>45020</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67699,7 +67699,7 @@
         <v>45271</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67777,7 +67777,7 @@
         <v>45642</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67850,7 +67850,7 @@
         <v>45632</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67928,7 +67928,7 @@
         <v>46280</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68001,7 +68001,7 @@
         <v>46280</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68074,7 +68074,7 @@
         <v>44547</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68147,7 +68147,7 @@
         <v>45223</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68225,7 +68225,7 @@
         <v>46238</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68298,7 +68298,7 @@
         <v>44589</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68371,7 +68371,7 @@
         <v>45593</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68444,7 +68444,7 @@
         <v>44985</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68522,7 +68522,7 @@
         <v>46283</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68595,7 +68595,7 @@
         <v>46184</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68668,7 +68668,7 @@
         <v>45622</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68746,7 +68746,7 @@
         <v>45372</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68824,7 +68824,7 @@
         <v>45019</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68897,7 +68897,7 @@
         <v>45770</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68970,7 +68970,7 @@
         <v>46282</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69043,7 +69043,7 @@
         <v>46185</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69121,7 +69121,7 @@
         <v>44720</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69194,7 +69194,7 @@
         <v>45382</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69267,7 +69267,7 @@
         <v>44844</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69345,7 +69345,7 @@
         <v>44967</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69423,7 +69423,7 @@
         <v>44943</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69496,7 +69496,7 @@
         <v>46244</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69569,7 +69569,7 @@
         <v>45567</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69642,7 +69642,7 @@
         <v>45636</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69720,7 +69720,7 @@
         <v>45624</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69793,7 +69793,7 @@
         <v>45632</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69871,7 +69871,7 @@
         <v>46244</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69944,7 +69944,7 @@
         <v>46241</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70017,7 +70017,7 @@
         <v>45763</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70095,7 +70095,7 @@
         <v>46288</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70173,7 +70173,7 @@
         <v>45271</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70246,7 +70246,7 @@
         <v>46289</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70324,7 +70324,7 @@
         <v>44808</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70397,7 +70397,7 @@
         <v>45019</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70470,7 +70470,7 @@
         <v>44603</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70543,7 +70543,7 @@
         <v>45622</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70616,7 +70616,7 @@
         <v>44967</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70689,7 +70689,7 @@
         <v>44967</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70762,7 +70762,7 @@
         <v>45544</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70835,7 +70835,7 @@
         <v>45617</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70913,7 +70913,7 @@
         <v>44907</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70991,7 +70991,7 @@
         <v>46288</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71069,7 +71069,7 @@
         <v>46289</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71142,7 +71142,7 @@
         <v>45539</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71215,7 +71215,7 @@
         <v>45604</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71293,7 +71293,7 @@
         <v>45607</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71366,7 +71366,7 @@
         <v>45545</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71444,7 +71444,7 @@
         <v>45422</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71522,7 +71522,7 @@
         <v>45618</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71600,7 +71600,7 @@
         <v>46293</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71678,7 +71678,7 @@
         <v>46293</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71756,7 +71756,7 @@
         <v>45076</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71829,7 +71829,7 @@
         <v>45439</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71902,7 +71902,7 @@
         <v>44699</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71975,7 +71975,7 @@
         <v>45357</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72048,7 +72048,7 @@
         <v>45175</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72121,7 +72121,7 @@
         <v>45733</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72199,7 +72199,7 @@
         <v>45615</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72272,7 +72272,7 @@
         <v>46251</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72350,7 +72350,7 @@
         <v>46100</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72423,7 +72423,7 @@
         <v>44964</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72501,7 +72501,7 @@
         <v>46198</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72579,7 +72579,7 @@
         <v>46294</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72657,7 +72657,7 @@
         <v>46099</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72735,7 +72735,7 @@
         <v>44908</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72813,7 +72813,7 @@
         <v>46069</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72886,7 +72886,7 @@
         <v>45422</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72964,7 +72964,7 @@
         <v>46231</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73037,7 +73037,7 @@
         <v>45506</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73115,7 +73115,7 @@
         <v>44595</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73188,7 +73188,7 @@
         <v>45622</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73266,7 +73266,7 @@
         <v>45622</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73344,7 +73344,7 @@
         <v>45177</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73422,7 +73422,7 @@
         <v>45719</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73500,7 +73500,7 @@
         <v>45260</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73573,7 +73573,7 @@
         <v>46202</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73646,7 +73646,7 @@
         <v>45687</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73719,7 +73719,7 @@
         <v>46253</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73792,7 +73792,7 @@
         <v>45741</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73865,7 +73865,7 @@
         <v>46254</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73943,7 +73943,7 @@
         <v>44859</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74016,7 +74016,7 @@
         <v>45545</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74089,7 +74089,7 @@
         <v>44502</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74162,7 +74162,7 @@
         <v>45124</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74235,7 +74235,7 @@
         <v>44789</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74308,7 +74308,7 @@
         <v>44789</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74381,7 +74381,7 @@
         <v>45489</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74459,7 +74459,7 @@
         <v>45301</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74532,7 +74532,7 @@
         <v>46296</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74610,7 +74610,7 @@
         <v>46071</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74683,7 +74683,7 @@
         <v>46253</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74761,7 +74761,7 @@
         <v>46253</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74839,7 +74839,7 @@
         <v>46272</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74912,7 +74912,7 @@
         <v>46253</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -74990,7 +74990,7 @@
         <v>45636</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75063,7 +75063,7 @@
         <v>46300</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75141,7 +75141,7 @@
         <v>46255</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75214,7 +75214,7 @@
         <v>45763</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75287,7 +75287,7 @@
         <v>45777</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75365,7 +75365,7 @@
         <v>46300</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75443,7 +75443,7 @@
         <v>45763</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75521,7 +75521,7 @@
         <v>45763</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75599,7 +75599,7 @@
         <v>45783</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75672,7 +75672,7 @@
         <v>46258</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75745,7 +75745,7 @@
         <v>44999</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75818,7 +75818,7 @@
         <v>46127</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75891,7 +75891,7 @@
         <v>45498</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75969,7 +75969,7 @@
         <v>45784</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76042,7 +76042,7 @@
         <v>45120</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76115,7 +76115,7 @@
         <v>46136</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76188,7 +76188,7 @@
         <v>46184</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76261,7 +76261,7 @@
         <v>45786</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76339,7 +76339,7 @@
         <v>45786</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76417,7 +76417,7 @@
         <v>46302</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76495,7 +76495,7 @@
         <v>46259</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76573,7 +76573,7 @@
         <v>44525</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76651,7 +76651,7 @@
         <v>46302</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76724,7 +76724,7 @@
         <v>44788</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76797,7 +76797,7 @@
         <v>45758</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76875,7 +76875,7 @@
         <v>46302</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76953,7 +76953,7 @@
         <v>46078</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77026,7 +77026,7 @@
         <v>45790</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77099,7 +77099,7 @@
         <v>45791</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77172,7 +77172,7 @@
         <v>46079</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77245,7 +77245,7 @@
         <v>46031</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77318,7 +77318,7 @@
         <v>46302</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77391,7 +77391,7 @@
         <v>45791</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77464,7 +77464,7 @@
         <v>45791</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77537,7 +77537,7 @@
         <v>45754</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77615,7 +77615,7 @@
         <v>46259</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77688,7 +77688,7 @@
         <v>46227</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77761,7 +77761,7 @@
         <v>45055</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77834,7 +77834,7 @@
         <v>45793</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77912,7 +77912,7 @@
         <v>45236</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77990,7 +77990,7 @@
         <v>45792</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78063,7 +78063,7 @@
         <v>45793</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78141,7 +78141,7 @@
         <v>46262</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78214,7 +78214,7 @@
         <v>45796</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78292,7 +78292,7 @@
         <v>45191</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78365,7 +78365,7 @@
         <v>46261</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78438,7 +78438,7 @@
         <v>45796</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78511,7 +78511,7 @@
         <v>45569</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78589,7 +78589,7 @@
         <v>45799</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78667,7 +78667,7 @@
         <v>45463</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78740,7 +78740,7 @@
         <v>45540</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78813,7 +78813,7 @@
         <v>45586</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78886,7 +78886,7 @@
         <v>45532</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78959,7 +78959,7 @@
         <v>45799</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79037,7 +79037,7 @@
         <v>46307</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79115,7 +79115,7 @@
         <v>45802</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79193,7 +79193,7 @@
         <v>45802</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79271,7 +79271,7 @@
         <v>46309</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79349,7 +79349,7 @@
         <v>46265</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79427,7 +79427,7 @@
         <v>45799</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79500,7 +79500,7 @@
         <v>45802</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79578,7 +79578,7 @@
         <v>44953</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79656,7 +79656,7 @@
         <v>44873</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79729,7 +79729,7 @@
         <v>45306</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79802,7 +79802,7 @@
         <v>44960</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79875,7 +79875,7 @@
         <v>45259</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79948,7 +79948,7 @@
         <v>45309</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80021,7 +80021,7 @@
         <v>46007</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80094,7 +80094,7 @@
         <v>45812</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80167,7 +80167,7 @@
         <v>45646</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80240,7 +80240,7 @@
         <v>45813</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80313,7 +80313,7 @@
         <v>46269</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80386,7 +80386,7 @@
         <v>45812</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80464,7 +80464,7 @@
         <v>45663</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80537,7 +80537,7 @@
         <v>45817</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80615,7 +80615,7 @@
         <v>45817</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80693,7 +80693,7 @@
         <v>45817</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80771,7 +80771,7 @@
         <v>44540</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80849,7 +80849,7 @@
         <v>46007</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80922,7 +80922,7 @@
         <v>45824</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81000,7 +81000,7 @@
         <v>45825</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81073,7 +81073,7 @@
         <v>45826</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81151,7 +81151,7 @@
         <v>45827</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81229,7 +81229,7 @@
         <v>45826</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81307,7 +81307,7 @@
         <v>45832</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81380,7 +81380,7 @@
         <v>45832</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81458,7 +81458,7 @@
         <v>45832</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81536,7 +81536,7 @@
         <v>45835</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81609,7 +81609,7 @@
         <v>45835</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81682,7 +81682,7 @@
         <v>45835</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81760,7 +81760,7 @@
         <v>45839</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81838,7 +81838,7 @@
         <v>45554</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81911,7 +81911,7 @@
         <v>45840</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81989,7 +81989,7 @@
         <v>45841</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82067,7 +82067,7 @@
         <v>45841</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82145,7 +82145,7 @@
         <v>45841</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82223,7 +82223,7 @@
         <v>45846</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82301,7 +82301,7 @@
         <v>45846</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82379,7 +82379,7 @@
         <v>45848</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82457,7 +82457,7 @@
         <v>45848</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82535,7 +82535,7 @@
         <v>45848</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82608,7 +82608,7 @@
         <v>45695</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82681,7 +82681,7 @@
         <v>45860</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82759,7 +82759,7 @@
         <v>45860</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82832,7 +82832,7 @@
         <v>45859</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82905,7 +82905,7 @@
         <v>45881</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82978,7 +82978,7 @@
         <v>45880</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83056,7 +83056,7 @@
         <v>45883</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83129,7 +83129,7 @@
         <v>45880</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83202,7 +83202,7 @@
         <v>45882</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83280,7 +83280,7 @@
         <v>45238</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83358,7 +83358,7 @@
         <v>45238</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83436,7 +83436,7 @@
         <v>44538</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83514,7 +83514,7 @@
         <v>45238</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83592,7 +83592,7 @@
         <v>45670</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83670,7 +83670,7 @@
         <v>45238</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83748,7 +83748,7 @@
         <v>45670</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83826,7 +83826,7 @@
         <v>45238</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83904,7 +83904,7 @@
         <v>44929</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83982,7 +83982,7 @@
         <v>45238</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84060,7 +84060,7 @@
         <v>45386</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84133,7 +84133,7 @@
         <v>45238</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84211,7 +84211,7 @@
         <v>45238</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84289,7 +84289,7 @@
         <v>45670</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84367,7 +84367,7 @@
         <v>45238</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84445,7 +84445,7 @@
         <v>45238</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84523,7 +84523,7 @@
         <v>45238</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84601,7 +84601,7 @@
         <v>45670</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84679,7 +84679,7 @@
         <v>45238</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84757,7 +84757,7 @@
         <v>45670</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -84835,7 +84835,7 @@
         <v>45670</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -84933,7 +84933,7 @@
         <v>46083</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -85011,7 +85011,7 @@
         <v>45650</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -601,7 +601,7 @@
         <v>45979</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45664</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44643</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45238</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45245</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45960</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>44771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>46019</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45478</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45502</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>44840</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>45734</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>46057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>45091</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45595</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>45950</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45981</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45219</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>46073</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45544</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44972</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45323</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45670</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45686</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>45502</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45297</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>45994</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46034</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>46043</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>46043</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>46070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>46114</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>45295</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>44884</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45106</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>46244</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45670</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45728</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44594</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44685</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45478</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>45631</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>44951</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45029</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>45056</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44964</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44673</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>45931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>44586</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45296</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45971</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>45979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>45995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>46085</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>46177</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45741</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>46182</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>45072</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45673</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45320</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>45734</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>46038</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>45775</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45763</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45791</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45799</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>45834</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44959</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44490</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>44825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44767</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>44711</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44774</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>44876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>44547</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44811</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44686</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44781</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44765</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44605</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44713</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>44823</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44879</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44722</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44816</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44831</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44741</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44812</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44546</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>44502</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>44651</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44509</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44739</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>44692</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>44691</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44797</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44544</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44853</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44545</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>44634</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>44732</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>44490</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44525</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44830</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44692</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44620</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44743</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44711</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44840</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44764</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44552</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44728</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>44831</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44728</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44571</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>44502</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>44820</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>44586</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>44728</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>44530</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>44503</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44711</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>44566</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44785</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44704</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>44684</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>44728</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>44692</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44659</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>45163</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>45775</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>44692</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45644</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45289</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45103</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45726</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44886</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45573</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45041</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45188</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>44503</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45068</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>45041</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44862</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45625</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>44599</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45631</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>45139</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>44894</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45352</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>45170</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>44994</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45642</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>45070</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45169</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>44601</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>44830</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>45621</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45345</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>45345</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>44895</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>44900</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45001</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45762</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>44783</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45691</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45253</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44795</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45309</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45149</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45533</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45610</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45622</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45336</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>45343</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>44886</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45397</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45566</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>44806</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45559</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45622</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45306</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45680</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45555</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44945</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45511</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>45646</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45426</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45176</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44678</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45562</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45037</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>45554</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45637</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>45670</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45622</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45622</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>44560</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45196</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>45243</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45419</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45623</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45425</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45183</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45236</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45189</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>44907</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44998</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>45148</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>45642</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>44781</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45758</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>44608</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45120</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45541</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44811</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45131</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45271</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45216</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44768</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45463</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45089</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45671</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>45677</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45646</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45184</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45499</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45883</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>45915</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>46043</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>46019</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>46033</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>45884</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>44664</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45824</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45176</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>45610</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45596</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45884</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45103</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45166</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44573</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44945</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45497</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>45223</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>46139</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45888</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>46048</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>46136</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>45888</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>45525</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45434</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>44748</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45890</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>46043</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45044</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45701</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>46136</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>46135</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>45855</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>45897</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>45897</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45896</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>45861</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45896</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45896</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>45896</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45509</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45897</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>45898</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>46048</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>46026</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>45951</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45884</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>46055</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>46021</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>46140</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>46031</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44788</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>46084</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>46054</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>45903</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>46070</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>46048</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45880</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>46140</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>46098</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>46038</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>45904</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45789</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>45904</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>45908</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45636</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45232</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45909</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45908</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45250</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45911</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>45915</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>45169</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>44886</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45546</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>45546</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45915</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>46146</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>45917</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>46119</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45917</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>46146</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>46035</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45917</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45919</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>46146</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45918</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45918</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45259</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45918</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>46146</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>46038</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45923</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>46055</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>44874</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>46030</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45924</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>44833</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45924</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>45925</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45170</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>44607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>46149</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>46149</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>44824</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44644</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>45912</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>45931</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>46128</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>45931</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>45222</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45936</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>45936</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>45936</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30381,7 +30381,7 @@
         <v>45936</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>45324</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45937</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>45938</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>45566</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30746,7 +30746,7 @@
         <v>45938</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>45938</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>45938</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>45939</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>45938</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>45938</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45489</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45938</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>45938</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>45938</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45939</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45938</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>45544</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>45937</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>45939</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>45939</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>45938</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>46155</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32065,7 +32065,7 @@
         <v>46119</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45946</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45947</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45946</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>45641</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>45946</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45642</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>45947</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45947</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45938</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>46042</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45950</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>46155</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45950</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>46026</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>45950</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45951</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>44964</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>46155</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45579</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>46035</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45429</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45429</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45946</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>46052</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>46157</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44915</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45042</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45537</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>45958</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>45959</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>45960</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>46161</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45618</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>45965</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>46160</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>45313</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>45712</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>45089</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45079</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45971</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>45971</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45208</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>46043</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45043</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>45971</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>45968</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45971</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>44832</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>46163</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>45973</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45973</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45973</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45222</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45973</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>45973</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>44686</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>44601</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45741</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>46051</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44704</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>45974</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>45636</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>46136</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36832,7 +36832,7 @@
         <v>45974</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         <v>45979</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
         <v>45141</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37056,7 +37056,7 @@
         <v>46111</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44652</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>45297</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45624</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45729</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>45743</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>45981</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45980</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45980</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>46164</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>46167</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45985</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>45303</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>44783</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>45985</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>45568</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45985</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>45985</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45986</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>46164</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45545</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45537</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45985</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45987</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>45273</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>46167</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>45748</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>44616</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>46169</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45020</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45020</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45197</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>45993</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>44987</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45428</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45607</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45995</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45994</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>45999</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45631</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>45618</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45546</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>46000</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>46168</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>44512</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40421,7 +40421,7 @@
         <v>46000</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>45246</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>46003</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>46170</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>46170</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>45628</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>44811</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>45603</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45603</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>44790</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45579</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>46006</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>46006</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45399</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>45635</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45525</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>45537</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>46035</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>46008</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>45622</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45622</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45667</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45670</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45287</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>45455</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45950</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>44596</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>46029</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42510,7 +42510,7 @@
         <v>46030</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42583,7 +42583,7 @@
         <v>46171</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>46171</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>44777</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>46021</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>46171</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>46043</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>45566</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>46024</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>46026</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45758</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>46176</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>45618</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45686</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>46030</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>46031</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>46030</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>46030</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>46175</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>46034</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>46175</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>44552</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>45604</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>46035</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>46035</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>46037</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>46037</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>46051</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46043</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>46042</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>46037</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44818,7 +44818,7 @@
         <v>46079</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44891,7 +44891,7 @@
         <v>46041</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>46038</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>46038</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>46039</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>46177</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>46178</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>46043</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>44797</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>46043</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>46043</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>46043</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>46043</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>46043</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>46043</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45928,7 +45928,7 @@
         <v>46179</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46001,7 +46001,7 @@
         <v>46177</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>46042</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>45532</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>46042</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>46042</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>46043</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>46043</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46512,7 +46512,7 @@
         <v>44812</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>46044</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>46044</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45754</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>46044</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>46045</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46960,7 +46960,7 @@
         <v>46045</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>46045</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>46044</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>46044</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45601</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>46069</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47398,7 +47398,7 @@
         <v>46048</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>46048</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>46084</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47617,7 +47617,7 @@
         <v>45499</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>46048</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>45140</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
         <v>46048</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>46051</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>46051</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>46050</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>46050</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>46050</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>46050</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>46051</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>46051</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>46181</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>46053</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48659,7 +48659,7 @@
         <v>46055</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45231</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48810,7 +48810,7 @@
         <v>46055</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48888,7 +48888,7 @@
         <v>46055</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>46052</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49034,7 +49034,7 @@
         <v>46053</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>46182</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>46056</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>46057</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>46181</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49409,7 +49409,7 @@
         <v>46057</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>46057</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45671</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49633,7 +49633,7 @@
         <v>46056</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49706,7 +49706,7 @@
         <v>45297</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49784,7 +49784,7 @@
         <v>46183</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
         <v>46062</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>46062</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50003,7 +50003,7 @@
         <v>46062</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>46062</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>46062</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>46062</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>46063</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>46062</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>45090</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50519,7 +50519,7 @@
         <v>46063</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>44797</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>46064</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50743,7 +50743,7 @@
         <v>46064</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>46065</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>46064</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>46064</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>46065</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>46064</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>46069</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51259,7 +51259,7 @@
         <v>46066</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51332,7 +51332,7 @@
         <v>46184</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>46069</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51483,7 +51483,7 @@
         <v>45072</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>46188</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>46066</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         <v>46069</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>46188</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51858,7 +51858,7 @@
         <v>46030</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51936,7 +51936,7 @@
         <v>46071</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>46071</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>46071</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52155,7 +52155,7 @@
         <v>46070</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52228,7 +52228,7 @@
         <v>46070</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>46185</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>46071</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52447,7 +52447,7 @@
         <v>46071</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>46070</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>46073</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52666,7 +52666,7 @@
         <v>46072</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>46072</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>46188</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>46188</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52963,7 +52963,7 @@
         <v>46073</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53036,7 +53036,7 @@
         <v>46072</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53114,7 +53114,7 @@
         <v>44960</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>46076</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53265,7 +53265,7 @@
         <v>45170</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>45121</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>46073</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53489,7 +53489,7 @@
         <v>46076</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53562,7 +53562,7 @@
         <v>46078</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>46079</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>46185</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>46079</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>46188</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>46079</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>46080</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54088,7 +54088,7 @@
         <v>46084</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45058</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54234,7 +54234,7 @@
         <v>46084</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54307,7 +54307,7 @@
         <v>46084</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>46084</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54453,7 +54453,7 @@
         <v>46084</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54526,7 +54526,7 @@
         <v>46084</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54599,7 +54599,7 @@
         <v>45541</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54677,7 +54677,7 @@
         <v>46086</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>46043</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>46087</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
         <v>45733</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54974,7 +54974,7 @@
         <v>46087</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55047,7 +55047,7 @@
         <v>45757</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55125,7 +55125,7 @@
         <v>46090</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55198,7 +55198,7 @@
         <v>45902</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55271,7 +55271,7 @@
         <v>46090</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55344,7 +55344,7 @@
         <v>45373</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55422,7 +55422,7 @@
         <v>45636</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55500,7 +55500,7 @@
         <v>46092</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55578,7 +55578,7 @@
         <v>45545</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55656,7 +55656,7 @@
         <v>45034</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>44690</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55807,7 +55807,7 @@
         <v>46093</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55880,7 +55880,7 @@
         <v>46098</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55953,7 +55953,7 @@
         <v>46098</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56026,7 +56026,7 @@
         <v>46098</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>46195</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56177,7 +56177,7 @@
         <v>46097</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>46098</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>46099</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>46196</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56479,7 +56479,7 @@
         <v>45579</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>45140</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56625,7 +56625,7 @@
         <v>46195</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56698,7 +56698,7 @@
         <v>46195</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>46104</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>46104</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56917,7 +56917,7 @@
         <v>46125</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56990,7 +56990,7 @@
         <v>46196</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57068,7 +57068,7 @@
         <v>45204</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57141,7 +57141,7 @@
         <v>46196</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57219,7 +57219,7 @@
         <v>45631</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>46107</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>44930</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         <v>44938</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57526,7 +57526,7 @@
         <v>46111</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57604,7 +57604,7 @@
         <v>46111</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57677,7 +57677,7 @@
         <v>46111</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>46112</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57828,7 +57828,7 @@
         <v>46112</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>46112</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57979,7 +57979,7 @@
         <v>46111</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>46111</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58135,7 +58135,7 @@
         <v>46111</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58213,7 +58213,7 @@
         <v>46198</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>44960</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58364,7 +58364,7 @@
         <v>46198</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>46178</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58510,7 +58510,7 @@
         <v>46197</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58583,7 +58583,7 @@
         <v>45364</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>46113</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58739,7 +58739,7 @@
         <v>46113</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58812,7 +58812,7 @@
         <v>45539</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58885,7 +58885,7 @@
         <v>46198</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58958,7 +58958,7 @@
         <v>46118</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59031,7 +59031,7 @@
         <v>46120</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59104,7 +59104,7 @@
         <v>46119</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59177,7 +59177,7 @@
         <v>46119</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59250,7 +59250,7 @@
         <v>46120</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59323,7 +59323,7 @@
         <v>46119</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45358</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59474,7 +59474,7 @@
         <v>46120</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59547,7 +59547,7 @@
         <v>46120</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59620,7 +59620,7 @@
         <v>46120</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59693,7 +59693,7 @@
         <v>46120</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59766,7 +59766,7 @@
         <v>44952</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>46120</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59917,7 +59917,7 @@
         <v>46122</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>46126</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60068,7 +60068,7 @@
         <v>46126</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60146,7 +60146,7 @@
         <v>46062</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60219,7 +60219,7 @@
         <v>46125</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60292,7 +60292,7 @@
         <v>45582</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>46126</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60448,7 +60448,7 @@
         <v>44729</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60521,7 +60521,7 @@
         <v>46100</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60594,7 +60594,7 @@
         <v>44713</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>44765</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>46133</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60813,7 +60813,7 @@
         <v>45545</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60891,7 +60891,7 @@
         <v>46112</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60964,7 +60964,7 @@
         <v>45771</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61042,7 +61042,7 @@
         <v>46134</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61120,7 +61120,7 @@
         <v>46134</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61198,7 +61198,7 @@
         <v>45637</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61271,7 +61271,7 @@
         <v>45063</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61349,7 +61349,7 @@
         <v>46204</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61427,7 +61427,7 @@
         <v>46136</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61500,7 +61500,7 @@
         <v>45037</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61573,7 +61573,7 @@
         <v>45149</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61646,7 +61646,7 @@
         <v>45175</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>46030</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61792,7 +61792,7 @@
         <v>46073</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61865,7 +61865,7 @@
         <v>46021</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61938,7 +61938,7 @@
         <v>46206</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62011,7 +62011,7 @@
         <v>44900</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62089,7 +62089,7 @@
         <v>44900</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62167,7 +62167,7 @@
         <v>44704</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62240,7 +62240,7 @@
         <v>45607</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62318,7 +62318,7 @@
         <v>45607</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62396,7 +62396,7 @@
         <v>45616</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62469,7 +62469,7 @@
         <v>46206</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62542,7 +62542,7 @@
         <v>46206</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62615,7 +62615,7 @@
         <v>45590</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62688,7 +62688,7 @@
         <v>44763</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62766,7 +62766,7 @@
         <v>45154</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62839,7 +62839,7 @@
         <v>45504</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62912,7 +62912,7 @@
         <v>45219</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62990,7 +62990,7 @@
         <v>45695</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63063,7 +63063,7 @@
         <v>46209</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63136,7 +63136,7 @@
         <v>44679</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63214,7 +63214,7 @@
         <v>45617</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63292,7 +63292,7 @@
         <v>44628</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63365,7 +63365,7 @@
         <v>46209</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63438,7 +63438,7 @@
         <v>46209</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63511,7 +63511,7 @@
         <v>46209</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63584,7 +63584,7 @@
         <v>45607</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63657,7 +63657,7 @@
         <v>46213</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63730,7 +63730,7 @@
         <v>46213</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63803,7 +63803,7 @@
         <v>45617</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63881,7 +63881,7 @@
         <v>45719</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63959,7 +63959,7 @@
         <v>46066</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64032,7 +64032,7 @@
         <v>45729</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64110,7 +64110,7 @@
         <v>44739</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64183,7 +64183,7 @@
         <v>46213</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64256,7 +64256,7 @@
         <v>46043</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64329,7 +64329,7 @@
         <v>45574</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64402,7 +64402,7 @@
         <v>45173</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64475,7 +64475,7 @@
         <v>45644</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64553,7 +64553,7 @@
         <v>46184</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64626,7 +64626,7 @@
         <v>46184</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64699,7 +64699,7 @@
         <v>44938</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64772,7 +64772,7 @@
         <v>45187</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64845,7 +64845,7 @@
         <v>46220</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64918,7 +64918,7 @@
         <v>46220</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -64996,7 +64996,7 @@
         <v>46220</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65074,7 +65074,7 @@
         <v>46220</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65147,7 +65147,7 @@
         <v>45062</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65220,7 +65220,7 @@
         <v>46223</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65298,7 +65298,7 @@
         <v>46226</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65371,7 +65371,7 @@
         <v>44952</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65449,7 +65449,7 @@
         <v>44952</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65527,7 +65527,7 @@
         <v>46226</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65600,7 +65600,7 @@
         <v>45513</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65678,7 +65678,7 @@
         <v>44551</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65751,7 +65751,7 @@
         <v>45142</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65829,7 +65829,7 @@
         <v>46273</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65907,7 +65907,7 @@
         <v>45142</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -65985,7 +65985,7 @@
         <v>46272</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66058,7 +66058,7 @@
         <v>46273</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66131,7 +66131,7 @@
         <v>46272</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66204,7 +66204,7 @@
         <v>45462</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66277,7 +66277,7 @@
         <v>45770</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66350,7 +66350,7 @@
         <v>46273</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66423,7 +66423,7 @@
         <v>44868</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66501,7 +66501,7 @@
         <v>46275</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66574,7 +66574,7 @@
         <v>46274</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66647,7 +66647,7 @@
         <v>45252</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -66720,7 +66720,7 @@
         <v>46274</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -66793,7 +66793,7 @@
         <v>45603</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -66871,7 +66871,7 @@
         <v>45489</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -66949,7 +66949,7 @@
         <v>45463</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -67027,7 +67027,7 @@
         <v>45617</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -67105,7 +67105,7 @@
         <v>44869</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -67178,7 +67178,7 @@
         <v>46234</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -67256,7 +67256,7 @@
         <v>45687</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -67329,7 +67329,7 @@
         <v>44999</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -67402,7 +67402,7 @@
         <v>44965</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -67475,7 +67475,7 @@
         <v>44939</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -67548,7 +67548,7 @@
         <v>45639</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -67621,7 +67621,7 @@
         <v>45020</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -67699,7 +67699,7 @@
         <v>45271</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -67777,7 +67777,7 @@
         <v>45642</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -67850,7 +67850,7 @@
         <v>45632</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -67928,7 +67928,7 @@
         <v>46280</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -68001,7 +68001,7 @@
         <v>46280</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -68074,7 +68074,7 @@
         <v>44547</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -68147,7 +68147,7 @@
         <v>45223</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -68225,7 +68225,7 @@
         <v>46238</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -68298,7 +68298,7 @@
         <v>44589</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -68371,7 +68371,7 @@
         <v>45593</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -68444,7 +68444,7 @@
         <v>44985</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -68522,7 +68522,7 @@
         <v>46283</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -68595,7 +68595,7 @@
         <v>46184</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -68668,7 +68668,7 @@
         <v>45622</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -68746,7 +68746,7 @@
         <v>45372</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -68824,7 +68824,7 @@
         <v>45019</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -68897,7 +68897,7 @@
         <v>45770</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -68970,7 +68970,7 @@
         <v>46282</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -69043,7 +69043,7 @@
         <v>46185</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -69121,7 +69121,7 @@
         <v>44720</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -69194,7 +69194,7 @@
         <v>45382</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -69267,7 +69267,7 @@
         <v>44844</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -69345,7 +69345,7 @@
         <v>44967</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -69423,7 +69423,7 @@
         <v>44943</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -69496,7 +69496,7 @@
         <v>46244</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -69569,7 +69569,7 @@
         <v>45567</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -69642,7 +69642,7 @@
         <v>45636</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -69720,7 +69720,7 @@
         <v>45624</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -69793,7 +69793,7 @@
         <v>45632</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -69871,7 +69871,7 @@
         <v>46244</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -69944,7 +69944,7 @@
         <v>46241</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -70017,7 +70017,7 @@
         <v>45763</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -70095,7 +70095,7 @@
         <v>46288</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -70173,7 +70173,7 @@
         <v>45271</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -70246,7 +70246,7 @@
         <v>46289</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -70324,7 +70324,7 @@
         <v>44808</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -70397,7 +70397,7 @@
         <v>45019</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -70470,7 +70470,7 @@
         <v>44603</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -70543,7 +70543,7 @@
         <v>45622</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -70616,7 +70616,7 @@
         <v>44967</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -70689,7 +70689,7 @@
         <v>44967</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -70762,7 +70762,7 @@
         <v>45544</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -70835,7 +70835,7 @@
         <v>45617</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -70913,7 +70913,7 @@
         <v>44907</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -70991,7 +70991,7 @@
         <v>46288</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -71069,7 +71069,7 @@
         <v>46289</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -71142,7 +71142,7 @@
         <v>45539</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -71215,7 +71215,7 @@
         <v>45604</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -71293,7 +71293,7 @@
         <v>45607</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -71366,7 +71366,7 @@
         <v>45545</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -71444,7 +71444,7 @@
         <v>45422</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -71522,7 +71522,7 @@
         <v>45618</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -71600,7 +71600,7 @@
         <v>46293</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -71678,7 +71678,7 @@
         <v>46293</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -71756,7 +71756,7 @@
         <v>45076</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -71829,7 +71829,7 @@
         <v>45439</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -71902,7 +71902,7 @@
         <v>44699</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -71975,7 +71975,7 @@
         <v>45357</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -72048,7 +72048,7 @@
         <v>45175</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -72121,7 +72121,7 @@
         <v>45733</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -72199,7 +72199,7 @@
         <v>45615</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -72272,7 +72272,7 @@
         <v>46251</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -72350,7 +72350,7 @@
         <v>46100</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -72423,7 +72423,7 @@
         <v>44964</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -72501,7 +72501,7 @@
         <v>46198</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -72579,7 +72579,7 @@
         <v>46294</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -72657,7 +72657,7 @@
         <v>46099</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -72735,7 +72735,7 @@
         <v>44908</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -72813,7 +72813,7 @@
         <v>46069</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -72886,7 +72886,7 @@
         <v>45422</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -72964,7 +72964,7 @@
         <v>46231</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -73037,7 +73037,7 @@
         <v>45506</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -73115,7 +73115,7 @@
         <v>44595</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -73188,7 +73188,7 @@
         <v>45622</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -73266,7 +73266,7 @@
         <v>45622</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -73344,7 +73344,7 @@
         <v>45177</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -73422,7 +73422,7 @@
         <v>45719</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -73500,7 +73500,7 @@
         <v>45260</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -73573,7 +73573,7 @@
         <v>46202</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -73646,7 +73646,7 @@
         <v>45687</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -73719,7 +73719,7 @@
         <v>46253</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -73792,7 +73792,7 @@
         <v>45741</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -73865,7 +73865,7 @@
         <v>46254</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -73943,7 +73943,7 @@
         <v>44859</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -74016,7 +74016,7 @@
         <v>45545</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -74089,7 +74089,7 @@
         <v>44502</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -74162,7 +74162,7 @@
         <v>45124</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -74235,7 +74235,7 @@
         <v>44789</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -74308,7 +74308,7 @@
         <v>44789</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -74381,7 +74381,7 @@
         <v>45489</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -74459,7 +74459,7 @@
         <v>45301</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -74532,7 +74532,7 @@
         <v>46296</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -74610,7 +74610,7 @@
         <v>46071</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -74683,7 +74683,7 @@
         <v>46253</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -74761,7 +74761,7 @@
         <v>46253</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -74839,7 +74839,7 @@
         <v>46272</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -74912,7 +74912,7 @@
         <v>46253</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -74990,7 +74990,7 @@
         <v>45636</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -75063,7 +75063,7 @@
         <v>46300</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -75141,7 +75141,7 @@
         <v>46255</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -75214,7 +75214,7 @@
         <v>45763</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -75287,7 +75287,7 @@
         <v>45777</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -75365,7 +75365,7 @@
         <v>46300</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -75443,7 +75443,7 @@
         <v>45763</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -75521,7 +75521,7 @@
         <v>45763</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -75599,7 +75599,7 @@
         <v>45783</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -75672,7 +75672,7 @@
         <v>46258</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -75745,7 +75745,7 @@
         <v>44999</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -75818,7 +75818,7 @@
         <v>46127</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -75891,7 +75891,7 @@
         <v>45498</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -75969,7 +75969,7 @@
         <v>45784</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -76042,7 +76042,7 @@
         <v>45120</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -76115,7 +76115,7 @@
         <v>46136</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -76188,7 +76188,7 @@
         <v>46184</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -76261,7 +76261,7 @@
         <v>45786</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -76339,7 +76339,7 @@
         <v>45786</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -76417,7 +76417,7 @@
         <v>46302</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -76495,7 +76495,7 @@
         <v>46259</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -76573,7 +76573,7 @@
         <v>44525</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -76651,7 +76651,7 @@
         <v>46302</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -76724,7 +76724,7 @@
         <v>44788</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -76797,7 +76797,7 @@
         <v>45758</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -76875,7 +76875,7 @@
         <v>46302</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -76953,7 +76953,7 @@
         <v>46078</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -77026,7 +77026,7 @@
         <v>45790</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -77099,7 +77099,7 @@
         <v>45791</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -77172,7 +77172,7 @@
         <v>46079</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -77245,7 +77245,7 @@
         <v>46031</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -77318,7 +77318,7 @@
         <v>46302</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -77391,7 +77391,7 @@
         <v>45791</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -77464,7 +77464,7 @@
         <v>45791</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -77537,7 +77537,7 @@
         <v>45754</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -77615,7 +77615,7 @@
         <v>46259</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -77688,7 +77688,7 @@
         <v>46227</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -77761,7 +77761,7 @@
         <v>45055</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -77834,7 +77834,7 @@
         <v>45793</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -77912,7 +77912,7 @@
         <v>45236</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -77990,7 +77990,7 @@
         <v>45792</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -78063,7 +78063,7 @@
         <v>45793</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -78141,7 +78141,7 @@
         <v>46262</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -78214,7 +78214,7 @@
         <v>45796</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -78292,7 +78292,7 @@
         <v>45191</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -78365,7 +78365,7 @@
         <v>46261</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -78438,7 +78438,7 @@
         <v>45796</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -78511,7 +78511,7 @@
         <v>45569</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -78589,7 +78589,7 @@
         <v>45799</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -78667,7 +78667,7 @@
         <v>45463</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -78740,7 +78740,7 @@
         <v>45540</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -78813,7 +78813,7 @@
         <v>45586</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -78886,7 +78886,7 @@
         <v>45532</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -78959,7 +78959,7 @@
         <v>45799</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -79037,7 +79037,7 @@
         <v>46307</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -79115,7 +79115,7 @@
         <v>45802</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -79193,7 +79193,7 @@
         <v>45802</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -79271,7 +79271,7 @@
         <v>46309</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -79349,7 +79349,7 @@
         <v>46265</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -79427,7 +79427,7 @@
         <v>45799</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -79500,7 +79500,7 @@
         <v>45802</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -79578,7 +79578,7 @@
         <v>44953</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -79656,7 +79656,7 @@
         <v>44873</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -79729,7 +79729,7 @@
         <v>45306</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -79802,7 +79802,7 @@
         <v>44960</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -79875,7 +79875,7 @@
         <v>45259</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -79948,7 +79948,7 @@
         <v>45309</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -80021,7 +80021,7 @@
         <v>46007</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -80094,7 +80094,7 @@
         <v>45812</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -80167,7 +80167,7 @@
         <v>45646</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -80240,7 +80240,7 @@
         <v>45813</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -80313,7 +80313,7 @@
         <v>46269</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -80386,7 +80386,7 @@
         <v>45812</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -80464,7 +80464,7 @@
         <v>45663</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -80537,7 +80537,7 @@
         <v>45817</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -80615,7 +80615,7 @@
         <v>45817</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -80693,7 +80693,7 @@
         <v>45817</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -80771,7 +80771,7 @@
         <v>44540</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -80849,7 +80849,7 @@
         <v>46007</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -80922,7 +80922,7 @@
         <v>45824</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -81000,7 +81000,7 @@
         <v>45825</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -81073,7 +81073,7 @@
         <v>45826</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -81151,7 +81151,7 @@
         <v>45827</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -81229,7 +81229,7 @@
         <v>45826</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -81307,7 +81307,7 @@
         <v>45832</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -81380,7 +81380,7 @@
         <v>45832</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -81458,7 +81458,7 @@
         <v>45832</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -81536,7 +81536,7 @@
         <v>45835</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -81609,7 +81609,7 @@
         <v>45835</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -81682,7 +81682,7 @@
         <v>45835</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -81760,7 +81760,7 @@
         <v>45839</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -81838,7 +81838,7 @@
         <v>45554</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -81911,7 +81911,7 @@
         <v>45840</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -81989,7 +81989,7 @@
         <v>45841</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -82067,7 +82067,7 @@
         <v>45841</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -82145,7 +82145,7 @@
         <v>45841</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -82223,7 +82223,7 @@
         <v>45846</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -82301,7 +82301,7 @@
         <v>45846</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -82379,7 +82379,7 @@
         <v>45848</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -82457,7 +82457,7 @@
         <v>45848</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -82535,7 +82535,7 @@
         <v>45848</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -82608,7 +82608,7 @@
         <v>45695</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -82681,7 +82681,7 @@
         <v>45860</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -82759,7 +82759,7 @@
         <v>45860</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -82832,7 +82832,7 @@
         <v>45859</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -82905,7 +82905,7 @@
         <v>45881</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -82978,7 +82978,7 @@
         <v>45880</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -83056,7 +83056,7 @@
         <v>45883</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -83129,7 +83129,7 @@
         <v>45880</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -83202,7 +83202,7 @@
         <v>45882</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -83280,7 +83280,7 @@
         <v>45238</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -83358,7 +83358,7 @@
         <v>45238</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -83436,7 +83436,7 @@
         <v>44538</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -83514,7 +83514,7 @@
         <v>45238</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -83592,7 +83592,7 @@
         <v>45670</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -83670,7 +83670,7 @@
         <v>45238</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -83748,7 +83748,7 @@
         <v>45670</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -83826,7 +83826,7 @@
         <v>45238</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -83904,7 +83904,7 @@
         <v>44929</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -83982,7 +83982,7 @@
         <v>45238</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -84060,7 +84060,7 @@
         <v>45386</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -84133,7 +84133,7 @@
         <v>45238</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -84211,7 +84211,7 @@
         <v>45238</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -84289,7 +84289,7 @@
         <v>45670</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -84367,7 +84367,7 @@
         <v>45238</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -84445,7 +84445,7 @@
         <v>45238</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -84523,7 +84523,7 @@
         <v>45238</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -84601,7 +84601,7 @@
         <v>45670</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -84679,7 +84679,7 @@
         <v>45238</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -84757,7 +84757,7 @@
         <v>45670</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -84835,7 +84835,7 @@
         <v>45670</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -84933,7 +84933,7 @@
         <v>46083</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -85011,7 +85011,7 @@
         <v>45650</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>

--- a/Översikt NORDANSTIG.xlsx
+++ b/Översikt NORDANSTIG.xlsx
@@ -601,7 +601,7 @@
         <v>45979</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45664</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44643</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45238</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45245</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>45960</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45296</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>46019</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>44771</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45478</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45502</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>44840</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>45219</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45950</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>45981</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>46210</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>46073</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>46057</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45595</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>45734</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>44525</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>45544</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45323</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45670</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45106</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>45994</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46034</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>46043</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>46070</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>45295</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>46114</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>44884</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44690</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>45502</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45297</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45502</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45686</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>45670</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45728</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44594</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44685</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>45072</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>45741</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>46085</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>45931</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>46177</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>45296</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>46182</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>45971</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45979</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>45995</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>45478</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>45763</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>45791</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>46038</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>45799</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>45834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44951</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44673</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45056</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>45775</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45734</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44964</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>45631</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>44586</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>45673</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45320</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>44959</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>45670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44825</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44767</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44711</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>44876</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>44774</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>44547</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44811</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44728</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44686</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44781</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44765</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>44605</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>44713</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>44855</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>44823</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>44879</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44831</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44816</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44722</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44741</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44812</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44546</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44502</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>44651</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44509</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>44739</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>44692</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>44691</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>44797</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>44544</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44853</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44545</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44634</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44732</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>44525</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44830</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>44620</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44692</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>44743</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>44840</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44764</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>44711</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>44552</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>44728</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44831</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>44728</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44502</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44571</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44820</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>44586</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44728</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44785</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44530</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>44503</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>44711</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44566</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>44704</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45568</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>44692</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>44684</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45888</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>44734</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44728</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45883</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45246</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45888</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44790</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>45364</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45890</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45712</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45324</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44789</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44765</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>45043</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45855</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45539</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45607</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45089</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45896</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45861</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45896</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>45896</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45896</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45733</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45897</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45183</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45897</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>45880</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>45897</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45898</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>45541</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45544</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45884</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>45607</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44690</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45904</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>45382</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>45903</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45422</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>45883</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>45604</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45904</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45546</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45546</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>45908</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45908</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>46160</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45909</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45554</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>46136</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45622</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>46111</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>46051</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>46043</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>46161</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45770</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45770</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45911</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45915</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45915</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>45917</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>46164</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18730,7 +18730,7 @@
         <v>46163</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>46164</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45917</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45917</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>45918</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45918</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45918</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>46168</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>46167</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45919</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45924</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45923</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>46167</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>45924</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>45925</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>45252</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>46169</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>45741</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45680</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>46030</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20210,7 +20210,7 @@
         <v>46171</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>46171</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>45912</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>46043</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>45037</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45001</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>46029</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45931</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>46170</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45931</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>46171</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>46170</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>45936</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>46175</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>45936</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45936</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>46035</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45936</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45434</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45373</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>45419</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>45937</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>45937</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>45938</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45938</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45938</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>44886</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45938</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45938</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45497</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45938</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>46175</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>45938</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>45938</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
         <v>45938</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>45938</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>45938</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45939</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>45163</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>45939</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45939</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45939</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>44844</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>46176</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45428</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>45426</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>46177</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>46042</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>45562</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>44874</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45946</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45617</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>46079</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45566</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45946</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45357</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45946</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>46177</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45754</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>46084</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>45763</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>44945</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>45947</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45950</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45947</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>46181</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45559</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45947</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45950</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45950</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>46181</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>46051</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>45951</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>45019</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>46043</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>45303</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>46179</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>46178</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>45938</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45667</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>45670</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>45670</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>45677</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>45621</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>46183</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>45958</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>46182</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>46185</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>44832</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>46184</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45635</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45946</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>46185</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>45960</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45959</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>45089</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>46188</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>46188</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>45902</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>46188</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         <v>45965</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>46188</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>46188</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45968</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>44833</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>45607</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>45617</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>45758</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>46195</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>46195</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>46195</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>45971</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45971</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>45971</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45971</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>45232</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>45636</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45719</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>45973</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>46197</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>45169</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>45973</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>45973</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>45974</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45973</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>45973</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>46196</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>45726</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45622</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>46196</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>46196</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>45974</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>46178</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44781</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>46198</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>46198</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45623</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>46198</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>45124</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45103</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>45980</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>45980</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>45979</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>44938</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45981</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>44812</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>45463</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>44908</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>45985</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>45985</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>45537</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>45985</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45986</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31679,7 +31679,7 @@
         <v>46204</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44907</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31835,7 +31835,7 @@
         <v>45985</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>45985</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>45489</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>46209</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>46206</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>46206</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>45987</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>46206</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44713</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>45546</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>46209</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>46209</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>45579</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>46209</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>45632</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>46066</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>44552</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33081,7 +33081,7 @@
         <v>46213</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>46213</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>45139</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45993</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>46043</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>45994</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>46213</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45995</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>45636</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45999</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>46184</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>46000</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33967,7 +33967,7 @@
         <v>46184</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>46220</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>46223</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>46000</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>46220</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>46220</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>46220</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45777</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>46226</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>46006</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>46003</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45783</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45763</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>46006</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>46226</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45763</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>44999</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>45784</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>46008</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>45498</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>46280</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>45120</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>46280</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>46234</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>45950</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>45786</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>44525</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>46282</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>46021</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45754</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>46024</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>46026</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45786</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36451,7 +36451,7 @@
         <v>46238</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>46030</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>45791</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>46184</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>45758</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>46030</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>46030</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45792</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>45791</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>45055</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>45236</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44862</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>46034</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37410,7 +37410,7 @@
         <v>44788</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37483,7 +37483,7 @@
         <v>45791</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>46031</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>46035</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45790</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45796</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>46185</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>45793</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>46035</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>46038</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>46037</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>46037</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>45140</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>46037</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>46038</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>46283</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45537</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>46241</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45569</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>46042</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>45191</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>46042</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39041,7 +39041,7 @@
         <v>46039</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>45793</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45796</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>46042</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>46041</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>46288</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>46288</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>46244</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>46043</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>45463</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>46043</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45532</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>46043</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>46044</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>46043</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>46044</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>46043</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45540</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>46043</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>46043</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>46044</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>46044</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>46043</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>46043</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>46044</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>46048</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>46048</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>46048</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>45586</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>46045</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>46045</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>46048</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45799</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>46045</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41543,7 +41543,7 @@
         <v>46244</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>46050</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45799</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>46050</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41845,7 +41845,7 @@
         <v>46050</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>45799</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>46050</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>45802</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>46052</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>46051</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>46051</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42371,7 +42371,7 @@
         <v>46051</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>46051</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45802</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>46289</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>45802</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>44953</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42824,7 +42824,7 @@
         <v>46056</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42897,7 +42897,7 @@
         <v>46053</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>46053</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>46056</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43116,7 +43116,7 @@
         <v>46055</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43189,7 +43189,7 @@
         <v>45306</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>46055</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>46055</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>44873</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>46289</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>44960</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43642,7 +43642,7 @@
         <v>46057</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43715,7 +43715,7 @@
         <v>46057</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>46057</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45259</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>45309</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>46062</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>46062</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>45297</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44231,7 +44231,7 @@
         <v>46062</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>46062</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>46062</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45812</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44528,7 +44528,7 @@
         <v>46062</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         <v>46069</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>46062</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
         <v>46198</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         